--- a/Outputs/10_lepa_per_metric_comparison.xlsx
+++ b/Outputs/10_lepa_per_metric_comparison.xlsx
@@ -613,70 +613,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LTR127_2015</t>
+          <t>LTR386_2019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTR127</t>
+          <t>LTR386</t>
         </is>
       </c>
       <c r="C4">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D4">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.3888888888888889</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="H4">
-        <v>0.3888888888888888</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="I4">
-        <v>1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.06666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="K4">
-        <v>0.06666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.6198132780082988</v>
+        <v>0.7766089108910891</v>
       </c>
       <c r="N4">
-        <v>0.4680962343096234</v>
+        <v>0.5198019801980198</v>
       </c>
       <c r="O4">
-        <v>0.1517170436986754</v>
+        <v>0.2568069306930693</v>
       </c>
       <c r="P4">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="Q4">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="R4">
-        <v>0.07999999999999999</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U4" t="b">
@@ -686,61 +686,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR386_2019</t>
+          <t>LTR163_2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTR386</t>
+          <t>LTR163</t>
         </is>
       </c>
       <c r="C5">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.746031746031746</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="H5">
-        <v>0.746031746031746</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-0.009021842355175669</v>
       </c>
       <c r="J5">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.7766089108910891</v>
+        <v>0.7742011278195489</v>
       </c>
       <c r="N5">
-        <v>0.5198019801980198</v>
+        <v>0.5106132075471698</v>
       </c>
       <c r="O5">
-        <v>0.2568069306930693</v>
+        <v>0.2635879202723791</v>
       </c>
       <c r="P5">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="Q5">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="R5">
-        <v>0.07000000000000006</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -749,90 +749,90 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR163_2022</t>
+          <t>LTR127_2015</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTR163</t>
+          <t>LTR127</t>
         </is>
       </c>
       <c r="C6">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="D6">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E6">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G6">
-        <v>0.7564102564102564</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="H6">
-        <v>0.7654320987654321</v>
+        <v>0.4523809523809523</v>
       </c>
       <c r="I6">
-        <v>-0.009021842355175669</v>
+        <v>-0.06349206349206338</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K6">
-        <v>0.8</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.7742011278195489</v>
+        <v>0.6198132780082988</v>
       </c>
       <c r="N6">
-        <v>0.5106132075471698</v>
+        <v>0.4680962343096234</v>
       </c>
       <c r="O6">
-        <v>0.2635879202723791</v>
+        <v>0.1517170436986754</v>
       </c>
       <c r="P6">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="Q6">
-        <v>0.73</v>
+        <v>0.25</v>
       </c>
       <c r="R6">
-        <v>0.06000000000000005</v>
+        <v>0.06</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR127_2017</t>
+          <t>LTR127_2020</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="C7">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D7">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E7">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
-        <v>-5.551115123125783E-17</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.4333333333333333</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="H7">
-        <v>0.3888888888888888</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="I7">
-        <v>0.04444444444444456</v>
+        <v>-0.0263888888888888</v>
       </c>
       <c r="J7">
         <v>0.2</v>
@@ -871,31 +871,31 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.640194489465154</v>
+        <v>0.62902706185567</v>
       </c>
       <c r="N7">
-        <v>0.4558346839546191</v>
+        <v>0.390222293814433</v>
       </c>
       <c r="O7">
-        <v>0.1843598055105349</v>
+        <v>0.238804768041237</v>
       </c>
       <c r="P7">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="Q7">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="R7">
         <v>0.06</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U7" t="b">
@@ -905,70 +905,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR127_2020</t>
+          <t>LTR450_2015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTR127</t>
+          <t>LTR450</t>
         </is>
       </c>
       <c r="C8">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.5777777777777778</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="H8">
-        <v>0.5888888888888889</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="I8">
-        <v>-0.01111111111111107</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K8">
-        <v>0.2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.62902706185567</v>
+        <v>0.6028761061946902</v>
       </c>
       <c r="N8">
-        <v>0.390222293814433</v>
+        <v>0.3429203539823009</v>
       </c>
       <c r="O8">
-        <v>0.238804768041237</v>
+        <v>0.2599557522123893</v>
       </c>
       <c r="P8">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="Q8">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="R8">
         <v>0.06</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="U8" t="b">
@@ -978,147 +978,147 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR450_2015</t>
+          <t>LTR1466_2019</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTR450</t>
+          <t>LTR1466</t>
         </is>
       </c>
       <c r="C9">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D9">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E9">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.5277777777777778</v>
+        <v>0.7283950617283951</v>
       </c>
       <c r="H9">
-        <v>0.5277777777777778</v>
+        <v>0.7202380952380952</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.008156966490299844</v>
       </c>
       <c r="J9">
-        <v>0.06666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0.06666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="M9">
-        <v>0.6028761061946902</v>
+        <v>0.7776280323450135</v>
       </c>
       <c r="N9">
-        <v>0.3429203539823009</v>
+        <v>0.6024258760107817</v>
       </c>
       <c r="O9">
-        <v>0.2599557522123893</v>
+        <v>0.1752021563342319</v>
       </c>
       <c r="P9">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="Q9">
-        <v>0.32</v>
+        <v>0.77</v>
       </c>
       <c r="R9">
-        <v>0.06</v>
+        <v>0.05999999999999994</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTR1466_2019</t>
+          <t>LTR127_2017</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTR1466</t>
+          <t>LTR127</t>
         </is>
       </c>
       <c r="C10">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D10">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E10">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G10">
-        <v>0.7283950617283951</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="H10">
-        <v>0.7202380952380952</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="I10">
-        <v>0.008156966490299844</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K10">
-        <v>0.9333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="L10">
-        <v>0.06666666666666665</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.7776280323450135</v>
+        <v>0.640194489465154</v>
       </c>
       <c r="N10">
-        <v>0.6024258760107817</v>
+        <v>0.4558346839546191</v>
       </c>
       <c r="O10">
-        <v>0.1752021563342319</v>
+        <v>0.1843598055105349</v>
       </c>
       <c r="P10">
-        <v>0.83</v>
+        <v>0.36</v>
       </c>
       <c r="Q10">
-        <v>0.77</v>
+        <v>0.31</v>
       </c>
       <c r="R10">
-        <v>0.05999999999999994</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1367,10 +1367,10 @@
         <v>0.782051282051282</v>
       </c>
       <c r="H14">
-        <v>0.7884615384615384</v>
+        <v>0.7901234567901233</v>
       </c>
       <c r="I14">
-        <v>-0.006410256410256387</v>
+        <v>-0.008072174738841253</v>
       </c>
       <c r="J14">
         <v>0.4666666666666667</v>
@@ -2024,10 +2024,10 @@
         <v>0.7799999999999999</v>
       </c>
       <c r="H23">
-        <v>0.7799999999999999</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>-0.002051282051282355</v>
       </c>
       <c r="J23">
         <v>0.6</v>
@@ -2657,70 +2657,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LTR1063_2021</t>
+          <t>LTR86_2016</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTR1063</t>
+          <t>LTR86</t>
         </is>
       </c>
       <c r="C32">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D32">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E32">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F32">
-        <v>-5.551115123125783E-17</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G32">
-        <v>0.3958333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H32">
-        <v>0.3958333333333333</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>-0.02272727272727282</v>
       </c>
       <c r="J32">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K32">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2.775557561562891E-17</v>
       </c>
       <c r="M32">
-        <v>0.6405693950177935</v>
+        <v>0.7788944723618091</v>
       </c>
       <c r="N32">
-        <v>0.567170818505338</v>
+        <v>0.6752512562814069</v>
       </c>
       <c r="O32">
-        <v>0.07339857651245552</v>
+        <v>0.1036432160804022</v>
       </c>
       <c r="P32">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="Q32">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="R32">
-        <v>0.01999999999999996</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U32" t="b">
@@ -2730,58 +2730,58 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LTR308_2018</t>
+          <t>LTR1063_2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LTR308</t>
+          <t>LTR1063</t>
         </is>
       </c>
       <c r="C33">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D33">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E33">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G33">
-        <v>0.3541666666666667</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H33">
-        <v>0.3541666666666667</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="K33">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="L33">
-        <v>2.775557561562891E-17</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>0.6134259259259259</v>
+        <v>0.6405693950177935</v>
       </c>
       <c r="N33">
-        <v>0.5324074074074073</v>
+        <v>0.567170818505338</v>
       </c>
       <c r="O33">
-        <v>0.0810185185185186</v>
+        <v>0.07339857651245552</v>
       </c>
       <c r="P33">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="Q33">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="R33">
         <v>0.01999999999999996</v>
@@ -2803,70 +2803,70 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LTR1447_2022</t>
+          <t>LTR308_2018</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LTR1447</t>
+          <t>LTR308</t>
         </is>
       </c>
       <c r="C34">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D34">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E34">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.7828282828282829</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="H34">
-        <v>0.7828282828282829</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0.6</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K34">
-        <v>0.6</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.775557561562891E-17</v>
       </c>
       <c r="M34">
-        <v>1.052013422818792</v>
+        <v>0.6134259259259259</v>
       </c>
       <c r="N34">
-        <v>1.042506720430108</v>
+        <v>0.5324074074074073</v>
       </c>
       <c r="O34">
-        <v>0.009506702388683896</v>
+        <v>0.0810185185185186</v>
       </c>
       <c r="P34">
-        <v>0.78</v>
+        <v>0.36</v>
       </c>
       <c r="Q34">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="R34">
-        <v>0.01000000000000001</v>
+        <v>0.01999999999999996</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="U34" t="b">
@@ -2876,70 +2876,70 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LTR1488_2019</t>
+          <t>LTR1447_2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTR1488</t>
+          <t>LTR1447</t>
         </is>
       </c>
       <c r="C35">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D35">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E35">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.6666666666666666</v>
+        <v>0.7828282828282829</v>
       </c>
       <c r="H35">
-        <v>0.6960784313725491</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="I35">
-        <v>-0.02941176470588247</v>
+        <v>-0.001485442661913194</v>
       </c>
       <c r="J35">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="K35">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0.6811097256857854</v>
+        <v>1.052013422818792</v>
       </c>
       <c r="N35">
-        <v>0.6795511221945136</v>
+        <v>1.042506720430108</v>
       </c>
       <c r="O35">
-        <v>0.001558603491271793</v>
+        <v>0.009506702388683896</v>
       </c>
       <c r="P35">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="Q35">
-        <v>0.52</v>
+        <v>0.77</v>
       </c>
       <c r="R35">
-        <v>-0.01000000000000001</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U35" t="b">
@@ -2949,70 +2949,70 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LTR1488_2022</t>
+          <t>LTR1449_2015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTR1488</t>
+          <t>LTR1449</t>
         </is>
       </c>
       <c r="C36">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="D36">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E36">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.5800000000000001</v>
+        <v>0.7698412698412698</v>
       </c>
       <c r="H36">
-        <v>0.576923076923077</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="I36">
-        <v>0.003076923076923088</v>
+        <v>-0.03015873015873016</v>
       </c>
       <c r="J36">
-        <v>0.1333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K36">
-        <v>0.1333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L36">
-        <v>2.775557561562891E-17</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>0.625</v>
+        <v>0.6937919463087248</v>
       </c>
       <c r="N36">
-        <v>0.5909653465346534</v>
+        <v>0.6937919463087248</v>
       </c>
       <c r="O36">
-        <v>0.03403465346534662</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="R36">
-        <v>0.01000000000000001</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U36" t="b">
@@ -3022,34 +3022,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LTR1492_2016</t>
+          <t>LTR1488_2019</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTR1492</t>
+          <t>LTR1488</t>
         </is>
       </c>
       <c r="C37">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D37">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E37">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H37">
-        <v>0.6111111111111112</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="I37">
-        <v>-0.01111111111111118</v>
+        <v>-0.03703703703703709</v>
       </c>
       <c r="J37">
         <v>0.2</v>
@@ -3061,22 +3061,22 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.6772113022113021</v>
+        <v>0.6811097256857854</v>
       </c>
       <c r="N37">
-        <v>0.6342137592137592</v>
+        <v>0.6795511221945136</v>
       </c>
       <c r="O37">
-        <v>0.04299754299754288</v>
+        <v>0.001558603491271793</v>
       </c>
       <c r="P37">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="Q37">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="R37">
-        <v>0.01000000000000001</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3095,34 +3095,34 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTR1501_2016</t>
+          <t>LTR1488_2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTR1501</t>
+          <t>LTR1488</t>
         </is>
       </c>
       <c r="C38">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D38">
         <v>0.3333333333333333</v>
       </c>
       <c r="E38">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F38">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0.753968253968254</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="H38">
-        <v>0.753968253968254</v>
+        <v>0.5864197530864197</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>-0.006419753086419622</v>
       </c>
       <c r="J38">
         <v>0.1333333333333333</v>
@@ -3134,19 +3134,19 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M38">
-        <v>0.6205568720379147</v>
+        <v>0.625</v>
       </c>
       <c r="N38">
-        <v>0.4102488151658767</v>
+        <v>0.5909653465346534</v>
       </c>
       <c r="O38">
-        <v>0.210308056872038</v>
+        <v>0.03403465346534662</v>
       </c>
       <c r="P38">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="Q38">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="R38">
         <v>0.01000000000000001</v>
@@ -3168,58 +3168,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LTR1687_2017</t>
+          <t>LTR1492_2016</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTR1687</t>
+          <t>LTR1492</t>
         </is>
       </c>
       <c r="C39">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D39">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E39">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.576923076923077</v>
+        <v>0.6</v>
       </c>
       <c r="H39">
-        <v>0.576923076923077</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>-0.01111111111111118</v>
       </c>
       <c r="J39">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K39">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0.6631679389312978</v>
+        <v>0.6772113022113021</v>
       </c>
       <c r="N39">
-        <v>0.625</v>
+        <v>0.6342137592137592</v>
       </c>
       <c r="O39">
-        <v>0.03816793893129777</v>
+        <v>0.04299754299754288</v>
       </c>
       <c r="P39">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="Q39">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="R39">
         <v>0.01000000000000001</v>
@@ -3241,31 +3241,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LTR297_2015</t>
+          <t>LTR1501_2016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTR297</t>
+          <t>LTR1501</t>
         </is>
       </c>
       <c r="C40">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D40">
         <v>0.3333333333333333</v>
       </c>
       <c r="E40">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G40">
-        <v>0.4166666666666667</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="H40">
-        <v>0.4166666666666667</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3280,31 +3280,31 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M40">
-        <v>0.5686475409836065</v>
+        <v>0.6205568720379147</v>
       </c>
       <c r="N40">
-        <v>0.5122950819672131</v>
+        <v>0.4102488151658767</v>
       </c>
       <c r="O40">
-        <v>0.05635245901639341</v>
+        <v>0.210308056872038</v>
       </c>
       <c r="P40">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="Q40">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="R40">
         <v>0.01000000000000001</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U40" t="b">
@@ -3314,70 +3314,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LTR337_2016</t>
+          <t>LTR1687_2017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTR337</t>
+          <t>LTR1687</t>
         </is>
       </c>
       <c r="C41">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D41">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="E41">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.7388888888888889</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="H41">
-        <v>0.7388888888888889</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K41">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0.7444707740916271</v>
+        <v>0.6631679389312978</v>
       </c>
       <c r="N41">
-        <v>0.7192930489731437</v>
+        <v>0.625</v>
       </c>
       <c r="O41">
-        <v>0.02517772511848337</v>
+        <v>0.03816793893129777</v>
       </c>
       <c r="P41">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="Q41">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="R41">
         <v>0.01000000000000001</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U41" t="b">
@@ -3387,70 +3387,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LTR337_2022</t>
+          <t>LTR297_2015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTR337</t>
+          <t>LTR297</t>
         </is>
       </c>
       <c r="C42">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="D42">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E42">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F42">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>0.7222222222222222</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H42">
-        <v>0.7156862745098039</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="I42">
-        <v>0.006535947712418277</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0.8</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K42">
-        <v>0.8</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>2.775557561562891E-17</v>
       </c>
       <c r="M42">
-        <v>0.759308510638298</v>
+        <v>0.5686475409836065</v>
       </c>
       <c r="N42">
-        <v>0.6490384615384616</v>
+        <v>0.5122950819672131</v>
       </c>
       <c r="O42">
-        <v>0.1102700490998364</v>
+        <v>0.05635245901639341</v>
       </c>
       <c r="P42">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="Q42">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="R42">
-        <v>-0.01000000000000001</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="U42" t="b">
@@ -3460,70 +3460,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LTR351_2019</t>
+          <t>LTR337_2016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTR351</t>
+          <t>LTR337</t>
         </is>
       </c>
       <c r="C43">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D43">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E43">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.7045454545454546</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="H43">
-        <v>0.7045454545454547</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="I43">
-        <v>-1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>0.2666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="K43">
-        <v>0.2666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="L43">
-        <v>-5.551115123125783E-17</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>0.6763059701492536</v>
+        <v>0.7444707740916271</v>
       </c>
       <c r="N43">
-        <v>0.6669776119402985</v>
+        <v>0.7192930489731437</v>
       </c>
       <c r="O43">
-        <v>0.009328358208955168</v>
+        <v>0.02517772511848337</v>
       </c>
       <c r="P43">
-        <v>0.54</v>
+        <v>0.78</v>
       </c>
       <c r="Q43">
-        <v>0.53</v>
+        <v>0.77</v>
       </c>
       <c r="R43">
         <v>0.01000000000000001</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U43" t="b">
@@ -3533,12 +3533,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LTR411_2022</t>
+          <t>LTR337_2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTR411</t>
+          <t>LTR337</t>
         </is>
       </c>
       <c r="C44">
@@ -3548,46 +3548,46 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="E44">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G44">
-        <v>0.8076923076923076</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H44">
-        <v>0.8266666666666667</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="I44">
-        <v>-0.01897435897435906</v>
+        <v>0.006535947712418277</v>
       </c>
       <c r="J44">
-        <v>0.7333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="K44">
-        <v>0.7333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0.7774122807017543</v>
+        <v>0.759308510638298</v>
       </c>
       <c r="N44">
-        <v>0.7214912280701754</v>
+        <v>0.6490384615384616</v>
       </c>
       <c r="O44">
-        <v>0.05592105263157887</v>
+        <v>0.1102700490998364</v>
       </c>
       <c r="P44">
+        <v>0.74</v>
+      </c>
+      <c r="Q44">
         <v>0.75</v>
       </c>
-      <c r="Q44">
-        <v>0.74</v>
-      </c>
       <c r="R44">
-        <v>0.01000000000000001</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -3606,61 +3606,61 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LTR86_2016</t>
+          <t>LTR351_2019</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTR86</t>
+          <t>LTR351</t>
         </is>
       </c>
       <c r="C45">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D45">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
         <v>0.5</v>
       </c>
       <c r="F45">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>0.6666666666666666</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="H45">
-        <v>0.6666666666666666</v>
+        <v>0.7045454545454547</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>-1.110223024625157E-16</v>
       </c>
       <c r="J45">
-        <v>0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K45">
-        <v>0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L45">
-        <v>2.775557561562891E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M45">
-        <v>0.7788944723618091</v>
+        <v>0.6763059701492536</v>
       </c>
       <c r="N45">
-        <v>0.6752512562814069</v>
+        <v>0.6669776119402985</v>
       </c>
       <c r="O45">
-        <v>0.1036432160804022</v>
+        <v>0.009328358208955168</v>
       </c>
       <c r="P45">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="Q45">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="R45">
-        <v>-0.01000000000000001</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LTR1502_2019</t>
+          <t>LTR411_2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LTR1502</t>
+          <t>LTR411</t>
         </is>
       </c>
       <c r="C46">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D46">
         <v>0.6666666666666666</v>
@@ -3700,49 +3700,49 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0.6666666666666666</v>
+        <v>0.8076923076923076</v>
       </c>
       <c r="H46">
-        <v>0.6666666666666666</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>-0.03846153846153855</v>
       </c>
       <c r="J46">
-        <v>0.2666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K46">
-        <v>0.2666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L46">
-        <v>-5.551115123125783E-17</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>0.6867283950617283</v>
+        <v>0.7774122807017543</v>
       </c>
       <c r="N46">
-        <v>0.6327160493827161</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="O46">
-        <v>0.05401234567901225</v>
+        <v>0.05592105263157887</v>
       </c>
       <c r="P46">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="Q46">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="R46">
-        <v>0.009999999999999898</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U46" t="b">
@@ -3752,12 +3752,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LTR337_2019</t>
+          <t>LTR1502_2019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LTR337</t>
+          <t>LTR1502</t>
         </is>
       </c>
       <c r="C47">
@@ -3773,10 +3773,10 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.6590909090909091</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H47">
-        <v>0.6590909090909091</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3791,13 +3791,13 @@
         <v>-5.551115123125783E-17</v>
       </c>
       <c r="M47">
-        <v>0.6812339331619538</v>
+        <v>0.6867283950617283</v>
       </c>
       <c r="N47">
-        <v>0.6411082474226804</v>
+        <v>0.6327160493827161</v>
       </c>
       <c r="O47">
-        <v>0.04012568573927344</v>
+        <v>0.05401234567901225</v>
       </c>
       <c r="P47">
         <v>0.57</v>
@@ -3825,70 +3825,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LTR1063_2017</t>
+          <t>LTR337_2019</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LTR1063</t>
+          <t>LTR337</t>
         </is>
       </c>
       <c r="C48">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D48">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E48">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.4166666666666667</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H48">
-        <v>0.4166666666666667</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0.06666666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K48">
-        <v>0.06666666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M48">
-        <v>0.6305661577608143</v>
+        <v>0.6812339331619538</v>
       </c>
       <c r="N48">
-        <v>0.6242048346055979</v>
+        <v>0.6411082474226804</v>
       </c>
       <c r="O48">
-        <v>0.006361323155216314</v>
+        <v>0.04012568573927344</v>
       </c>
       <c r="P48">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="Q48">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>0.009999999999999898</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U48" t="b">
@@ -3898,70 +3898,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LTR1299_2015</t>
+          <t>LTR1063_2017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LTR1299</t>
+          <t>LTR1063</t>
         </is>
       </c>
       <c r="C49">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.9782608695652174</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H49">
-        <v>0.9855072463768115</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="I49">
-        <v>-0.007246376811594124</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>0.9333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K49">
-        <v>0.9333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0.79053480475382</v>
+        <v>0.6305661577608143</v>
       </c>
       <c r="N49">
-        <v>0.79053480475382</v>
+        <v>0.6242048346055979</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>0.006361323155216314</v>
       </c>
       <c r="P49">
-        <v>0.93</v>
+        <v>0.36</v>
       </c>
       <c r="Q49">
-        <v>0.93</v>
+        <v>0.36</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="U49" t="b">
@@ -3971,7 +3971,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LTR1299_2019</t>
+          <t>LTR1299_2015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3980,49 +3980,49 @@
         </is>
       </c>
       <c r="C50">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D50">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.9242424242424243</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H50">
-        <v>0.9318181818181818</v>
+        <v>1.007246376811594</v>
       </c>
       <c r="I50">
-        <v>-0.007575757575757458</v>
+        <v>-0.02898550724637661</v>
       </c>
       <c r="J50">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K50">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>0.7226138828633406</v>
+        <v>0.79053480475382</v>
       </c>
       <c r="N50">
-        <v>0.7226138828633405</v>
+        <v>0.79053480475382</v>
       </c>
       <c r="O50">
-        <v>1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="Q50">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -4044,7 +4044,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LTR1299_2022</t>
+          <t>LTR1299_2019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4053,49 +4053,49 @@
         </is>
       </c>
       <c r="C51">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.9074074074074074</v>
+        <v>0.9242424242424243</v>
       </c>
       <c r="H51">
-        <v>0.9120370370370371</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="I51">
-        <v>-0.00462962962962965</v>
+        <v>-0.007575757575757458</v>
       </c>
       <c r="J51">
-        <v>1.266666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="K51">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L51">
-        <v>0.06666666666666665</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>0.9577287946428572</v>
+        <v>0.7226138828633406</v>
       </c>
       <c r="N51">
-        <v>0.9556361607142857</v>
+        <v>0.7226138828633405</v>
       </c>
       <c r="O51">
-        <v>0.002092633928571508</v>
+        <v>1.110223024625157E-16</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -4117,16 +4117,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LTR1320_2016</t>
+          <t>LTR1299_2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LTR1320</t>
+          <t>LTR1299</t>
         </is>
       </c>
       <c r="C52">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -4138,31 +4138,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0.9464285714285715</v>
+        <v>0.9074074074074074</v>
       </c>
       <c r="H52">
-        <v>0.9464285714285715</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>-0.01851851851851849</v>
       </c>
       <c r="J52">
-        <v>1.533333333333333</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="K52">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L52">
-        <v>0.1333333333333335</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="M52">
-        <v>0.8657495256166983</v>
+        <v>0.9577287946428572</v>
       </c>
       <c r="N52">
-        <v>0.8657495256166983</v>
+        <v>0.9556361607142857</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>0.002092633928571508</v>
       </c>
       <c r="P52">
         <v>1</v>
@@ -4190,7 +4190,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LTR1320_2019</t>
+          <t>LTR1320_2016</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4199,61 +4199,61 @@
         </is>
       </c>
       <c r="C53">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D53">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0.8571428571428572</v>
+        <v>0.9464285714285715</v>
       </c>
       <c r="H53">
-        <v>0.8571428571428572</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>-0.01785714285714279</v>
       </c>
       <c r="J53">
-        <v>0.6666666666666666</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="K53">
-        <v>0.6666666666666666</v>
+        <v>1.4</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>0.1333333333333335</v>
       </c>
       <c r="M53">
-        <v>0.6916199158485272</v>
+        <v>0.8657495256166983</v>
       </c>
       <c r="N53">
-        <v>0.6916199158485273</v>
+        <v>0.8657495256166983</v>
       </c>
       <c r="O53">
-        <v>-1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="Q53">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="R53">
         <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U53" t="b">
@@ -4263,7 +4263,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LTR1320_2022</t>
+          <t>LTR1320_2019</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4272,61 +4272,61 @@
         </is>
       </c>
       <c r="C54">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0.9482758620689654</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="H54">
-        <v>0.9482758620689654</v>
+        <v>0.8560606060606061</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>0.001082251082251129</v>
       </c>
       <c r="J54">
-        <v>1.066666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K54">
-        <v>1.066666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L54">
-        <v>-4.440892098500626E-16</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>0.9419642857142857</v>
+        <v>0.6916199158485272</v>
       </c>
       <c r="N54">
-        <v>0.9433285509325681</v>
+        <v>0.6916199158485273</v>
       </c>
       <c r="O54">
-        <v>-0.001364265218282368</v>
+        <v>-1.110223024625157E-16</v>
       </c>
       <c r="P54">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="Q54">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="R54">
         <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U54" t="b">
@@ -4336,16 +4336,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LTR1379_2015</t>
+          <t>LTR1320_2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTR1379</t>
+          <t>LTR1320</t>
         </is>
       </c>
       <c r="C55">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -4357,37 +4357,37 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.9545454545454546</v>
+        <v>0.9482758620689654</v>
       </c>
       <c r="H55">
-        <v>0.9545454545454547</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="I55">
-        <v>-1.110223024625157E-16</v>
+        <v>-0.01724137931034497</v>
       </c>
       <c r="J55">
-        <v>0.9333333333333333</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="K55">
-        <v>0.9333333333333333</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>-4.440892098500626E-16</v>
       </c>
       <c r="M55">
-        <v>0.782323883161512</v>
+        <v>0.9419642857142857</v>
       </c>
       <c r="N55">
-        <v>0.781786941580756</v>
+        <v>0.9433285509325681</v>
       </c>
       <c r="O55">
-        <v>0.0005369415807560118</v>
+        <v>-0.001364265218282368</v>
       </c>
       <c r="P55">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="Q55">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -4409,7 +4409,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LTR1379_2019</t>
+          <t>LTR1379_2015</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4418,61 +4418,61 @@
         </is>
       </c>
       <c r="C56">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D56">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.8623188405797101</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="H56">
-        <v>0.8623188405797101</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>-0.01515151515151514</v>
       </c>
       <c r="J56">
-        <v>0.6</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K56">
-        <v>0.6</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0.7549055232558139</v>
+        <v>0.782323883161512</v>
       </c>
       <c r="N56">
-        <v>0.7549055232558139</v>
+        <v>0.781786941580756</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>0.0005369415807560118</v>
       </c>
       <c r="P56">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="Q56">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="R56">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U56" t="b">
@@ -4482,7 +4482,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LTR1379_2022</t>
+          <t>LTR1379_2019</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4491,49 +4491,49 @@
         </is>
       </c>
       <c r="C57">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D57">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E57">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0.8064516129032259</v>
+        <v>0.8623188405797101</v>
       </c>
       <c r="H57">
-        <v>0.8064516129032259</v>
+        <v>0.8623188405797101</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>0.8666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="K57">
-        <v>0.8666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57">
-        <v>0.6558675699300699</v>
+        <v>0.7549055232558139</v>
       </c>
       <c r="N57">
-        <v>0.6456043956043956</v>
+        <v>0.7549055232558139</v>
       </c>
       <c r="O57">
-        <v>0.01026317432567425</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="Q57">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -4555,16 +4555,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LTR1385_2016</t>
+          <t>LTR1379_2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTR1385</t>
+          <t>LTR1379</t>
         </is>
       </c>
       <c r="C58">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D58">
         <v>0.8333333333333334</v>
@@ -4576,49 +4576,49 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0.9722222222222222</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="H58">
-        <v>0.9722222222222222</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
       <c r="J58">
-        <v>0.6</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K58">
-        <v>0.6</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58">
-        <v>0.8421814671814671</v>
+        <v>0.6558675699300699</v>
       </c>
       <c r="N58">
-        <v>0.8421814671814671</v>
+        <v>0.6456043956043956</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>0.01026317432567425</v>
       </c>
       <c r="P58">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="Q58">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="R58">
         <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U58" t="b">
@@ -4628,7 +4628,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LTR1385_2019</t>
+          <t>LTR1385_2016</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4637,61 +4637,61 @@
         </is>
       </c>
       <c r="C59">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D59">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E59">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0.6833333333333332</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="H59">
-        <v>0.6833333333333332</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K59">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59">
-        <v>0.7584212662337662</v>
+        <v>0.8421814671814671</v>
       </c>
       <c r="N59">
-        <v>0.7584212662337662</v>
+        <v>0.8421814671814671</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q59">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R59">
         <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="U59" t="b">
@@ -4701,7 +4701,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LTR1385_2022</t>
+          <t>LTR1385_2019</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D60">
         <v>0.6666666666666666</v>
@@ -4722,37 +4722,37 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.8174603174603176</v>
+        <v>0.6833333333333332</v>
       </c>
       <c r="H60">
-        <v>0.8174603174603176</v>
+        <v>0.6833333333333332</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K60">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0.9122670807453416</v>
+        <v>0.7584212662337662</v>
       </c>
       <c r="N60">
-        <v>0.9130094043887146</v>
+        <v>0.7584212662337662</v>
       </c>
       <c r="O60">
-        <v>-0.0007423236433730107</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="Q60">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -4774,70 +4774,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LTR1447_2019</t>
+          <t>LTR1385_2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTR1447</t>
+          <t>LTR1385</t>
         </is>
       </c>
       <c r="C61">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D61">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E61">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.7361111111111112</v>
+        <v>0.8174603174603176</v>
       </c>
       <c r="H61">
-        <v>0.7361111111111112</v>
+        <v>0.8174603174603176</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0.2666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="K61">
-        <v>0.2666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L61">
-        <v>-5.551115123125783E-17</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>0.7019519519519519</v>
+        <v>0.9122670807453416</v>
       </c>
       <c r="N61">
-        <v>0.7019519519519519</v>
+        <v>0.9130094043887146</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>-0.0007423236433730107</v>
       </c>
       <c r="P61">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="Q61">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="R61">
         <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="U61" t="b">
@@ -4847,70 +4847,70 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LTR1449_2015</t>
+          <t>LTR1447_2019</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTR1449</t>
+          <t>LTR1447</t>
         </is>
       </c>
       <c r="C62">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D62">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="E62">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>0.7698412698412698</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="H62">
-        <v>0.775</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="I62">
-        <v>-0.005158730158730251</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>0.4666666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K62">
-        <v>0.4666666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M62">
-        <v>0.6937919463087248</v>
+        <v>0.7019519519519519</v>
       </c>
       <c r="N62">
-        <v>0.6937919463087248</v>
+        <v>0.7019519519519519</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="Q62">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="R62">
         <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="U62" t="b">
@@ -4944,10 +4944,10 @@
         <v>0.8409090909090909</v>
       </c>
       <c r="H63">
-        <v>0.8484848484848485</v>
+        <v>0.8478260869565218</v>
       </c>
       <c r="I63">
-        <v>-0.007575757575757569</v>
+        <v>-0.006916996047430901</v>
       </c>
       <c r="J63">
         <v>0.3333333333333333</v>
@@ -5236,10 +5236,10 @@
         <v>0.7901234567901234</v>
       </c>
       <c r="H67">
-        <v>0.7901234567901233</v>
+        <v>0.808641975308642</v>
       </c>
       <c r="I67">
-        <v>1.110223024625157E-16</v>
+        <v>-0.0185185185185186</v>
       </c>
       <c r="J67">
         <v>0.4666666666666667</v>
@@ -5382,10 +5382,10 @@
         <v>0.9019607843137255</v>
       </c>
       <c r="H69">
-        <v>0.9019607843137255</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>-0.01470588235294112</v>
       </c>
       <c r="J69">
         <v>0.6666666666666666</v>
@@ -5674,10 +5674,10 @@
         <v>0.7011494252873564</v>
       </c>
       <c r="H73">
-        <v>0.7011494252873564</v>
+        <v>0.7055555555555556</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>-0.004406130268199249</v>
       </c>
       <c r="J73">
         <v>0.4</v>
@@ -5820,10 +5820,10 @@
         <v>0.7701149425287356</v>
       </c>
       <c r="H75">
-        <v>0.7758620689655172</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I75">
-        <v>-0.005747126436781658</v>
+        <v>-0.00766283524904221</v>
       </c>
       <c r="J75">
         <v>0.2</v>
@@ -5893,10 +5893,10 @@
         <v>0.8253968253968255</v>
       </c>
       <c r="H76">
-        <v>0.8253968253968256</v>
+        <v>0.8257575757575757</v>
       </c>
       <c r="I76">
-        <v>-1.110223024625157E-16</v>
+        <v>-0.0003607503607502283</v>
       </c>
       <c r="J76">
         <v>0.6666666666666666</v>
@@ -6540,22 +6540,22 @@
         <v>82</v>
       </c>
       <c r="C3">
-        <v>0.001072238521249652</v>
+        <v>-0.003034997622772077</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005026380955348395</v>
+        <v>0.008000955722806301</v>
       </c>
       <c r="F3">
-        <v>0.9964892565883873</v>
+        <v>0.9948954977090645</v>
       </c>
       <c r="G3">
-        <v>5.986467335472058E-88</v>
+        <v>1.845644815360817E-81</v>
       </c>
       <c r="H3">
-        <v>68.29268292682927</v>
+        <v>58.53658536585365</v>
       </c>
     </row>
     <row r="4">
@@ -6624,22 +6624,22 @@
         <v>82</v>
       </c>
       <c r="C6">
-        <v>0.01463414634146341</v>
+        <v>0.01402439024390243</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.01780487804878049</v>
+        <v>0.01768292682926829</v>
       </c>
       <c r="F6">
-        <v>0.9908736580695875</v>
+        <v>0.9911315006021287</v>
       </c>
       <c r="G6">
-        <v>2.120992596125486E-71</v>
+        <v>6.773526914327024E-72</v>
       </c>
       <c r="H6">
-        <v>43.90243902439025</v>
+        <v>42.68292682926829</v>
       </c>
     </row>
   </sheetData>
@@ -6799,7 +6799,7 @@
         <v>82</v>
       </c>
       <c r="D5">
-        <v>0.699</v>
+        <v>0.703</v>
       </c>
       <c r="E5">
         <v>0.171</v>
@@ -6811,7 +6811,7 @@
         <v>0.25</v>
       </c>
       <c r="H5">
-        <v>0.986</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="6">
@@ -6982,7 +6982,7 @@
         <v>0.591</v>
       </c>
       <c r="E11">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="F11">
         <v>0.59</v>
@@ -7076,19 +7076,19 @@
         <v>82</v>
       </c>
       <c r="C3">
-        <v>0.0011</v>
+        <v>-0.003</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="F3">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="G3">
-        <v>68.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="4">
@@ -7151,19 +7151,19 @@
         <v>82</v>
       </c>
       <c r="C6">
-        <v>0.0146</v>
+        <v>0.014</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.0178</v>
+        <v>0.0177</v>
       </c>
       <c r="F6">
         <v>0.991</v>
       </c>
       <c r="G6">
-        <v>43.9</v>
+        <v>42.7</v>
       </c>
     </row>
   </sheetData>

--- a/Outputs/10_lepa_per_metric_comparison.xlsx
+++ b/Outputs/10_lepa_per_metric_comparison.xlsx
@@ -1,23 +1,550 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_15673CAE8F55B9F673CF72A2687C167482D12F60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="per_site" sheetId="1" r:id="rId1"/>
     <sheet name="summary" sheetId="2" r:id="rId2"/>
-    <sheet name="publication_distribution" sheetId="3" r:id="rId3"/>
-    <sheet name="publication_residuals" sheetId="4" r:id="rId4"/>
+    <sheet name="paired_tests" sheetId="3" r:id="rId3"/>
+    <sheet name="publication_distribution" sheetId="4" r:id="rId4"/>
+    <sheet name="publication_residuals" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="168">
+  <si>
+    <t>site_code</t>
+  </si>
+  <si>
+    <t>site_id</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>lepa_DSFI</t>
+  </si>
+  <si>
+    <t>our_DSFI</t>
+  </si>
+  <si>
+    <t>res_DSFI</t>
+  </si>
+  <si>
+    <t>lepa_ASPT</t>
+  </si>
+  <si>
+    <t>our_ASPT</t>
+  </si>
+  <si>
+    <t>res_ASPT</t>
+  </si>
+  <si>
+    <t>lepa_DEP</t>
+  </si>
+  <si>
+    <t>our_DEP</t>
+  </si>
+  <si>
+    <t>res_DEP</t>
+  </si>
+  <si>
+    <t>lepa_EHPCrHi</t>
+  </si>
+  <si>
+    <t>our_EHPCrHi</t>
+  </si>
+  <si>
+    <t>res_EHPCrHi</t>
+  </si>
+  <si>
+    <t>lepa_LRMI</t>
+  </si>
+  <si>
+    <t>our_LRMI</t>
+  </si>
+  <si>
+    <t>res_LRMI</t>
+  </si>
+  <si>
+    <t>lepa_class</t>
+  </si>
+  <si>
+    <t>our_class</t>
+  </si>
+  <si>
+    <t>class_match</t>
+  </si>
+  <si>
+    <t>LTR1492_2022</t>
+  </si>
+  <si>
+    <t>LTR1492</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>LTR163_2019</t>
+  </si>
+  <si>
+    <t>LTR163</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>LTR386_2019</t>
+  </si>
+  <si>
+    <t>LTR386</t>
+  </si>
+  <si>
+    <t>LTR163_2022</t>
+  </si>
+  <si>
+    <t>LTR127_2015</t>
+  </si>
+  <si>
+    <t>LTR127</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>LTR127_2020</t>
+  </si>
+  <si>
+    <t>LTR450_2015</t>
+  </si>
+  <si>
+    <t>LTR450</t>
+  </si>
+  <si>
+    <t>LTR1466_2019</t>
+  </si>
+  <si>
+    <t>LTR1466</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>LTR127_2017</t>
+  </si>
+  <si>
+    <t>LTR625_2022</t>
+  </si>
+  <si>
+    <t>LTR625</t>
+  </si>
+  <si>
+    <t>LTR297_2021</t>
+  </si>
+  <si>
+    <t>LTR297</t>
+  </si>
+  <si>
+    <t>LTR86_2015</t>
+  </si>
+  <si>
+    <t>LTR86</t>
+  </si>
+  <si>
+    <t>LTR1447_2015</t>
+  </si>
+  <si>
+    <t>LTR1447</t>
+  </si>
+  <si>
+    <t>LTR1466_2016</t>
+  </si>
+  <si>
+    <t>LTR1687_2016</t>
+  </si>
+  <si>
+    <t>LTR1687</t>
+  </si>
+  <si>
+    <t>LTR1687_2022</t>
+  </si>
+  <si>
+    <t>LTR1461_2016</t>
+  </si>
+  <si>
+    <t>LTR1461</t>
+  </si>
+  <si>
+    <t>LTR1461_2019</t>
+  </si>
+  <si>
+    <t>LTR1461_2022</t>
+  </si>
+  <si>
+    <t>LTR1466_2022</t>
+  </si>
+  <si>
+    <t>LTR1488_2015</t>
+  </si>
+  <si>
+    <t>LTR1488</t>
+  </si>
+  <si>
+    <t>LTR386_2016</t>
+  </si>
+  <si>
+    <t>LTR386_2022</t>
+  </si>
+  <si>
+    <t>LTR1488_2016</t>
+  </si>
+  <si>
+    <t>LTR1492_2019</t>
+  </si>
+  <si>
+    <t>LTR1502_2015</t>
+  </si>
+  <si>
+    <t>LTR1502</t>
+  </si>
+  <si>
+    <t>LTR163_2016</t>
+  </si>
+  <si>
+    <t>LTR297_2018</t>
+  </si>
+  <si>
+    <t>LTR450_2020</t>
+  </si>
+  <si>
+    <t>LTR706_2015</t>
+  </si>
+  <si>
+    <t>LTR706</t>
+  </si>
+  <si>
+    <t>LTR86_2016</t>
+  </si>
+  <si>
+    <t>LTR1063_2021</t>
+  </si>
+  <si>
+    <t>LTR1063</t>
+  </si>
+  <si>
+    <t>LTR308_2018</t>
+  </si>
+  <si>
+    <t>LTR308</t>
+  </si>
+  <si>
+    <t>LTR1447_2022</t>
+  </si>
+  <si>
+    <t>LTR1449_2015</t>
+  </si>
+  <si>
+    <t>LTR1449</t>
+  </si>
+  <si>
+    <t>LTR1488_2019</t>
+  </si>
+  <si>
+    <t>LTR1488_2022</t>
+  </si>
+  <si>
+    <t>LTR1492_2016</t>
+  </si>
+  <si>
+    <t>LTR1501_2016</t>
+  </si>
+  <si>
+    <t>LTR1501</t>
+  </si>
+  <si>
+    <t>LTR1687_2017</t>
+  </si>
+  <si>
+    <t>LTR297_2015</t>
+  </si>
+  <si>
+    <t>LTR337_2016</t>
+  </si>
+  <si>
+    <t>LTR337</t>
+  </si>
+  <si>
+    <t>LTR337_2022</t>
+  </si>
+  <si>
+    <t>LTR351_2019</t>
+  </si>
+  <si>
+    <t>LTR351</t>
+  </si>
+  <si>
+    <t>LTR411_2022</t>
+  </si>
+  <si>
+    <t>LTR411</t>
+  </si>
+  <si>
+    <t>LTR1502_2019</t>
+  </si>
+  <si>
+    <t>LTR337_2019</t>
+  </si>
+  <si>
+    <t>LTR1063_2017</t>
+  </si>
+  <si>
+    <t>LTR1299_2015</t>
+  </si>
+  <si>
+    <t>LTR1299</t>
+  </si>
+  <si>
+    <t>LTR1299_2019</t>
+  </si>
+  <si>
+    <t>LTR1299_2022</t>
+  </si>
+  <si>
+    <t>LTR1320_2016</t>
+  </si>
+  <si>
+    <t>LTR1320</t>
+  </si>
+  <si>
+    <t>LTR1320_2019</t>
+  </si>
+  <si>
+    <t>LTR1320_2022</t>
+  </si>
+  <si>
+    <t>LTR1379_2015</t>
+  </si>
+  <si>
+    <t>LTR1379</t>
+  </si>
+  <si>
+    <t>LTR1379_2019</t>
+  </si>
+  <si>
+    <t>LTR1379_2022</t>
+  </si>
+  <si>
+    <t>LTR1385_2016</t>
+  </si>
+  <si>
+    <t>LTR1385</t>
+  </si>
+  <si>
+    <t>LTR1385_2019</t>
+  </si>
+  <si>
+    <t>LTR1385_2022</t>
+  </si>
+  <si>
+    <t>LTR1447_2019</t>
+  </si>
+  <si>
+    <t>LTR1449_2019</t>
+  </si>
+  <si>
+    <t>LTR1449_2022</t>
+  </si>
+  <si>
+    <t>LTR1501_2019</t>
+  </si>
+  <si>
+    <t>LTR1501_2022</t>
+  </si>
+  <si>
+    <t>LTR1502_2022</t>
+  </si>
+  <si>
+    <t>LTR1601_2021</t>
+  </si>
+  <si>
+    <t>LTR1601</t>
+  </si>
+  <si>
+    <t>LTR232_2015</t>
+  </si>
+  <si>
+    <t>LTR232</t>
+  </si>
+  <si>
+    <t>LTR232_2019</t>
+  </si>
+  <si>
+    <t>LTR232_2022</t>
+  </si>
+  <si>
+    <t>LTR308_2021</t>
+  </si>
+  <si>
+    <t>LTR351_2015</t>
+  </si>
+  <si>
+    <t>LTR351_2022</t>
+  </si>
+  <si>
+    <t>LTR411_2015</t>
+  </si>
+  <si>
+    <t>LTR411_2019</t>
+  </si>
+  <si>
+    <t>LTR625_2015</t>
+  </si>
+  <si>
+    <t>LTR625_2019</t>
+  </si>
+  <si>
+    <t>LTR627_2015</t>
+  </si>
+  <si>
+    <t>LTR627</t>
+  </si>
+  <si>
+    <t>LTR706_2018</t>
+  </si>
+  <si>
+    <t>LTR706_2021</t>
+  </si>
+  <si>
+    <t>LTR86_2017</t>
+  </si>
+  <si>
+    <t>LTR86_2020</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>mean_residual</t>
+  </si>
+  <si>
+    <t>median_residual</t>
+  </si>
+  <si>
+    <t>mean_abs_res</t>
+  </si>
+  <si>
+    <t>pearson_r</t>
+  </si>
+  <si>
+    <t>pearson_p</t>
+  </si>
+  <si>
+    <t>pct_exact</t>
+  </si>
+  <si>
+    <t>DSFI</t>
+  </si>
+  <si>
+    <t>ASPT</t>
+  </si>
+  <si>
+    <t>#DEP</t>
+  </si>
+  <si>
+    <t>%EHP–%CrHi</t>
+  </si>
+  <si>
+    <t>EQR</t>
+  </si>
+  <si>
+    <t>median_diff</t>
+  </si>
+  <si>
+    <t>W_stat</t>
+  </si>
+  <si>
+    <t>W_p</t>
+  </si>
+  <si>
+    <t>LRMI</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>LEPA</t>
+  </si>
+  <si>
+    <t>OTL</t>
+  </si>
+  <si>
+    <t>LEPA − LT-OTL (mean)</t>
+  </si>
+  <si>
+    <t>LEPA − LT-OTL (median)</t>
+  </si>
+  <si>
+    <t>Mean |residual|</t>
+  </si>
+  <si>
+    <t>Pearson r</t>
+  </si>
+  <si>
+    <t>% within ±0.005</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -62,17 +589,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -110,7 +645,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -144,6 +679,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -178,9 +714,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -353,127 +890,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>site_code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>site_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_DSFI</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>our_DSFI</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>res_DSFI</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_ASPT</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>our_ASPT</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>res_ASPT</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_DEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>our_DEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>res_DEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_EHPCrHi</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>our_EHPCrHi</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>res_EHPCrHi</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_LRMI</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>our_LRMI</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>res_LRMI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>lepa_class</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>our_class</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>class_match</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LTR1492_2022</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+    <row r="1" spans="1:21" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2">
         <v>2022</v>
@@ -488,13 +979,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="H2">
-        <v>0.7291666666666666</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="I2">
-        <v>-0.00694444444444442</v>
+        <v>-6.9444444444444198E-3</v>
       </c>
       <c r="J2">
         <v>0.1333333333333333</v>
@@ -506,13 +997,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M2">
-        <v>0.634014423076923</v>
+        <v>0.63401442307692302</v>
       </c>
       <c r="N2">
-        <v>0.2103365384615385</v>
+        <v>0.21033653846153849</v>
       </c>
       <c r="O2">
-        <v>0.4236778846153845</v>
+        <v>0.42367788461538453</v>
       </c>
       <c r="P2">
         <v>0.5</v>
@@ -523,51 +1014,43 @@
       <c r="R2">
         <v>0.11</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>24</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LTR163_2019</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
       </c>
       <c r="C3">
         <v>2019</v>
       </c>
       <c r="D3">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E3">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="H3">
-        <v>0.7820512820512823</v>
+        <v>0.78205128205128227</v>
       </c>
       <c r="I3">
-        <v>-0.00427350427350448</v>
+        <v>-4.2735042735044804E-3</v>
       </c>
       <c r="J3">
         <v>0.4</v>
@@ -579,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.6988396624472573</v>
+        <v>0.69883966244725726</v>
       </c>
       <c r="N3">
-        <v>0.3889767932489451</v>
+        <v>0.38897679324894507</v>
       </c>
       <c r="O3">
-        <v>0.3098628691983122</v>
+        <v>0.30986286919831219</v>
       </c>
       <c r="P3">
         <v>0.68</v>
@@ -594,32 +1077,24 @@
         <v>0.6</v>
       </c>
       <c r="R3">
-        <v>0.08000000000000007</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" t="s">
+        <v>27</v>
       </c>
       <c r="U3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LTR386_2019</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
       </c>
       <c r="C4">
         <v>2019</v>
@@ -634,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.746031746031746</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="H4">
-        <v>0.746031746031746</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -652,13 +1127,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.7766089108910891</v>
+        <v>0.77660891089108908</v>
       </c>
       <c r="N4">
-        <v>0.5198019801980198</v>
+        <v>0.51980198019801982</v>
       </c>
       <c r="O4">
-        <v>0.2568069306930693</v>
+        <v>0.25680693069306931</v>
       </c>
       <c r="P4">
         <v>0.66</v>
@@ -667,53 +1142,45 @@
         <v>0.59</v>
       </c>
       <c r="R4">
-        <v>0.07000000000000006</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LTR163_2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
       </c>
       <c r="C5">
         <v>2022</v>
       </c>
       <c r="D5">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E5">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7564102564102564</v>
+        <v>0.75641025641025639</v>
       </c>
       <c r="H5">
-        <v>0.7654320987654321</v>
+        <v>0.76543209876543206</v>
       </c>
       <c r="I5">
-        <v>-0.009021842355175669</v>
+        <v>-9.0218423551756688E-3</v>
       </c>
       <c r="J5">
         <v>0.8</v>
@@ -725,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.7742011278195489</v>
+        <v>0.77420112781954886</v>
       </c>
       <c r="N5">
-        <v>0.5106132075471698</v>
+        <v>0.51061320754716977</v>
       </c>
       <c r="O5">
-        <v>0.2635879202723791</v>
+        <v>0.26358792027237909</v>
       </c>
       <c r="P5">
         <v>0.79</v>
@@ -740,71 +1207,63 @@
         <v>0.73</v>
       </c>
       <c r="R5">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" t="s">
+        <v>27</v>
       </c>
       <c r="U5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LTR127_2015</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
         <v>2015</v>
       </c>
       <c r="D6">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="G6">
         <v>0.3888888888888889</v>
       </c>
       <c r="H6">
-        <v>0.4523809523809523</v>
+        <v>0.45238095238095227</v>
       </c>
       <c r="I6">
-        <v>-0.06349206349206338</v>
+        <v>-6.3492063492063378E-2</v>
       </c>
       <c r="J6">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K6">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.6198132780082988</v>
+        <v>0.61981327800829877</v>
       </c>
       <c r="N6">
-        <v>0.4680962343096234</v>
+        <v>0.46809623430962338</v>
       </c>
       <c r="O6">
-        <v>0.1517170436986754</v>
+        <v>0.15171704369867539</v>
       </c>
       <c r="P6">
         <v>0.31</v>
@@ -815,30 +1274,22 @@
       <c r="R6">
         <v>0.06</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Bad</t>
-        </is>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" t="s">
+        <v>33</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LTR127_2020</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
       </c>
       <c r="C7">
         <v>2020</v>
@@ -853,13 +1304,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5777777777777778</v>
+        <v>0.57777777777777783</v>
       </c>
       <c r="H7">
-        <v>0.6041666666666666</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="I7">
-        <v>-0.0263888888888888</v>
+        <v>-2.6388888888888799E-2</v>
       </c>
       <c r="J7">
         <v>0.2</v>
@@ -871,13 +1322,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.62902706185567</v>
+        <v>0.62902706185567003</v>
       </c>
       <c r="N7">
-        <v>0.390222293814433</v>
+        <v>0.39022229381443302</v>
       </c>
       <c r="O7">
-        <v>0.238804768041237</v>
+        <v>0.23880476804123699</v>
       </c>
       <c r="P7">
         <v>0.48</v>
@@ -888,69 +1339,61 @@
       <c r="R7">
         <v>0.06</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
       </c>
       <c r="U7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LTR450_2015</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LTR450</t>
-        </is>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
       </c>
       <c r="C8">
         <v>2015</v>
       </c>
       <c r="D8">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E8">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.5277777777777778</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="H8">
-        <v>0.5277777777777778</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K8">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.6028761061946902</v>
+        <v>0.60287610619469023</v>
       </c>
       <c r="N8">
-        <v>0.3429203539823009</v>
+        <v>0.34292035398230092</v>
       </c>
       <c r="O8">
-        <v>0.2599557522123893</v>
+        <v>0.25995575221238931</v>
       </c>
       <c r="P8">
         <v>0.38</v>
@@ -961,69 +1404,61 @@
       <c r="R8">
         <v>0.06</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" t="s">
+        <v>24</v>
       </c>
       <c r="U8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LTR1466_2019</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
       </c>
       <c r="C9">
         <v>2019</v>
       </c>
       <c r="D9">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E9">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.7283950617283951</v>
+        <v>0.72839506172839508</v>
       </c>
       <c r="H9">
-        <v>0.7202380952380952</v>
+        <v>0.72023809523809523</v>
       </c>
       <c r="I9">
-        <v>0.008156966490299844</v>
+        <v>8.156966490299844E-3</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L9">
-        <v>0.06666666666666665</v>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="M9">
-        <v>0.7776280323450135</v>
+        <v>0.77762803234501354</v>
       </c>
       <c r="N9">
-        <v>0.6024258760107817</v>
+        <v>0.60242587601078168</v>
       </c>
       <c r="O9">
-        <v>0.1752021563342319</v>
+        <v>0.17520215633423189</v>
       </c>
       <c r="P9">
         <v>0.83</v>
@@ -1032,53 +1467,45 @@
         <v>0.77</v>
       </c>
       <c r="R9">
-        <v>0.05999999999999994</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>5.9999999999999942E-2</v>
+      </c>
+      <c r="S9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s">
+        <v>27</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LTR127_2017</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
       </c>
       <c r="C10">
         <v>2017</v>
       </c>
       <c r="D10">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E10">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F10">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G10">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="H10">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="I10">
-        <v>5.551115123125783E-17</v>
+        <v>5.5511151231257827E-17</v>
       </c>
       <c r="J10">
         <v>0.2</v>
@@ -1093,10 +1520,10 @@
         <v>0.640194489465154</v>
       </c>
       <c r="N10">
-        <v>0.4558346839546191</v>
+        <v>0.45583468395461912</v>
       </c>
       <c r="O10">
-        <v>0.1843598055105349</v>
+        <v>0.18435980551053491</v>
       </c>
       <c r="P10">
         <v>0.36</v>
@@ -1105,41 +1532,33 @@
         <v>0.31</v>
       </c>
       <c r="R10">
-        <v>0.04999999999999999</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" t="s">
+        <v>24</v>
       </c>
       <c r="U10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LTR625_2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LTR625</t>
-        </is>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
       </c>
       <c r="C11">
         <v>2022</v>
       </c>
       <c r="D11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1148,25 +1567,25 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="H11">
-        <v>0.7999999999999999</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="I11">
-        <v>0.02222222222222237</v>
+        <v>2.2222222222222369E-2</v>
       </c>
       <c r="J11">
-        <v>1.066666666666667</v>
+        <v>1.0666666666666671</v>
       </c>
       <c r="K11">
-        <v>1.066666666666667</v>
+        <v>1.0666666666666671</v>
       </c>
       <c r="L11">
-        <v>-4.440892098500626E-16</v>
+        <v>-4.4408920985006262E-16</v>
       </c>
       <c r="M11">
-        <v>0.7462661463939719</v>
+        <v>0.74626614639397193</v>
       </c>
       <c r="N11">
-        <v>0.5844750406945198</v>
+        <v>0.58447504069451983</v>
       </c>
       <c r="O11">
         <v>0.1617911056994521</v>
@@ -1178,59 +1597,51 @@
         <v>0.78</v>
       </c>
       <c r="R11">
-        <v>0.04999999999999993</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>4.9999999999999933E-2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>27</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LTR297_2021</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
       </c>
       <c r="C12">
         <v>2021</v>
       </c>
       <c r="D12">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G12">
-        <v>0.7051282051282052</v>
+        <v>0.70512820512820518</v>
       </c>
       <c r="H12">
-        <v>0.7051282051282052</v>
+        <v>0.70512820512820518</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K12">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1251,71 +1662,63 @@
         <v>0.54</v>
       </c>
       <c r="R12">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>-4.0000000000000042E-2</v>
+      </c>
+      <c r="S12" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" t="s">
+        <v>23</v>
       </c>
       <c r="U12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LTR86_2015</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
       </c>
       <c r="C13">
         <v>2015</v>
       </c>
       <c r="D13">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E13">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.6388888888888888</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="H13">
-        <v>0.6388888888888888</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K13">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L13">
-        <v>0.0666666666666666</v>
+        <v>6.6666666666666596E-2</v>
       </c>
       <c r="M13">
         <v>0.6891025641025641</v>
       </c>
       <c r="N13">
-        <v>0.5982905982905983</v>
+        <v>0.59829059829059827</v>
       </c>
       <c r="O13">
-        <v>0.09081196581196582</v>
+        <v>9.0811965811965822E-2</v>
       </c>
       <c r="P13">
         <v>0.5</v>
@@ -1324,105 +1727,89 @@
         <v>0.46</v>
       </c>
       <c r="R13">
-        <v>0.03999999999999998</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.999999999999998E-2</v>
+      </c>
+      <c r="S13" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" t="s">
+        <v>23</v>
       </c>
       <c r="U13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LTR1447_2015</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LTR1447</t>
-        </is>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
       </c>
       <c r="C14">
         <v>2015</v>
       </c>
       <c r="D14">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E14">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F14">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="G14">
-        <v>0.782051282051282</v>
+        <v>0.78205128205128205</v>
       </c>
       <c r="H14">
         <v>0.7901234567901233</v>
       </c>
       <c r="I14">
-        <v>-0.008072174738841253</v>
+        <v>-8.0721747388412535E-3</v>
       </c>
       <c r="J14">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K14">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.6768018018018018</v>
+        <v>0.67680180180180183</v>
       </c>
       <c r="N14">
-        <v>0.6768018018018018</v>
+        <v>0.67680180180180183</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="Q14">
         <v>0.65</v>
       </c>
       <c r="R14">
-        <v>0.03999999999999992</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T14" t="s">
+        <v>27</v>
       </c>
       <c r="U14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LTR1466_2016</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
       </c>
       <c r="C15">
         <v>2016</v>
@@ -1437,65 +1824,57 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.6533333333333333</v>
+        <v>0.65333333333333332</v>
       </c>
       <c r="H15">
-        <v>0.6533333333333333</v>
+        <v>0.65333333333333332</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K15">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.6954713493530498</v>
+        <v>0.69547134935304977</v>
       </c>
       <c r="N15">
-        <v>0.5641698473282443</v>
+        <v>0.56416984732824427</v>
       </c>
       <c r="O15">
-        <v>0.1313015020248055</v>
+        <v>0.13130150202480551</v>
       </c>
       <c r="P15">
         <v>0.6</v>
       </c>
       <c r="Q15">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="R15">
-        <v>0.03999999999999992</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+      <c r="S15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T15" t="s">
+        <v>23</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LTR1687_2016</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
       </c>
       <c r="C16">
         <v>2016</v>
@@ -1510,28 +1889,28 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="H16">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K16">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.7490458015267176</v>
+        <v>0.74904580152671763</v>
       </c>
       <c r="N16">
-        <v>0.5717054263565891</v>
+        <v>0.57170542635658905</v>
       </c>
       <c r="O16">
         <v>0.1773403751701286</v>
@@ -1540,44 +1919,36 @@
         <v>0.59</v>
       </c>
       <c r="Q16">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R16">
-        <v>0.03999999999999992</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+      <c r="S16" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" t="s">
+        <v>23</v>
       </c>
       <c r="U16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LTR1687_2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
       </c>
       <c r="C17">
         <v>2022</v>
       </c>
       <c r="D17">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E17">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1586,28 +1957,28 @@
         <v>1.074074074074074</v>
       </c>
       <c r="H17">
-        <v>0.9666666666666667</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="I17">
-        <v>0.1074074074074075</v>
+        <v>0.10740740740740751</v>
       </c>
       <c r="J17">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K17">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L17">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M17">
-        <v>0.777027027027027</v>
+        <v>0.77702702702702697</v>
       </c>
       <c r="N17">
         <v>0.7432432432432432</v>
       </c>
       <c r="O17">
-        <v>0.03378378378378377</v>
+        <v>3.3783783783783772E-2</v>
       </c>
       <c r="P17">
         <v>0.7</v>
@@ -1616,50 +1987,42 @@
         <v>0.66</v>
       </c>
       <c r="R17">
-        <v>0.03999999999999992</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+      <c r="S17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T17" t="s">
+        <v>27</v>
       </c>
       <c r="U17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LTR1461_2016</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
       </c>
       <c r="C18">
         <v>2016</v>
       </c>
       <c r="D18">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E18">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F18">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G18">
-        <v>0.8703703703703703</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="H18">
-        <v>0.8703703703703703</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1674,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0.8234797297297297</v>
+        <v>0.82347972972972971</v>
       </c>
       <c r="N18">
-        <v>0.7908163265306123</v>
+        <v>0.79081632653061229</v>
       </c>
       <c r="O18">
-        <v>0.03266340319911742</v>
+        <v>3.2663403199117418E-2</v>
       </c>
       <c r="P18">
         <v>0.64</v>
@@ -1689,32 +2052,24 @@
         <v>0.67</v>
       </c>
       <c r="R18">
-        <v>-0.03000000000000003</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>-3.000000000000003E-2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>27</v>
+      </c>
+      <c r="T18" t="s">
+        <v>27</v>
       </c>
       <c r="U18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LTR1461_2019</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
       </c>
       <c r="C19">
         <v>2019</v>
@@ -1729,13 +2084,13 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.7413793103448275</v>
+        <v>0.74137931034482751</v>
       </c>
       <c r="H19">
-        <v>0.7559523809523809</v>
+        <v>0.75595238095238093</v>
       </c>
       <c r="I19">
-        <v>-0.01457307060755342</v>
+        <v>-1.457307060755342E-2</v>
       </c>
       <c r="J19">
         <v>0.6</v>
@@ -1747,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.7889990982867447</v>
+        <v>0.78899909828674475</v>
       </c>
       <c r="N19">
-        <v>0.6670808856755536</v>
+        <v>0.66708088567555357</v>
       </c>
       <c r="O19">
-        <v>0.1219182126111912</v>
+        <v>0.12191821261119121</v>
       </c>
       <c r="P19">
         <v>0.66</v>
@@ -1762,32 +2117,24 @@
         <v>0.63</v>
       </c>
       <c r="R19">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T19" t="s">
+        <v>27</v>
       </c>
       <c r="U19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LTR1461_2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
       </c>
       <c r="C20">
         <v>2022</v>
@@ -1802,31 +2149,31 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.6274509803921569</v>
+        <v>0.62745098039215685</v>
       </c>
       <c r="H20">
-        <v>0.6274509803921569</v>
+        <v>0.62745098039215685</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K20">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L20">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M20">
-        <v>0.7568807339449541</v>
+        <v>0.75688073394495414</v>
       </c>
       <c r="N20">
-        <v>0.6594036697247707</v>
+        <v>0.65940366972477071</v>
       </c>
       <c r="O20">
-        <v>0.09747706422018343</v>
+        <v>9.7477064220183429E-2</v>
       </c>
       <c r="P20">
         <v>0.54</v>
@@ -1835,32 +2182,24 @@
         <v>0.51</v>
       </c>
       <c r="R20">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+      <c r="S20" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" t="s">
+        <v>23</v>
       </c>
       <c r="U20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LTR1466_2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
       </c>
       <c r="C21">
         <v>2022</v>
@@ -1875,28 +2214,28 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.5686274509803922</v>
+        <v>0.56862745098039225</v>
       </c>
       <c r="H21">
-        <v>0.5686274509803922</v>
+        <v>0.56862745098039225</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K21">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0.6712392108508015</v>
+        <v>0.67123921085080152</v>
       </c>
       <c r="N21">
-        <v>0.5630421313506815</v>
+        <v>0.56304213135068149</v>
       </c>
       <c r="O21">
         <v>0.10819707950012</v>
@@ -1908,32 +2247,24 @@
         <v>0.49</v>
       </c>
       <c r="R21">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" t="s">
+        <v>23</v>
       </c>
       <c r="U21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LTR1488_2015</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
       </c>
       <c r="C22">
         <v>2015</v>
@@ -1948,31 +2279,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="H22">
-        <v>0.7105263157894736</v>
+        <v>0.71052631578947356</v>
       </c>
       <c r="I22">
-        <v>0.01169590643274865</v>
+        <v>1.169590643274865E-2</v>
       </c>
       <c r="J22">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K22">
         <v>0.4</v>
       </c>
       <c r="L22">
-        <v>0.06666666666666665</v>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="M22">
         <v>0.7799586776859504</v>
       </c>
       <c r="N22">
-        <v>0.759297520661157</v>
+        <v>0.75929752066115697</v>
       </c>
       <c r="O22">
-        <v>0.02066115702479343</v>
+        <v>2.0661157024793431E-2</v>
       </c>
       <c r="P22">
         <v>0.62</v>
@@ -1981,53 +2312,45 @@
         <v>0.59</v>
       </c>
       <c r="R22">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+      <c r="S22" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" t="s">
+        <v>23</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LTR386_2016</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
       </c>
       <c r="C23">
         <v>2016</v>
       </c>
       <c r="D23">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E23">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F23">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G23">
-        <v>0.7799999999999999</v>
+        <v>0.77999999999999992</v>
       </c>
       <c r="H23">
-        <v>0.7820512820512823</v>
+        <v>0.78205128205128227</v>
       </c>
       <c r="I23">
-        <v>-0.002051282051282355</v>
+        <v>-2.0512820512823549E-3</v>
       </c>
       <c r="J23">
         <v>0.6</v>
@@ -2039,56 +2362,48 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.704828660436137</v>
+        <v>0.70482866043613701</v>
       </c>
       <c r="N23">
-        <v>0.6756230529595015</v>
+        <v>0.67562305295950154</v>
       </c>
       <c r="O23">
-        <v>0.02920560747663548</v>
+        <v>2.9205607476635479E-2</v>
       </c>
       <c r="P23">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="Q23">
         <v>0.72</v>
       </c>
       <c r="R23">
-        <v>-0.03000000000000003</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>-3.000000000000003E-2</v>
+      </c>
+      <c r="S23" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" t="s">
+        <v>27</v>
       </c>
       <c r="U23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LTR386_2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
       </c>
       <c r="C24">
         <v>2022</v>
       </c>
       <c r="D24">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E24">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2097,10 +2412,10 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="H24">
-        <v>0.8118279569892474</v>
+        <v>0.81182795698924737</v>
       </c>
       <c r="I24">
-        <v>0.01039426523297493</v>
+        <v>1.0394265232974931E-2</v>
       </c>
       <c r="J24">
         <v>0.6</v>
@@ -2112,13 +2427,13 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.7205029013539651</v>
+        <v>0.72050290135396511</v>
       </c>
       <c r="N24">
-        <v>0.5766369047619048</v>
+        <v>0.57663690476190477</v>
       </c>
       <c r="O24">
-        <v>0.1438659965920603</v>
+        <v>0.14386599659206031</v>
       </c>
       <c r="P24">
         <v>0.74</v>
@@ -2127,53 +2442,45 @@
         <v>0.71</v>
       </c>
       <c r="R24">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+      <c r="S24" t="s">
+        <v>27</v>
+      </c>
+      <c r="T24" t="s">
+        <v>27</v>
       </c>
       <c r="U24" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LTR1488_2016</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
       </c>
       <c r="C25">
         <v>2016</v>
       </c>
       <c r="D25">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E25">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.8492063492063492</v>
+        <v>0.84920634920634919</v>
       </c>
       <c r="H25">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I25">
-        <v>0.01587301587301582</v>
+        <v>1.587301587301582E-2</v>
       </c>
       <c r="J25">
         <v>0.4</v>
@@ -2185,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.8073566084788031</v>
+        <v>0.80735660847880308</v>
       </c>
       <c r="N25">
-        <v>0.7590399002493765</v>
+        <v>0.75903990024937651</v>
       </c>
       <c r="O25">
-        <v>0.04831670822942657</v>
+        <v>4.8316708229426568E-2</v>
       </c>
       <c r="P25">
         <v>0.68</v>
@@ -2200,32 +2507,24 @@
         <v>0.66</v>
       </c>
       <c r="R25">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S25" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" t="s">
+        <v>27</v>
       </c>
       <c r="U25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LTR1492_2019</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
       </c>
       <c r="C26">
         <v>2019</v>
@@ -2240,13 +2539,13 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.607843137254902</v>
+        <v>0.60784313725490202</v>
       </c>
       <c r="H26">
-        <v>0.6018518518518517</v>
+        <v>0.60185185185185175</v>
       </c>
       <c r="I26">
-        <v>0.005991285403050273</v>
+        <v>5.9912854030502727E-3</v>
       </c>
       <c r="J26">
         <v>0.2</v>
@@ -2258,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.669378698224852</v>
+        <v>0.66937869822485196</v>
       </c>
       <c r="N26">
         <v>0.5750739644970414</v>
       </c>
       <c r="O26">
-        <v>0.09430473372781056</v>
+        <v>9.4304733727810564E-2</v>
       </c>
       <c r="P26">
         <v>0.49</v>
@@ -2273,41 +2572,33 @@
         <v>0.47</v>
       </c>
       <c r="R26">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S26" t="s">
+        <v>23</v>
+      </c>
+      <c r="T26" t="s">
+        <v>23</v>
       </c>
       <c r="U26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LTR1502_2015</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LTR1502</t>
-        </is>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
       </c>
       <c r="C27">
         <v>2015</v>
       </c>
       <c r="D27">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E27">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2322,22 +2613,22 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K27">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.7174744897959184</v>
+        <v>0.71747448979591844</v>
       </c>
       <c r="N27">
-        <v>0.6345663265306123</v>
+        <v>0.63456632653061229</v>
       </c>
       <c r="O27">
-        <v>0.08290816326530615</v>
+        <v>8.2908163265306145E-2</v>
       </c>
       <c r="P27">
         <v>0.72</v>
@@ -2346,32 +2637,24 @@
         <v>0.7</v>
       </c>
       <c r="R27">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S27" t="s">
+        <v>27</v>
+      </c>
+      <c r="T27" t="s">
+        <v>27</v>
       </c>
       <c r="U27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LTR163_2016</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
       </c>
       <c r="C28">
         <v>2016</v>
@@ -2386,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.7976190476190476</v>
+        <v>0.79761904761904756</v>
       </c>
       <c r="H28">
-        <v>0.7988505747126436</v>
+        <v>0.79885057471264365</v>
       </c>
       <c r="I28">
-        <v>-0.001231527093596085</v>
+        <v>-1.2315270935960849E-3</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2404,13 +2687,13 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.7215862632869992</v>
+        <v>0.72158626328699915</v>
       </c>
       <c r="N28">
-        <v>0.6541291905151266</v>
+        <v>0.65412919051512664</v>
       </c>
       <c r="O28">
-        <v>0.06745707277187252</v>
+        <v>6.7457072771872517E-2</v>
       </c>
       <c r="P28">
         <v>0.88</v>
@@ -2419,53 +2702,45 @@
         <v>0.86</v>
       </c>
       <c r="R28">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S28" t="s">
+        <v>39</v>
+      </c>
+      <c r="T28" t="s">
+        <v>39</v>
       </c>
       <c r="U28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LTR297_2018</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
       <c r="D29">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E29">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F29">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G29">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="H29">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="I29">
-        <v>5.551115123125783E-17</v>
+        <v>5.5511151231257827E-17</v>
       </c>
       <c r="J29">
         <v>0.2</v>
@@ -2477,13 +2752,13 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.7674050632911391</v>
+        <v>0.76740506329113911</v>
       </c>
       <c r="N29">
-        <v>0.6645569620253163</v>
+        <v>0.66455696202531633</v>
       </c>
       <c r="O29">
-        <v>0.1028481012658228</v>
+        <v>0.10284810126582281</v>
       </c>
       <c r="P29">
         <v>0.39</v>
@@ -2492,41 +2767,33 @@
         <v>0.37</v>
       </c>
       <c r="R29">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S29" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" t="s">
+        <v>24</v>
       </c>
       <c r="U29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LTR450_2020</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LTR450</t>
-        </is>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
       </c>
       <c r="C30">
         <v>2020</v>
       </c>
       <c r="D30">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E30">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2550,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.6114457831325301</v>
+        <v>0.61144578313253006</v>
       </c>
       <c r="N30">
-        <v>0.5406626506024096</v>
+        <v>0.54066265060240959</v>
       </c>
       <c r="O30">
-        <v>0.07078313253012047</v>
+        <v>7.0783132530120474E-2</v>
       </c>
       <c r="P30">
         <v>0.38</v>
@@ -2565,53 +2832,45 @@
         <v>0.36</v>
       </c>
       <c r="R30">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S30" t="s">
+        <v>24</v>
+      </c>
+      <c r="T30" t="s">
+        <v>24</v>
       </c>
       <c r="U30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LTR706_2015</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LTR706</t>
-        </is>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
       </c>
       <c r="C31">
         <v>2015</v>
       </c>
       <c r="D31">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E31">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.4259259259259259</v>
+        <v>0.42592592592592587</v>
       </c>
       <c r="H31">
-        <v>0.4259259259259258</v>
+        <v>0.42592592592592582</v>
       </c>
       <c r="I31">
-        <v>5.551115123125783E-17</v>
+        <v>5.5511151231257827E-17</v>
       </c>
       <c r="J31">
         <v>0.1333333333333333</v>
@@ -2623,13 +2882,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M31">
-        <v>0.6716417910447761</v>
+        <v>0.67164179104477606</v>
       </c>
       <c r="N31">
-        <v>0.5876865671641791</v>
+        <v>0.58768656716417911</v>
       </c>
       <c r="O31">
-        <v>0.08395522388059695</v>
+        <v>8.3955223880596952E-2</v>
       </c>
       <c r="P31">
         <v>0.39</v>
@@ -2638,53 +2897,45 @@
         <v>0.37</v>
       </c>
       <c r="R31">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+      <c r="S31" t="s">
+        <v>24</v>
+      </c>
+      <c r="T31" t="s">
+        <v>24</v>
       </c>
       <c r="U31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LTR86_2016</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
       </c>
       <c r="C32">
         <v>2016</v>
       </c>
       <c r="D32">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G32">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H32">
-        <v>0.6893939393939394</v>
+        <v>0.68939393939393945</v>
       </c>
       <c r="I32">
-        <v>-0.02272727272727282</v>
+        <v>-2.2727272727272822E-2</v>
       </c>
       <c r="J32">
         <v>0.1333333333333333</v>
@@ -2696,10 +2947,10 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M32">
-        <v>0.7788944723618091</v>
+        <v>0.77889447236180909</v>
       </c>
       <c r="N32">
-        <v>0.6752512562814069</v>
+        <v>0.67525125628140692</v>
       </c>
       <c r="O32">
         <v>0.1036432160804022</v>
@@ -2711,50 +2962,42 @@
         <v>0.5</v>
       </c>
       <c r="R32">
-        <v>-0.02000000000000002</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>-2.0000000000000021E-2</v>
+      </c>
+      <c r="S32" t="s">
+        <v>23</v>
+      </c>
+      <c r="T32" t="s">
+        <v>23</v>
       </c>
       <c r="U32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LTR1063_2021</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LTR1063</t>
-        </is>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
       </c>
       <c r="C33">
         <v>2021</v>
       </c>
       <c r="D33">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E33">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F33">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G33">
-        <v>0.3958333333333333</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="H33">
-        <v>0.3958333333333333</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2769,13 +3012,13 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0.6405693950177935</v>
+        <v>0.64056939501779353</v>
       </c>
       <c r="N33">
-        <v>0.567170818505338</v>
+        <v>0.56717081850533801</v>
       </c>
       <c r="O33">
-        <v>0.07339857651245552</v>
+        <v>7.3398576512455516E-2</v>
       </c>
       <c r="P33">
         <v>0.35</v>
@@ -2784,50 +3027,42 @@
         <v>0.33</v>
       </c>
       <c r="R33">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>1.9999999999999959E-2</v>
+      </c>
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+      <c r="T33" t="s">
+        <v>24</v>
       </c>
       <c r="U33" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LTR308_2018</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>LTR308</t>
-        </is>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
       </c>
       <c r="C34">
         <v>2018</v>
       </c>
       <c r="D34">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E34">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.3541666666666667</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="H34">
-        <v>0.3541666666666667</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2842,13 +3077,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M34">
-        <v>0.6134259259259259</v>
+        <v>0.61342592592592593</v>
       </c>
       <c r="N34">
-        <v>0.5324074074074073</v>
+        <v>0.53240740740740733</v>
       </c>
       <c r="O34">
-        <v>0.0810185185185186</v>
+        <v>8.1018518518518601E-2</v>
       </c>
       <c r="P34">
         <v>0.36</v>
@@ -2857,53 +3092,45 @@
         <v>0.34</v>
       </c>
       <c r="R34">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>1.9999999999999959E-2</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+      <c r="T34" t="s">
+        <v>24</v>
       </c>
       <c r="U34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LTR1447_2022</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LTR1447</t>
-        </is>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
       <c r="D35">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E35">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.7828282828282829</v>
+        <v>0.78282828282828287</v>
       </c>
       <c r="H35">
-        <v>0.7843137254901961</v>
+        <v>0.78431372549019607</v>
       </c>
       <c r="I35">
-        <v>-0.001485442661913194</v>
+        <v>-1.485442661913194E-3</v>
       </c>
       <c r="J35">
         <v>0.6</v>
@@ -2915,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1.052013422818792</v>
+        <v>1.0520134228187921</v>
       </c>
       <c r="N35">
-        <v>1.042506720430108</v>
+        <v>1.0425067204301079</v>
       </c>
       <c r="O35">
-        <v>0.009506702388683896</v>
+        <v>9.5067023886838964E-3</v>
       </c>
       <c r="P35">
         <v>0.78</v>
@@ -2930,105 +3157,89 @@
         <v>0.77</v>
       </c>
       <c r="R35">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S35" t="s">
+        <v>27</v>
+      </c>
+      <c r="T35" t="s">
+        <v>27</v>
       </c>
       <c r="U35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LTR1449_2015</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>LTR1449</t>
-        </is>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
       </c>
       <c r="C36">
         <v>2015</v>
       </c>
       <c r="D36">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E36">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.7698412698412698</v>
+        <v>0.76984126984126977</v>
       </c>
       <c r="H36">
-        <v>0.7999999999999999</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="I36">
-        <v>-0.03015873015873016</v>
+        <v>-3.0158730158730159E-2</v>
       </c>
       <c r="J36">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K36">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0.6937919463087248</v>
+        <v>0.69379194630872476</v>
       </c>
       <c r="N36">
-        <v>0.6937919463087248</v>
+        <v>0.69379194630872476</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="Q36">
         <v>0.7</v>
       </c>
       <c r="R36">
-        <v>-0.01000000000000001</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>-1.0000000000000011E-2</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+      <c r="T36" t="s">
+        <v>27</v>
       </c>
       <c r="U36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LTR1488_2019</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
       </c>
       <c r="C37">
         <v>2019</v>
@@ -3043,13 +3254,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H37">
-        <v>0.7037037037037037</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="I37">
-        <v>-0.03703703703703709</v>
+        <v>-3.703703703703709E-2</v>
       </c>
       <c r="J37">
         <v>0.2</v>
@@ -3061,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.6811097256857854</v>
+        <v>0.68110972568578543</v>
       </c>
       <c r="N37">
-        <v>0.6795511221945136</v>
+        <v>0.67955112219451363</v>
       </c>
       <c r="O37">
-        <v>0.001558603491271793</v>
+        <v>1.558603491271793E-3</v>
       </c>
       <c r="P37">
         <v>0.51</v>
@@ -3076,53 +3287,45 @@
         <v>0.52</v>
       </c>
       <c r="R37">
-        <v>-0.01000000000000001</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>-1.0000000000000011E-2</v>
+      </c>
+      <c r="S37" t="s">
+        <v>23</v>
+      </c>
+      <c r="T37" t="s">
+        <v>23</v>
       </c>
       <c r="U37" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LTR1488_2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
       </c>
       <c r="C38">
         <v>2022</v>
       </c>
       <c r="D38">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E38">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.5800000000000001</v>
+        <v>0.58000000000000007</v>
       </c>
       <c r="H38">
-        <v>0.5864197530864197</v>
+        <v>0.58641975308641969</v>
       </c>
       <c r="I38">
-        <v>-0.006419753086419622</v>
+        <v>-6.4197530864196217E-3</v>
       </c>
       <c r="J38">
         <v>0.1333333333333333</v>
@@ -3137,10 +3340,10 @@
         <v>0.625</v>
       </c>
       <c r="N38">
-        <v>0.5909653465346534</v>
+        <v>0.59096534653465338</v>
       </c>
       <c r="O38">
-        <v>0.03403465346534662</v>
+        <v>3.403465346534662E-2</v>
       </c>
       <c r="P38">
         <v>0.42</v>
@@ -3149,41 +3352,33 @@
         <v>0.41</v>
       </c>
       <c r="R38">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S38" t="s">
+        <v>23</v>
+      </c>
+      <c r="T38" t="s">
+        <v>23</v>
       </c>
       <c r="U38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LTR1492_2016</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
       </c>
       <c r="C39">
         <v>2016</v>
       </c>
       <c r="D39">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E39">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3192,10 +3387,10 @@
         <v>0.6</v>
       </c>
       <c r="H39">
-        <v>0.6111111111111112</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="I39">
-        <v>-0.01111111111111118</v>
+        <v>-1.1111111111111179E-2</v>
       </c>
       <c r="J39">
         <v>0.2</v>
@@ -3210,10 +3405,10 @@
         <v>0.6772113022113021</v>
       </c>
       <c r="N39">
-        <v>0.6342137592137592</v>
+        <v>0.63421375921375922</v>
       </c>
       <c r="O39">
-        <v>0.04299754299754288</v>
+        <v>4.2997542997542881E-2</v>
       </c>
       <c r="P39">
         <v>0.45</v>
@@ -3222,50 +3417,42 @@
         <v>0.44</v>
       </c>
       <c r="R39">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S39" t="s">
+        <v>23</v>
+      </c>
+      <c r="T39" t="s">
+        <v>23</v>
       </c>
       <c r="U39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LTR1501_2016</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LTR1501</t>
-        </is>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
       </c>
       <c r="C40">
         <v>2016</v>
       </c>
       <c r="D40">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E40">
         <v>0.5</v>
       </c>
       <c r="F40">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G40">
-        <v>0.753968253968254</v>
+        <v>0.75396825396825395</v>
       </c>
       <c r="H40">
-        <v>0.753968253968254</v>
+        <v>0.75396825396825395</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3280,13 +3467,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M40">
-        <v>0.6205568720379147</v>
+        <v>0.62055687203791465</v>
       </c>
       <c r="N40">
-        <v>0.4102488151658767</v>
+        <v>0.41024881516587669</v>
       </c>
       <c r="O40">
-        <v>0.210308056872038</v>
+        <v>0.21030805687203799</v>
       </c>
       <c r="P40">
         <v>0.46</v>
@@ -3295,32 +3482,24 @@
         <v>0.45</v>
       </c>
       <c r="R40">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S40" t="s">
+        <v>23</v>
+      </c>
+      <c r="T40" t="s">
+        <v>23</v>
       </c>
       <c r="U40" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LTR1687_2017</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
       </c>
       <c r="C41">
         <v>2017</v>
@@ -3335,10 +3514,10 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.576923076923077</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="H41">
-        <v>0.576923076923077</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3353,13 +3532,13 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0.6631679389312978</v>
+        <v>0.66316793893129777</v>
       </c>
       <c r="N41">
         <v>0.625</v>
       </c>
       <c r="O41">
-        <v>0.03816793893129777</v>
+        <v>3.8167938931297767E-2</v>
       </c>
       <c r="P41">
         <v>0.54</v>
@@ -3368,50 +3547,42 @@
         <v>0.53</v>
       </c>
       <c r="R41">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S41" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" t="s">
+        <v>23</v>
       </c>
       <c r="U41" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LTR297_2015</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
       </c>
       <c r="C42">
         <v>2015</v>
       </c>
       <c r="D42">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E42">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.4166666666666667</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H42">
-        <v>0.4166666666666667</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3426,13 +3597,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M42">
-        <v>0.5686475409836065</v>
+        <v>0.56864754098360648</v>
       </c>
       <c r="N42">
-        <v>0.5122950819672131</v>
+        <v>0.51229508196721307</v>
       </c>
       <c r="O42">
-        <v>0.05635245901639341</v>
+        <v>5.6352459016393408E-2</v>
       </c>
       <c r="P42">
         <v>0.36</v>
@@ -3441,50 +3612,42 @@
         <v>0.35</v>
       </c>
       <c r="R42">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+      <c r="T42" t="s">
+        <v>24</v>
       </c>
       <c r="U42" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LTR337_2016</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" t="s">
+        <v>87</v>
       </c>
       <c r="C43">
         <v>2016</v>
       </c>
       <c r="D43">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E43">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.7388888888888889</v>
+        <v>0.73888888888888893</v>
       </c>
       <c r="H43">
-        <v>0.7388888888888889</v>
+        <v>0.73888888888888893</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3502,10 +3665,10 @@
         <v>0.7444707740916271</v>
       </c>
       <c r="N43">
-        <v>0.7192930489731437</v>
+        <v>0.71929304897314372</v>
       </c>
       <c r="O43">
-        <v>0.02517772511848337</v>
+        <v>2.517772511848337E-2</v>
       </c>
       <c r="P43">
         <v>0.78</v>
@@ -3514,53 +3677,45 @@
         <v>0.77</v>
       </c>
       <c r="R43">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S43" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" t="s">
+        <v>27</v>
       </c>
       <c r="U43" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LTR337_2022</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
       </c>
       <c r="C44">
         <v>2022</v>
       </c>
       <c r="D44">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E44">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F44">
-        <v>-0.1666666666666667</v>
+        <v>-0.16666666666666671</v>
       </c>
       <c r="G44">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="H44">
-        <v>0.7156862745098039</v>
+        <v>0.71568627450980393</v>
       </c>
       <c r="I44">
-        <v>0.006535947712418277</v>
+        <v>6.5359477124182774E-3</v>
       </c>
       <c r="J44">
         <v>0.8</v>
@@ -3572,10 +3727,10 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0.759308510638298</v>
+        <v>0.75930851063829796</v>
       </c>
       <c r="N44">
-        <v>0.6490384615384616</v>
+        <v>0.64903846153846156</v>
       </c>
       <c r="O44">
         <v>0.1102700490998364</v>
@@ -3587,32 +3742,24 @@
         <v>0.75</v>
       </c>
       <c r="R44">
-        <v>-0.01000000000000001</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>-1.0000000000000011E-2</v>
+      </c>
+      <c r="S44" t="s">
+        <v>27</v>
+      </c>
+      <c r="T44" t="s">
+        <v>27</v>
       </c>
       <c r="U44" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LTR351_2019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LTR351</t>
-        </is>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
       </c>
       <c r="C45">
         <v>2019</v>
@@ -3627,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.7045454545454546</v>
+        <v>0.70454545454545459</v>
       </c>
       <c r="H45">
         <v>0.7045454545454547</v>
@@ -3636,22 +3783,22 @@
         <v>-1.110223024625157E-16</v>
       </c>
       <c r="J45">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K45">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L45">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M45">
-        <v>0.6763059701492536</v>
+        <v>0.67630597014925364</v>
       </c>
       <c r="N45">
-        <v>0.6669776119402985</v>
+        <v>0.66697761194029848</v>
       </c>
       <c r="O45">
-        <v>0.009328358208955168</v>
+        <v>9.3283582089551675E-3</v>
       </c>
       <c r="P45">
         <v>0.54</v>
@@ -3660,41 +3807,33 @@
         <v>0.53</v>
       </c>
       <c r="R45">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S45" t="s">
+        <v>23</v>
+      </c>
+      <c r="T45" t="s">
+        <v>23</v>
       </c>
       <c r="U45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LTR411_2022</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LTR411</t>
-        </is>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>92</v>
       </c>
       <c r="C46">
         <v>2022</v>
       </c>
       <c r="D46">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E46">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3703,28 +3842,28 @@
         <v>0.8076923076923076</v>
       </c>
       <c r="H46">
-        <v>0.8461538461538461</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="I46">
-        <v>-0.03846153846153855</v>
+        <v>-3.8461538461538547E-2</v>
       </c>
       <c r="J46">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K46">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>0.7774122807017543</v>
+        <v>0.77741228070175428</v>
       </c>
       <c r="N46">
-        <v>0.7214912280701754</v>
+        <v>0.72149122807017541</v>
       </c>
       <c r="O46">
-        <v>0.05592105263157887</v>
+        <v>5.5921052631578871E-2</v>
       </c>
       <c r="P46">
         <v>0.75</v>
@@ -3733,217 +3872,193 @@
         <v>0.74</v>
       </c>
       <c r="R46">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+      <c r="S46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46" t="s">
+        <v>27</v>
       </c>
       <c r="U46" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LTR1502_2019</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LTR1502</t>
-        </is>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
       </c>
       <c r="C47">
         <v>2019</v>
       </c>
       <c r="D47">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E47">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H47">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K47">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L47">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M47">
-        <v>0.6867283950617283</v>
+        <v>0.68672839506172834</v>
       </c>
       <c r="N47">
-        <v>0.6327160493827161</v>
+        <v>0.63271604938271608</v>
       </c>
       <c r="O47">
-        <v>0.05401234567901225</v>
+        <v>5.4012345679012252E-2</v>
       </c>
       <c r="P47">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Q47">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="R47">
-        <v>0.009999999999999898</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>9.9999999999998979E-3</v>
+      </c>
+      <c r="S47" t="s">
+        <v>23</v>
+      </c>
+      <c r="T47" t="s">
+        <v>23</v>
       </c>
       <c r="U47" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LTR337_2019</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+    <row r="48" spans="1:21">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>87</v>
       </c>
       <c r="C48">
         <v>2019</v>
       </c>
       <c r="D48">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E48">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.6590909090909091</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H48">
-        <v>0.6590909090909091</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K48">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L48">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M48">
         <v>0.6812339331619538</v>
       </c>
       <c r="N48">
-        <v>0.6411082474226804</v>
+        <v>0.64110824742268036</v>
       </c>
       <c r="O48">
-        <v>0.04012568573927344</v>
+        <v>4.0125685739273442E-2</v>
       </c>
       <c r="P48">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Q48">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="R48">
-        <v>0.009999999999999898</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>9.9999999999998979E-3</v>
+      </c>
+      <c r="S48" t="s">
+        <v>23</v>
+      </c>
+      <c r="T48" t="s">
+        <v>23</v>
       </c>
       <c r="U48" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LTR1063_2017</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LTR1063</t>
-        </is>
+    <row r="49" spans="1:21">
+      <c r="A49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
       </c>
       <c r="C49">
         <v>2017</v>
       </c>
       <c r="D49">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E49">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.4166666666666667</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H49">
-        <v>0.4166666666666667</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K49">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0.6305661577608143</v>
+        <v>0.63056615776081426</v>
       </c>
       <c r="N49">
-        <v>0.6242048346055979</v>
+        <v>0.62420483460559795</v>
       </c>
       <c r="O49">
-        <v>0.006361323155216314</v>
+        <v>6.3613231552163141E-3</v>
       </c>
       <c r="P49">
         <v>0.36</v>
@@ -3954,30 +4069,22 @@
       <c r="R49">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+      <c r="T49" t="s">
+        <v>24</v>
       </c>
       <c r="U49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LTR1299_2015</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LTR1299</t>
-        </is>
+    <row r="50" spans="1:21">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
       </c>
       <c r="C50">
         <v>2015</v>
@@ -3992,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.9782608695652174</v>
+        <v>0.97826086956521741</v>
       </c>
       <c r="H50">
         <v>1.007246376811594</v>
       </c>
       <c r="I50">
-        <v>-0.02898550724637661</v>
+        <v>-2.8985507246376611E-2</v>
       </c>
       <c r="J50">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K50">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>0.79053480475382</v>
+        <v>0.79053480475381999</v>
       </c>
       <c r="N50">
-        <v>0.79053480475382</v>
+        <v>0.79053480475381999</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -4027,51 +4134,43 @@
       <c r="R50">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S50" t="s">
+        <v>39</v>
+      </c>
+      <c r="T50" t="s">
+        <v>39</v>
       </c>
       <c r="U50" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LTR1299_2019</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LTR1299</t>
-        </is>
+    <row r="51" spans="1:21">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
       </c>
       <c r="C51">
         <v>2019</v>
       </c>
       <c r="D51">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E51">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.9242424242424243</v>
+        <v>0.92424242424242431</v>
       </c>
       <c r="H51">
-        <v>0.9318181818181818</v>
+        <v>0.93181818181818177</v>
       </c>
       <c r="I51">
-        <v>-0.007575757575757458</v>
+        <v>-7.575757575757458E-3</v>
       </c>
       <c r="J51">
         <v>0.8</v>
@@ -4083,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0.7226138828633406</v>
+        <v>0.72261388286334061</v>
       </c>
       <c r="N51">
         <v>0.7226138828633405</v>
@@ -4100,30 +4199,22 @@
       <c r="R51">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S51" t="s">
+        <v>39</v>
+      </c>
+      <c r="T51" t="s">
+        <v>39</v>
       </c>
       <c r="U51" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LTR1299_2022</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LTR1299</t>
-        </is>
+    <row r="52" spans="1:21">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>97</v>
       </c>
       <c r="C52">
         <v>2022</v>
@@ -4138,31 +4229,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0.9074074074074074</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="H52">
-        <v>0.9259259259259259</v>
+        <v>0.92592592592592593</v>
       </c>
       <c r="I52">
-        <v>-0.01851851851851849</v>
+        <v>-1.851851851851849E-2</v>
       </c>
       <c r="J52">
-        <v>1.266666666666667</v>
+        <v>1.2666666666666671</v>
       </c>
       <c r="K52">
         <v>1.2</v>
       </c>
       <c r="L52">
-        <v>0.06666666666666665</v>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="M52">
-        <v>0.9577287946428572</v>
+        <v>0.95772879464285721</v>
       </c>
       <c r="N52">
         <v>0.9556361607142857</v>
       </c>
       <c r="O52">
-        <v>0.002092633928571508</v>
+        <v>2.0926339285715079E-3</v>
       </c>
       <c r="P52">
         <v>1</v>
@@ -4173,30 +4264,22 @@
       <c r="R52">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S52" t="s">
+        <v>39</v>
+      </c>
+      <c r="T52" t="s">
+        <v>39</v>
       </c>
       <c r="U52" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LTR1320_2016</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LTR1320</t>
-        </is>
+    <row r="53" spans="1:21">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
       </c>
       <c r="C53">
         <v>2016</v>
@@ -4211,13 +4294,13 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0.9464285714285715</v>
+        <v>0.94642857142857151</v>
       </c>
       <c r="H53">
         <v>0.9642857142857143</v>
       </c>
       <c r="I53">
-        <v>-0.01785714285714279</v>
+        <v>-1.785714285714279E-2</v>
       </c>
       <c r="J53">
         <v>1.533333333333333</v>
@@ -4229,10 +4312,10 @@
         <v>0.1333333333333335</v>
       </c>
       <c r="M53">
-        <v>0.8657495256166983</v>
+        <v>0.86574952561669827</v>
       </c>
       <c r="N53">
-        <v>0.8657495256166983</v>
+        <v>0.86574952561669827</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -4246,66 +4329,58 @@
       <c r="R53">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S53" t="s">
+        <v>39</v>
+      </c>
+      <c r="T53" t="s">
+        <v>39</v>
       </c>
       <c r="U53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>LTR1320_2019</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LTR1320</t>
-        </is>
+    <row r="54" spans="1:21">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
       </c>
       <c r="C54">
         <v>2019</v>
       </c>
       <c r="D54">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E54">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0.8571428571428572</v>
+        <v>0.85714285714285721</v>
       </c>
       <c r="H54">
-        <v>0.8560606060606061</v>
+        <v>0.85606060606060608</v>
       </c>
       <c r="I54">
-        <v>0.001082251082251129</v>
+        <v>1.0822510822511291E-3</v>
       </c>
       <c r="J54">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K54">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <v>0.6916199158485272</v>
+        <v>0.69161991584852722</v>
       </c>
       <c r="N54">
-        <v>0.6916199158485273</v>
+        <v>0.69161991584852733</v>
       </c>
       <c r="O54">
         <v>-1.110223024625157E-16</v>
@@ -4319,30 +4394,22 @@
       <c r="R54">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S54" t="s">
+        <v>27</v>
+      </c>
+      <c r="T54" t="s">
+        <v>27</v>
       </c>
       <c r="U54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LTR1320_2022</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LTR1320</t>
-        </is>
+    <row r="55" spans="1:21">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>101</v>
       </c>
       <c r="C55">
         <v>2022</v>
@@ -4357,31 +4424,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.9482758620689654</v>
+        <v>0.94827586206896541</v>
       </c>
       <c r="H55">
-        <v>0.9655172413793104</v>
+        <v>0.96551724137931039</v>
       </c>
       <c r="I55">
-        <v>-0.01724137931034497</v>
+        <v>-1.724137931034497E-2</v>
       </c>
       <c r="J55">
-        <v>1.066666666666667</v>
+        <v>1.0666666666666671</v>
       </c>
       <c r="K55">
-        <v>1.066666666666667</v>
+        <v>1.0666666666666671</v>
       </c>
       <c r="L55">
-        <v>-4.440892098500626E-16</v>
+        <v>-4.4408920985006262E-16</v>
       </c>
       <c r="M55">
         <v>0.9419642857142857</v>
       </c>
       <c r="N55">
-        <v>0.9433285509325681</v>
+        <v>0.94332855093256807</v>
       </c>
       <c r="O55">
-        <v>-0.001364265218282368</v>
+        <v>-1.364265218282368E-3</v>
       </c>
       <c r="P55">
         <v>0.99</v>
@@ -4392,30 +4459,22 @@
       <c r="R55">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S55" t="s">
+        <v>39</v>
+      </c>
+      <c r="T55" t="s">
+        <v>39</v>
       </c>
       <c r="U55" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LTR1379_2015</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LTR1379</t>
-        </is>
+    <row r="56" spans="1:21">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
       </c>
       <c r="C56">
         <v>2015</v>
@@ -4430,31 +4489,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.9545454545454546</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="H56">
-        <v>0.9696969696969697</v>
+        <v>0.96969696969696972</v>
       </c>
       <c r="I56">
-        <v>-0.01515151515151514</v>
+        <v>-1.515151515151514E-2</v>
       </c>
       <c r="J56">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K56">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0.782323883161512</v>
+        <v>0.78232388316151202</v>
       </c>
       <c r="N56">
-        <v>0.781786941580756</v>
+        <v>0.78178694158075601</v>
       </c>
       <c r="O56">
-        <v>0.0005369415807560118</v>
+        <v>5.3694158075601184E-4</v>
       </c>
       <c r="P56">
         <v>0.92</v>
@@ -4465,48 +4524,40 @@
       <c r="R56">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S56" t="s">
+        <v>39</v>
+      </c>
+      <c r="T56" t="s">
+        <v>39</v>
       </c>
       <c r="U56" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LTR1379_2019</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LTR1379</t>
-        </is>
+    <row r="57" spans="1:21">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
       </c>
       <c r="C57">
         <v>2019</v>
       </c>
       <c r="D57">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E57">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0.8623188405797101</v>
+        <v>0.86231884057971009</v>
       </c>
       <c r="H57">
-        <v>0.8623188405797101</v>
+        <v>0.86231884057971009</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -4521,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>0.7549055232558139</v>
+        <v>0.75490552325581395</v>
       </c>
       <c r="N57">
-        <v>0.7549055232558139</v>
+        <v>0.75490552325581395</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -4538,48 +4589,40 @@
       <c r="R57">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S57" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" t="s">
+        <v>27</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LTR1379_2022</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LTR1379</t>
-        </is>
+    <row r="58" spans="1:21">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>105</v>
       </c>
       <c r="C58">
         <v>2022</v>
       </c>
       <c r="D58">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E58">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0.8064516129032259</v>
+        <v>0.80645161290322587</v>
       </c>
       <c r="H58">
-        <v>0.8064516129032259</v>
+        <v>0.80645161290322587</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4594,13 +4637,13 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>0.6558675699300699</v>
+        <v>0.65586756993006989</v>
       </c>
       <c r="N58">
-        <v>0.6456043956043956</v>
+        <v>0.64560439560439564</v>
       </c>
       <c r="O58">
-        <v>0.01026317432567425</v>
+        <v>1.026317432567425E-2</v>
       </c>
       <c r="P58">
         <v>0.79</v>
@@ -4611,48 +4654,40 @@
       <c r="R58">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S58" t="s">
+        <v>27</v>
+      </c>
+      <c r="T58" t="s">
+        <v>27</v>
       </c>
       <c r="U58" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LTR1385_2016</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>LTR1385</t>
-        </is>
+    <row r="59" spans="1:21">
+      <c r="A59" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
       </c>
       <c r="C59">
         <v>2016</v>
       </c>
       <c r="D59">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E59">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0.9722222222222222</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="H59">
-        <v>0.9722222222222222</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4667,65 +4702,57 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>0.8421814671814671</v>
+        <v>0.84218146718146714</v>
       </c>
       <c r="N59">
-        <v>0.8421814671814671</v>
+        <v>0.84218146718146714</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="Q59">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="R59">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S59" t="s">
+        <v>39</v>
+      </c>
+      <c r="T59" t="s">
+        <v>39</v>
       </c>
       <c r="U59" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>LTR1385_2019</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>LTR1385</t>
-        </is>
+    <row r="60" spans="1:21">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
       </c>
       <c r="C60">
         <v>2019</v>
       </c>
       <c r="D60">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E60">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.6833333333333332</v>
+        <v>0.68333333333333324</v>
       </c>
       <c r="H60">
-        <v>0.6833333333333332</v>
+        <v>0.68333333333333324</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4740,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0.7584212662337662</v>
+        <v>0.75842126623376616</v>
       </c>
       <c r="N60">
-        <v>0.7584212662337662</v>
+        <v>0.75842126623376616</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -4757,48 +4784,40 @@
       <c r="R60">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S60" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" t="s">
+        <v>27</v>
       </c>
       <c r="U60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>LTR1385_2022</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>LTR1385</t>
-        </is>
+    <row r="61" spans="1:21">
+      <c r="A61" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
       </c>
       <c r="C61">
         <v>2022</v>
       </c>
       <c r="D61">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E61">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.8174603174603176</v>
+        <v>0.81746031746031755</v>
       </c>
       <c r="H61">
-        <v>0.8174603174603176</v>
+        <v>0.81746031746031755</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4813,13 +4832,13 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>0.9122670807453416</v>
+        <v>0.91226708074534157</v>
       </c>
       <c r="N61">
-        <v>0.9130094043887146</v>
+        <v>0.91300940438871458</v>
       </c>
       <c r="O61">
-        <v>-0.0007423236433730107</v>
+        <v>-7.4232364337301071E-4</v>
       </c>
       <c r="P61">
         <v>0.75</v>
@@ -4830,30 +4849,22 @@
       <c r="R61">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S61" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" t="s">
+        <v>27</v>
       </c>
       <c r="U61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>LTR1447_2019</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>LTR1447</t>
-        </is>
+    <row r="62" spans="1:21">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" t="s">
+        <v>48</v>
       </c>
       <c r="C62">
         <v>2019</v>
@@ -4868,138 +4879,122 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>0.7361111111111112</v>
+        <v>0.73611111111111116</v>
       </c>
       <c r="H62">
-        <v>0.7361111111111112</v>
+        <v>0.73611111111111116</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K62">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L62">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M62">
-        <v>0.7019519519519519</v>
+        <v>0.70195195195195192</v>
       </c>
       <c r="N62">
-        <v>0.7019519519519519</v>
+        <v>0.70195195195195192</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Q62">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R62">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S62" t="s">
+        <v>23</v>
+      </c>
+      <c r="T62" t="s">
+        <v>23</v>
       </c>
       <c r="U62" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>LTR1449_2019</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>LTR1449</t>
-        </is>
+    <row r="63" spans="1:21">
+      <c r="A63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" t="s">
+        <v>78</v>
       </c>
       <c r="C63">
         <v>2019</v>
       </c>
       <c r="D63">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E63">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>0.8409090909090909</v>
+        <v>0.84090909090909094</v>
       </c>
       <c r="H63">
-        <v>0.8478260869565218</v>
+        <v>0.84782608695652184</v>
       </c>
       <c r="I63">
-        <v>-0.006916996047430901</v>
+        <v>-6.9169960474309011E-3</v>
       </c>
       <c r="J63">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K63">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <v>0.7537553648068669</v>
+        <v>0.75375536480686689</v>
       </c>
       <c r="N63">
-        <v>0.7539398280802292</v>
+        <v>0.75393982808022919</v>
       </c>
       <c r="O63">
-        <v>-0.0001844632733623008</v>
+        <v>-1.8446327336230081E-4</v>
       </c>
       <c r="P63">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="Q63">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="R63">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S63" t="s">
+        <v>27</v>
+      </c>
+      <c r="T63" t="s">
+        <v>27</v>
       </c>
       <c r="U63" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>LTR1449_2022</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>LTR1449</t>
-        </is>
+    <row r="64" spans="1:21">
+      <c r="A64" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" t="s">
+        <v>78</v>
       </c>
       <c r="C64">
         <v>2022</v>
@@ -5014,28 +5009,28 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.9080459770114943</v>
+        <v>0.90804597701149425</v>
       </c>
       <c r="H64">
         <v>0.9137931034482758</v>
       </c>
       <c r="I64">
-        <v>-0.005747126436781547</v>
+        <v>-5.7471264367815467E-3</v>
       </c>
       <c r="J64">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K64">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
-        <v>0.8074199507389163</v>
+        <v>0.80741995073891626</v>
       </c>
       <c r="N64">
-        <v>0.8074199507389163</v>
+        <v>0.80741995073891626</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -5049,30 +5044,22 @@
       <c r="R64">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S64" t="s">
+        <v>39</v>
+      </c>
+      <c r="T64" t="s">
+        <v>39</v>
       </c>
       <c r="U64" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>LTR1501_2019</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>LTR1501</t>
-        </is>
+    <row r="65" spans="1:21">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" t="s">
+        <v>83</v>
       </c>
       <c r="C65">
         <v>2019</v>
@@ -5087,31 +5074,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>0.7115384615384616</v>
+        <v>0.71153846153846156</v>
       </c>
       <c r="H65">
-        <v>0.7037037037037037</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="I65">
-        <v>0.007834757834757844</v>
+        <v>7.8347578347578439E-3</v>
       </c>
       <c r="J65">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="K65">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="L65">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="M65">
-        <v>0.6457838479809975</v>
+        <v>0.64578384798099753</v>
       </c>
       <c r="N65">
-        <v>0.6368764845605701</v>
+        <v>0.63687648456057011</v>
       </c>
       <c r="O65">
-        <v>0.008907363420427417</v>
+        <v>8.9073634204274166E-3</v>
       </c>
       <c r="P65">
         <v>0.53</v>
@@ -5122,30 +5109,22 @@
       <c r="R65">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S65" t="s">
+        <v>23</v>
+      </c>
+      <c r="T65" t="s">
+        <v>23</v>
       </c>
       <c r="U65" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>LTR1501_2022</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>LTR1501</t>
-        </is>
+    <row r="66" spans="1:21">
+      <c r="A66" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" t="s">
+        <v>83</v>
       </c>
       <c r="C66">
         <v>2022</v>
@@ -5160,10 +5139,10 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>0.7037037037037037</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="H66">
-        <v>0.7037037037037037</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5181,10 +5160,10 @@
         <v>0.7540137614678899</v>
       </c>
       <c r="N66">
-        <v>0.7396788990825688</v>
+        <v>0.73967889908256879</v>
       </c>
       <c r="O66">
-        <v>0.01433486238532111</v>
+        <v>1.433486238532111E-2</v>
       </c>
       <c r="P66">
         <v>0.52</v>
@@ -5195,69 +5174,61 @@
       <c r="R66">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S66" t="s">
+        <v>23</v>
+      </c>
+      <c r="T66" t="s">
+        <v>23</v>
       </c>
       <c r="U66" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>LTR1502_2022</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>LTR1502</t>
-        </is>
+    <row r="67" spans="1:21">
+      <c r="A67" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
       </c>
       <c r="C67">
         <v>2022</v>
       </c>
       <c r="D67">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E67">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0.7901234567901234</v>
+        <v>0.79012345679012341</v>
       </c>
       <c r="H67">
-        <v>0.808641975308642</v>
+        <v>0.80864197530864201</v>
       </c>
       <c r="I67">
-        <v>-0.0185185185185186</v>
+        <v>-1.8518518518518601E-2</v>
       </c>
       <c r="J67">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K67">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <v>0.7647280966767372</v>
+        <v>0.76472809667673725</v>
       </c>
       <c r="N67">
-        <v>0.740530303030303</v>
+        <v>0.74053030303030298</v>
       </c>
       <c r="O67">
-        <v>0.02419779364643426</v>
+        <v>2.4197793646434259E-2</v>
       </c>
       <c r="P67">
         <v>0.67</v>
@@ -5268,30 +5239,22 @@
       <c r="R67">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S67" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" t="s">
+        <v>27</v>
       </c>
       <c r="U67" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>LTR1601_2021</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>LTR1601</t>
-        </is>
+    <row r="68" spans="1:21">
+      <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
+        <v>119</v>
       </c>
       <c r="C68">
         <v>2021</v>
@@ -5306,19 +5269,19 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H68">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K68">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -5327,7 +5290,7 @@
         <v>0.5316091954022989</v>
       </c>
       <c r="N68">
-        <v>0.5316091954022988</v>
+        <v>0.53160919540229878</v>
       </c>
       <c r="O68">
         <v>1.110223024625157E-16</v>
@@ -5341,30 +5304,22 @@
       <c r="R68">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Bad</t>
-        </is>
+      <c r="S68" t="s">
+        <v>33</v>
+      </c>
+      <c r="T68" t="s">
+        <v>33</v>
       </c>
       <c r="U68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>LTR232_2015</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>LTR232</t>
-        </is>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" t="s">
+        <v>121</v>
       </c>
       <c r="C69">
         <v>2015</v>
@@ -5379,28 +5334,28 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>0.9019607843137255</v>
+        <v>0.90196078431372551</v>
       </c>
       <c r="H69">
-        <v>0.9166666666666666</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="I69">
-        <v>-0.01470588235294112</v>
+        <v>-1.4705882352941121E-2</v>
       </c>
       <c r="J69">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K69">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0.6944444444444444</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="N69">
-        <v>0.6944444444444444</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -5414,66 +5369,58 @@
       <c r="R69">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="S69" t="s">
+        <v>39</v>
+      </c>
+      <c r="T69" t="s">
+        <v>39</v>
       </c>
       <c r="U69" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>LTR232_2019</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>LTR232</t>
-        </is>
+    <row r="70" spans="1:21">
+      <c r="A70" t="s">
+        <v>122</v>
+      </c>
+      <c r="B70" t="s">
+        <v>121</v>
       </c>
       <c r="C70">
         <v>2019</v>
       </c>
       <c r="D70">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E70">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>0.7716049382716049</v>
+        <v>0.77160493827160492</v>
       </c>
       <c r="H70">
-        <v>0.7716049382716049</v>
+        <v>0.77160493827160492</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K70">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0.6162891986062717</v>
+        <v>0.61628919860627174</v>
       </c>
       <c r="N70">
-        <v>0.6162891986062717</v>
+        <v>0.61628919860627174</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -5487,30 +5434,22 @@
       <c r="R70">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S70" t="s">
+        <v>27</v>
+      </c>
+      <c r="T70" t="s">
+        <v>27</v>
       </c>
       <c r="U70" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>LTR232_2022</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>LTR232</t>
-        </is>
+    <row r="71" spans="1:21">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>121</v>
       </c>
       <c r="C71">
         <v>2022</v>
@@ -5525,19 +5464,19 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>0.7156862745098039</v>
+        <v>0.71568627450980393</v>
       </c>
       <c r="H71">
-        <v>0.7156862745098039</v>
+        <v>0.71568627450980393</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
       <c r="J71">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="K71">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -5546,10 +5485,10 @@
         <v>0.6875</v>
       </c>
       <c r="N71">
-        <v>0.6636904761904762</v>
+        <v>0.66369047619047616</v>
       </c>
       <c r="O71">
-        <v>0.02380952380952384</v>
+        <v>2.3809523809523839E-2</v>
       </c>
       <c r="P71">
         <v>0.59</v>
@@ -5560,42 +5499,34 @@
       <c r="R71">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S71" t="s">
+        <v>23</v>
+      </c>
+      <c r="T71" t="s">
+        <v>23</v>
       </c>
       <c r="U71" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>LTR308_2021</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>LTR308</t>
-        </is>
+    <row r="72" spans="1:21">
+      <c r="A72" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
       </c>
       <c r="C72">
         <v>2021</v>
       </c>
       <c r="D72">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E72">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F72">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G72">
         <v>0.25</v>
@@ -5616,10 +5547,10 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>0.631533101045296</v>
+        <v>0.63153310104529603</v>
       </c>
       <c r="N72">
-        <v>0.631533101045296</v>
+        <v>0.63153310104529603</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5633,30 +5564,22 @@
       <c r="R72">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S72" t="s">
+        <v>24</v>
+      </c>
+      <c r="T72" t="s">
+        <v>24</v>
       </c>
       <c r="U72" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>LTR351_2015</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>LTR351</t>
-        </is>
+    <row r="73" spans="1:21">
+      <c r="A73" t="s">
+        <v>125</v>
+      </c>
+      <c r="B73" t="s">
+        <v>90</v>
       </c>
       <c r="C73">
         <v>2015</v>
@@ -5671,13 +5594,13 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>0.7011494252873564</v>
+        <v>0.70114942528735635</v>
       </c>
       <c r="H73">
         <v>0.7055555555555556</v>
       </c>
       <c r="I73">
-        <v>-0.004406130268199249</v>
+        <v>-4.4061302681992487E-3</v>
       </c>
       <c r="J73">
         <v>0.4</v>
@@ -5689,13 +5612,13 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0.7475023786869647</v>
+        <v>0.74750237868696467</v>
       </c>
       <c r="N73">
-        <v>0.7457183634633682</v>
+        <v>0.74571836346336817</v>
       </c>
       <c r="O73">
-        <v>0.001784015223596502</v>
+        <v>1.7840152235965019E-3</v>
       </c>
       <c r="P73">
         <v>0.59</v>
@@ -5706,48 +5629,40 @@
       <c r="R73">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S73" t="s">
+        <v>23</v>
+      </c>
+      <c r="T73" t="s">
+        <v>23</v>
       </c>
       <c r="U73" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>LTR351_2022</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>LTR351</t>
-        </is>
+    <row r="74" spans="1:21">
+      <c r="A74" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" t="s">
+        <v>90</v>
       </c>
       <c r="C74">
         <v>2022</v>
       </c>
       <c r="D74">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E74">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>0.8154761904761906</v>
+        <v>0.81547619047619058</v>
       </c>
       <c r="H74">
-        <v>0.8154761904761906</v>
+        <v>0.81547619047619058</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5762,13 +5677,13 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0.7749999999999999</v>
+        <v>0.77499999999999991</v>
       </c>
       <c r="N74">
-        <v>0.7419692737430167</v>
+        <v>0.74196927374301669</v>
       </c>
       <c r="O74">
-        <v>0.03303072625698322</v>
+        <v>3.3030726256983223E-2</v>
       </c>
       <c r="P74">
         <v>0.71</v>
@@ -5779,51 +5694,43 @@
       <c r="R74">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S74" t="s">
+        <v>27</v>
+      </c>
+      <c r="T74" t="s">
+        <v>27</v>
       </c>
       <c r="U74" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>LTR411_2015</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>LTR411</t>
-        </is>
+    <row r="75" spans="1:21">
+      <c r="A75" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s">
+        <v>92</v>
       </c>
       <c r="C75">
         <v>2015</v>
       </c>
       <c r="D75">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E75">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0.7701149425287356</v>
+        <v>0.77011494252873558</v>
       </c>
       <c r="H75">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="I75">
-        <v>-0.00766283524904221</v>
+        <v>-7.6628352490422103E-3</v>
       </c>
       <c r="J75">
         <v>0.2</v>
@@ -5835,83 +5742,75 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0.6576236263736264</v>
+        <v>0.65762362637362637</v>
       </c>
       <c r="N75">
-        <v>0.623282967032967</v>
+        <v>0.62328296703296704</v>
       </c>
       <c r="O75">
-        <v>0.03434065934065933</v>
+        <v>3.434065934065933E-2</v>
       </c>
       <c r="P75">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Q75">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="R75">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S75" t="s">
+        <v>23</v>
+      </c>
+      <c r="T75" t="s">
+        <v>23</v>
       </c>
       <c r="U75" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>LTR411_2019</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>LTR411</t>
-        </is>
+    <row r="76" spans="1:21">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" t="s">
+        <v>92</v>
       </c>
       <c r="C76">
         <v>2019</v>
       </c>
       <c r="D76">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E76">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0.8253968253968255</v>
+        <v>0.82539682539682546</v>
       </c>
       <c r="H76">
-        <v>0.8257575757575757</v>
+        <v>0.82575757575757569</v>
       </c>
       <c r="I76">
-        <v>-0.0003607503607502283</v>
+        <v>-3.6075036075022831E-4</v>
       </c>
       <c r="J76">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K76">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76">
-        <v>0.7379201680672268</v>
+        <v>0.73792016806722682</v>
       </c>
       <c r="N76">
-        <v>0.7379201680672268</v>
+        <v>0.73792016806722682</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -5925,69 +5824,61 @@
       <c r="R76">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S76" t="s">
+        <v>27</v>
+      </c>
+      <c r="T76" t="s">
+        <v>27</v>
       </c>
       <c r="U76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>LTR625_2015</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LTR625</t>
-        </is>
+    <row r="77" spans="1:21">
+      <c r="A77" t="s">
+        <v>129</v>
+      </c>
+      <c r="B77" t="s">
+        <v>42</v>
       </c>
       <c r="C77">
         <v>2015</v>
       </c>
       <c r="D77">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E77">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0.5833333333333334</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H77">
-        <v>0.576923076923077</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="I77">
-        <v>0.006410256410256387</v>
+        <v>6.4102564102563866E-3</v>
       </c>
       <c r="J77">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K77">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77">
-        <v>0.6361607142857142</v>
+        <v>0.63616071428571419</v>
       </c>
       <c r="N77">
-        <v>0.6310679611650485</v>
+        <v>0.63106796116504849</v>
       </c>
       <c r="O77">
-        <v>0.005092753120665705</v>
+        <v>5.0927531206657051E-3</v>
       </c>
       <c r="P77">
         <v>0.4</v>
@@ -5998,51 +5889,43 @@
       <c r="R77">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S77" t="s">
+        <v>23</v>
+      </c>
+      <c r="T77" t="s">
+        <v>23</v>
       </c>
       <c r="U77" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>LTR625_2019</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LTR625</t>
-        </is>
+    <row r="78" spans="1:21">
+      <c r="A78" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" t="s">
+        <v>42</v>
       </c>
       <c r="C78">
         <v>2019</v>
       </c>
       <c r="D78">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E78">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H78">
-        <v>0.8387096774193549</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="I78">
-        <v>-0.005376344086021501</v>
+        <v>-5.3763440860215006E-3</v>
       </c>
       <c r="J78">
         <v>0.4</v>
@@ -6054,47 +5937,39 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>0.7126168224299064</v>
+        <v>0.71261682242990643</v>
       </c>
       <c r="N78">
-        <v>0.7005962521294719</v>
+        <v>0.70059625212947185</v>
       </c>
       <c r="O78">
-        <v>0.01202057030043457</v>
+        <v>1.2020570300434571E-2</v>
       </c>
       <c r="P78">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="Q78">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="R78">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="S78" t="s">
+        <v>27</v>
+      </c>
+      <c r="T78" t="s">
+        <v>27</v>
       </c>
       <c r="U78" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>LTR627_2015</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>LTR627</t>
-        </is>
+    <row r="79" spans="1:21">
+      <c r="A79" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" t="s">
+        <v>132</v>
       </c>
       <c r="C79">
         <v>2015</v>
@@ -6109,10 +5984,10 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="H79">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -6127,56 +6002,48 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>0.5917553191489361</v>
+        <v>0.59175531914893609</v>
       </c>
       <c r="N79">
-        <v>0.5913978494623656</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="O79">
-        <v>0.0003574696865704663</v>
+        <v>3.5746968657046629E-4</v>
       </c>
       <c r="P79">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q79">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R79">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Bad</t>
-        </is>
+      <c r="S79" t="s">
+        <v>33</v>
+      </c>
+      <c r="T79" t="s">
+        <v>33</v>
       </c>
       <c r="U79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>LTR706_2018</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>LTR706</t>
-        </is>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B80" t="s">
+        <v>70</v>
       </c>
       <c r="C80">
         <v>2018</v>
       </c>
       <c r="D80">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E80">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -6200,10 +6067,10 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M80">
-        <v>0.7437499999999999</v>
+        <v>0.74374999999999991</v>
       </c>
       <c r="N80">
-        <v>0.7437499999999999</v>
+        <v>0.74374999999999991</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -6217,42 +6084,34 @@
       <c r="R80">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="S80" t="s">
+        <v>23</v>
+      </c>
+      <c r="T80" t="s">
+        <v>23</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>LTR706_2021</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LTR706</t>
-        </is>
+    <row r="81" spans="1:21">
+      <c r="A81" t="s">
+        <v>134</v>
+      </c>
+      <c r="B81" t="s">
+        <v>70</v>
       </c>
       <c r="C81">
         <v>2021</v>
       </c>
       <c r="D81">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E81">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F81">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G81">
         <v>0.5</v>
@@ -6273,13 +6132,13 @@
         <v>0</v>
       </c>
       <c r="M81">
-        <v>0.6625</v>
+        <v>0.66249999999999998</v>
       </c>
       <c r="N81">
-        <v>0.6632653061224489</v>
+        <v>0.66326530612244894</v>
       </c>
       <c r="O81">
-        <v>-0.000765306122448961</v>
+        <v>-7.6530612244896101E-4</v>
       </c>
       <c r="P81">
         <v>0.38</v>
@@ -6290,42 +6149,34 @@
       <c r="R81">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S81" t="s">
+        <v>24</v>
+      </c>
+      <c r="T81" t="s">
+        <v>24</v>
       </c>
       <c r="U81" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>LTR86_2017</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+    <row r="82" spans="1:21">
+      <c r="A82" t="s">
+        <v>135</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
       </c>
       <c r="C82">
         <v>2017</v>
       </c>
       <c r="D82">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E82">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F82">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G82">
         <v>0.5</v>
@@ -6337,19 +6188,19 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K82">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82">
-        <v>0.7979910714285715</v>
+        <v>0.79799107142857151</v>
       </c>
       <c r="N82">
-        <v>0.7979910714285715</v>
+        <v>0.79799107142857151</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -6363,48 +6214,40 @@
       <c r="R82">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S82" t="s">
+        <v>24</v>
+      </c>
+      <c r="T82" t="s">
+        <v>24</v>
       </c>
       <c r="U82" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>LTR86_2020</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+    <row r="83" spans="1:21">
+      <c r="A83" t="s">
+        <v>136</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
       </c>
       <c r="C83">
         <v>2020</v>
       </c>
       <c r="D83">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="E83">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="F83">
-        <v>-5.551115123125783E-17</v>
+        <v>-5.5511151231257827E-17</v>
       </c>
       <c r="G83">
         <v>0.4861111111111111</v>
       </c>
       <c r="H83">
-        <v>0.4861111111111112</v>
+        <v>0.48611111111111122</v>
       </c>
       <c r="I83">
         <v>-1.110223024625157E-16</v>
@@ -6419,13 +6262,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M83">
-        <v>0.6452429149797571</v>
+        <v>0.64524291497975705</v>
       </c>
       <c r="N83">
-        <v>0.6453665987780041</v>
+        <v>0.64536659877800406</v>
       </c>
       <c r="O83">
-        <v>-0.0001236837982470096</v>
+        <v>-1.2368379824700959E-4</v>
       </c>
       <c r="P83">
         <v>0.36</v>
@@ -6436,15 +6279,11 @@
       <c r="R83">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="S83" t="s">
+        <v>24</v>
+      </c>
+      <c r="T83" t="s">
+        <v>24</v>
       </c>
       <c r="U83" t="b">
         <v>1</v>
@@ -6456,187 +6295,161 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mean_residual</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>median_residual</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_abs_res</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>pearson_r</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pearson_p</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pct_exact</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>145</v>
       </c>
       <c r="B2">
         <v>82</v>
       </c>
       <c r="C2">
-        <v>-0.008130081300813016</v>
+        <v>-8.1300813008130159E-3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.01626016260162602</v>
+        <v>1.6260162601626021E-2</v>
       </c>
       <c r="F2">
-        <v>0.9805716706551791</v>
+        <v>0.98057167065517914</v>
       </c>
       <c r="G2">
-        <v>2.324811138368751E-58</v>
+        <v>2.3248111383687509E-58</v>
       </c>
       <c r="H2">
-        <v>90.2439024390244</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>90.243902439024396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>146</v>
       </c>
       <c r="B3">
         <v>82</v>
       </c>
       <c r="C3">
-        <v>-0.003034997622772077</v>
+        <v>-3.0349976227720772E-3</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.008000955722806301</v>
+        <v>8.0009557228063015E-3</v>
       </c>
       <c r="F3">
-        <v>0.9948954977090645</v>
+        <v>0.99489549770906449</v>
       </c>
       <c r="G3">
-        <v>1.845644815360817E-81</v>
+        <v>1.8456448153608171E-81</v>
       </c>
       <c r="H3">
-        <v>58.53658536585365</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>58.536585365853647</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>147</v>
       </c>
       <c r="B4">
         <v>82</v>
       </c>
       <c r="C4">
-        <v>0.004878048780487794</v>
+        <v>4.8780487804877936E-3</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.004878048780487825</v>
+        <v>4.8780487804878248E-3</v>
       </c>
       <c r="F4">
-        <v>0.9982745313545018</v>
+        <v>0.99827453135450184</v>
       </c>
       <c r="G4">
-        <v>2.833078589344756E-100</v>
+        <v>2.8330785893447558E-100</v>
       </c>
       <c r="H4">
-        <v>93.90243902439023</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>93.902439024390233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>148</v>
       </c>
       <c r="B5">
         <v>82</v>
       </c>
       <c r="C5">
-        <v>0.06199191185655632</v>
+        <v>6.1991911856556323E-2</v>
       </c>
       <c r="D5">
-        <v>0.02719166629755942</v>
+        <v>2.7191666297559421E-2</v>
       </c>
       <c r="E5">
-        <v>0.06206947385791518</v>
+        <v>6.2069473857915183E-2</v>
       </c>
       <c r="F5">
-        <v>0.7743997728048058</v>
+        <v>0.77439977280480576</v>
       </c>
       <c r="G5">
-        <v>1.419858208644212E-17</v>
+        <v>1.4198582086442121E-17</v>
       </c>
       <c r="H5">
-        <v>35.36585365853659</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EQR</t>
-        </is>
+        <v>35.365853658536587</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>149</v>
       </c>
       <c r="B6">
         <v>82</v>
       </c>
       <c r="C6">
-        <v>0.01402439024390243</v>
+        <v>1.4024390243902431E-2</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.01768292682926829</v>
+        <v>1.7682926829268291E-2</v>
       </c>
       <c r="F6">
-        <v>0.9911315006021287</v>
+        <v>0.99113150060212873</v>
       </c>
       <c r="G6">
-        <v>6.773526914327024E-72</v>
+        <v>6.7735269143270236E-72</v>
       </c>
       <c r="H6">
         <v>42.68292682926829</v>
@@ -6648,350 +6461,110 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LEPA</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2">
+        <v>82</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>21.5</v>
+      </c>
+      <c r="E2">
+        <v>2.856962661506433E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3">
         <v>82</v>
       </c>
-      <c r="D2">
-        <v>0.571</v>
-      </c>
-      <c r="E2">
-        <v>0.261</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OTL</t>
-        </is>
-      </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>283</v>
+      </c>
+      <c r="E3">
+        <v>4.986171585865202E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4">
         <v>82</v>
       </c>
-      <c r="D3">
-        <v>0.579</v>
-      </c>
-      <c r="E3">
-        <v>0.263</v>
-      </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LEPA</t>
-        </is>
-      </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>165</v>
+      </c>
+      <c r="E4">
+        <v>0.67510875834133199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5">
         <v>82</v>
       </c>
-      <c r="D4">
-        <v>0.7</v>
-      </c>
-      <c r="E4">
-        <v>0.172</v>
-      </c>
-      <c r="F4">
-        <v>0.725</v>
-      </c>
-      <c r="G4">
-        <v>0.25</v>
-      </c>
-      <c r="H4">
-        <v>1.074</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OTL</t>
-        </is>
-      </c>
       <c r="C5">
+        <v>2.7191666297559421E-2</v>
+      </c>
+      <c r="D5">
+        <v>2173</v>
+      </c>
+      <c r="E5">
+        <v>9.351120724331913E-12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6">
         <v>82</v>
       </c>
-      <c r="D5">
-        <v>0.703</v>
-      </c>
-      <c r="E5">
-        <v>0.171</v>
-      </c>
-      <c r="F5">
-        <v>0.725</v>
-      </c>
-      <c r="G5">
-        <v>0.25</v>
-      </c>
-      <c r="H5">
-        <v>1.007</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LEPA</t>
-        </is>
-      </c>
       <c r="C6">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.437</v>
+        <v>989</v>
       </c>
       <c r="E6">
-        <v>0.319</v>
-      </c>
-      <c r="F6">
-        <v>0.367</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>1.533</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OTL</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>82</v>
-      </c>
-      <c r="D7">
-        <v>0.433</v>
-      </c>
-      <c r="E7">
-        <v>0.311</v>
-      </c>
-      <c r="F7">
-        <v>0.367</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LEPA</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>82</v>
-      </c>
-      <c r="D8">
-        <v>0.718</v>
-      </c>
-      <c r="E8">
-        <v>0.089</v>
-      </c>
-      <c r="F8">
-        <v>0.703</v>
-      </c>
-      <c r="G8">
-        <v>0.532</v>
-      </c>
-      <c r="H8">
-        <v>1.052</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>OTL</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>82</v>
-      </c>
-      <c r="D9">
-        <v>0.656</v>
-      </c>
-      <c r="E9">
-        <v>0.134</v>
-      </c>
-      <c r="F9">
-        <v>0.657</v>
-      </c>
-      <c r="G9">
-        <v>0.21</v>
-      </c>
-      <c r="H9">
-        <v>1.043</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EQR</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LEPA</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>82</v>
-      </c>
-      <c r="D10">
-        <v>0.605</v>
-      </c>
-      <c r="E10">
-        <v>0.185</v>
-      </c>
-      <c r="F10">
-        <v>0.595</v>
-      </c>
-      <c r="G10">
-        <v>0.23</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EQR</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OTL</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>82</v>
-      </c>
-      <c r="D11">
-        <v>0.591</v>
-      </c>
-      <c r="E11">
-        <v>0.189</v>
-      </c>
-      <c r="F11">
-        <v>0.59</v>
-      </c>
-      <c r="G11">
-        <v>0.23</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
+        <v>6.6033834348955154E-6</v>
       </c>
     </row>
   </sheetData>
@@ -7000,89 +6573,367 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2">
+        <v>82</v>
+      </c>
+      <c r="D2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="E2">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3">
+        <v>82</v>
+      </c>
+      <c r="D3">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="E3">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4">
+        <v>82</v>
+      </c>
+      <c r="D4">
+        <v>0.7</v>
+      </c>
+      <c r="E4">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="G4">
+        <v>0.25</v>
+      </c>
+      <c r="H4">
+        <v>1.0740000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="E5">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="G5">
+        <v>0.25</v>
+      </c>
+      <c r="H5">
+        <v>1.0069999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>82</v>
+      </c>
+      <c r="D6">
+        <v>0.437</v>
+      </c>
+      <c r="E6">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1.5329999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7">
+        <v>82</v>
+      </c>
+      <c r="D7">
+        <v>0.433</v>
+      </c>
+      <c r="E7">
+        <v>0.311</v>
+      </c>
+      <c r="F7">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8">
+        <v>82</v>
+      </c>
+      <c r="D8">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="E8">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="F8">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="G8">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="H8">
+        <v>1.052</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9">
+        <v>82</v>
+      </c>
+      <c r="D9">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="E9">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="G9">
+        <v>0.21</v>
+      </c>
+      <c r="H9">
+        <v>1.0429999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10">
+        <v>82</v>
+      </c>
+      <c r="D10">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="E10">
+        <v>0.185</v>
+      </c>
+      <c r="F10">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="G10">
+        <v>0.23</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11">
+        <v>82</v>
+      </c>
+      <c r="D11">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="E11">
+        <v>0.189</v>
+      </c>
+      <c r="F11">
+        <v>0.59</v>
+      </c>
+      <c r="G11">
+        <v>0.23</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LEPA − LT-OTL (mean)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LEPA − LT-OTL (median)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mean |residual|</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Pearson r</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>% within ±0.005</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>145</v>
       </c>
       <c r="B2">
         <v>82</v>
       </c>
       <c r="C2">
-        <v>-0.0081</v>
+        <v>-8.0999999999999996E-3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.0163</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="F2">
-        <v>0.981</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="G2">
         <v>90.2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>146</v>
       </c>
       <c r="B3">
         <v>82</v>
       </c>
       <c r="C3">
-        <v>-0.003</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F3">
         <v>0.995</v>
@@ -7091,76 +6942,70 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>147</v>
       </c>
       <c r="B4">
         <v>82</v>
       </c>
       <c r="C4">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="F4">
         <v>0.998</v>
       </c>
       <c r="G4">
-        <v>93.90000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>93.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>148</v>
       </c>
       <c r="B5">
         <v>82</v>
       </c>
       <c r="C5">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="D5">
-        <v>0.0272</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="E5">
-        <v>0.0621</v>
+        <v>6.2100000000000002E-2</v>
       </c>
       <c r="F5">
-        <v>0.774</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="G5">
         <v>35.4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EQR</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>149</v>
       </c>
       <c r="B6">
         <v>82</v>
       </c>
       <c r="C6">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.0177</v>
+        <v>1.77E-2</v>
       </c>
       <c r="F6">
-        <v>0.991</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="G6">
         <v>42.7</v>

--- a/Outputs/10_lepa_per_metric_comparison.xlsx
+++ b/Outputs/10_lepa_per_metric_comparison.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_15673CAE8F55B9F673CF72A2687C167482D12F60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="per_site" sheetId="1" r:id="rId1"/>
@@ -14,537 +13,12 @@
     <sheet name="publication_distribution" sheetId="4" r:id="rId4"/>
     <sheet name="publication_residuals" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="168">
-  <si>
-    <t>site_code</t>
-  </si>
-  <si>
-    <t>site_id</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>lepa_DSFI</t>
-  </si>
-  <si>
-    <t>our_DSFI</t>
-  </si>
-  <si>
-    <t>res_DSFI</t>
-  </si>
-  <si>
-    <t>lepa_ASPT</t>
-  </si>
-  <si>
-    <t>our_ASPT</t>
-  </si>
-  <si>
-    <t>res_ASPT</t>
-  </si>
-  <si>
-    <t>lepa_DEP</t>
-  </si>
-  <si>
-    <t>our_DEP</t>
-  </si>
-  <si>
-    <t>res_DEP</t>
-  </si>
-  <si>
-    <t>lepa_EHPCrHi</t>
-  </si>
-  <si>
-    <t>our_EHPCrHi</t>
-  </si>
-  <si>
-    <t>res_EHPCrHi</t>
-  </si>
-  <si>
-    <t>lepa_LRMI</t>
-  </si>
-  <si>
-    <t>our_LRMI</t>
-  </si>
-  <si>
-    <t>res_LRMI</t>
-  </si>
-  <si>
-    <t>lepa_class</t>
-  </si>
-  <si>
-    <t>our_class</t>
-  </si>
-  <si>
-    <t>class_match</t>
-  </si>
-  <si>
-    <t>LTR1492_2022</t>
-  </si>
-  <si>
-    <t>LTR1492</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Poor</t>
-  </si>
-  <si>
-    <t>LTR163_2019</t>
-  </si>
-  <si>
-    <t>LTR163</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>LTR386_2019</t>
-  </si>
-  <si>
-    <t>LTR386</t>
-  </si>
-  <si>
-    <t>LTR163_2022</t>
-  </si>
-  <si>
-    <t>LTR127_2015</t>
-  </si>
-  <si>
-    <t>LTR127</t>
-  </si>
-  <si>
-    <t>Bad</t>
-  </si>
-  <si>
-    <t>LTR127_2020</t>
-  </si>
-  <si>
-    <t>LTR450_2015</t>
-  </si>
-  <si>
-    <t>LTR450</t>
-  </si>
-  <si>
-    <t>LTR1466_2019</t>
-  </si>
-  <si>
-    <t>LTR1466</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>LTR127_2017</t>
-  </si>
-  <si>
-    <t>LTR625_2022</t>
-  </si>
-  <si>
-    <t>LTR625</t>
-  </si>
-  <si>
-    <t>LTR297_2021</t>
-  </si>
-  <si>
-    <t>LTR297</t>
-  </si>
-  <si>
-    <t>LTR86_2015</t>
-  </si>
-  <si>
-    <t>LTR86</t>
-  </si>
-  <si>
-    <t>LTR1447_2015</t>
-  </si>
-  <si>
-    <t>LTR1447</t>
-  </si>
-  <si>
-    <t>LTR1466_2016</t>
-  </si>
-  <si>
-    <t>LTR1687_2016</t>
-  </si>
-  <si>
-    <t>LTR1687</t>
-  </si>
-  <si>
-    <t>LTR1687_2022</t>
-  </si>
-  <si>
-    <t>LTR1461_2016</t>
-  </si>
-  <si>
-    <t>LTR1461</t>
-  </si>
-  <si>
-    <t>LTR1461_2019</t>
-  </si>
-  <si>
-    <t>LTR1461_2022</t>
-  </si>
-  <si>
-    <t>LTR1466_2022</t>
-  </si>
-  <si>
-    <t>LTR1488_2015</t>
-  </si>
-  <si>
-    <t>LTR1488</t>
-  </si>
-  <si>
-    <t>LTR386_2016</t>
-  </si>
-  <si>
-    <t>LTR386_2022</t>
-  </si>
-  <si>
-    <t>LTR1488_2016</t>
-  </si>
-  <si>
-    <t>LTR1492_2019</t>
-  </si>
-  <si>
-    <t>LTR1502_2015</t>
-  </si>
-  <si>
-    <t>LTR1502</t>
-  </si>
-  <si>
-    <t>LTR163_2016</t>
-  </si>
-  <si>
-    <t>LTR297_2018</t>
-  </si>
-  <si>
-    <t>LTR450_2020</t>
-  </si>
-  <si>
-    <t>LTR706_2015</t>
-  </si>
-  <si>
-    <t>LTR706</t>
-  </si>
-  <si>
-    <t>LTR86_2016</t>
-  </si>
-  <si>
-    <t>LTR1063_2021</t>
-  </si>
-  <si>
-    <t>LTR1063</t>
-  </si>
-  <si>
-    <t>LTR308_2018</t>
-  </si>
-  <si>
-    <t>LTR308</t>
-  </si>
-  <si>
-    <t>LTR1447_2022</t>
-  </si>
-  <si>
-    <t>LTR1449_2015</t>
-  </si>
-  <si>
-    <t>LTR1449</t>
-  </si>
-  <si>
-    <t>LTR1488_2019</t>
-  </si>
-  <si>
-    <t>LTR1488_2022</t>
-  </si>
-  <si>
-    <t>LTR1492_2016</t>
-  </si>
-  <si>
-    <t>LTR1501_2016</t>
-  </si>
-  <si>
-    <t>LTR1501</t>
-  </si>
-  <si>
-    <t>LTR1687_2017</t>
-  </si>
-  <si>
-    <t>LTR297_2015</t>
-  </si>
-  <si>
-    <t>LTR337_2016</t>
-  </si>
-  <si>
-    <t>LTR337</t>
-  </si>
-  <si>
-    <t>LTR337_2022</t>
-  </si>
-  <si>
-    <t>LTR351_2019</t>
-  </si>
-  <si>
-    <t>LTR351</t>
-  </si>
-  <si>
-    <t>LTR411_2022</t>
-  </si>
-  <si>
-    <t>LTR411</t>
-  </si>
-  <si>
-    <t>LTR1502_2019</t>
-  </si>
-  <si>
-    <t>LTR337_2019</t>
-  </si>
-  <si>
-    <t>LTR1063_2017</t>
-  </si>
-  <si>
-    <t>LTR1299_2015</t>
-  </si>
-  <si>
-    <t>LTR1299</t>
-  </si>
-  <si>
-    <t>LTR1299_2019</t>
-  </si>
-  <si>
-    <t>LTR1299_2022</t>
-  </si>
-  <si>
-    <t>LTR1320_2016</t>
-  </si>
-  <si>
-    <t>LTR1320</t>
-  </si>
-  <si>
-    <t>LTR1320_2019</t>
-  </si>
-  <si>
-    <t>LTR1320_2022</t>
-  </si>
-  <si>
-    <t>LTR1379_2015</t>
-  </si>
-  <si>
-    <t>LTR1379</t>
-  </si>
-  <si>
-    <t>LTR1379_2019</t>
-  </si>
-  <si>
-    <t>LTR1379_2022</t>
-  </si>
-  <si>
-    <t>LTR1385_2016</t>
-  </si>
-  <si>
-    <t>LTR1385</t>
-  </si>
-  <si>
-    <t>LTR1385_2019</t>
-  </si>
-  <si>
-    <t>LTR1385_2022</t>
-  </si>
-  <si>
-    <t>LTR1447_2019</t>
-  </si>
-  <si>
-    <t>LTR1449_2019</t>
-  </si>
-  <si>
-    <t>LTR1449_2022</t>
-  </si>
-  <si>
-    <t>LTR1501_2019</t>
-  </si>
-  <si>
-    <t>LTR1501_2022</t>
-  </si>
-  <si>
-    <t>LTR1502_2022</t>
-  </si>
-  <si>
-    <t>LTR1601_2021</t>
-  </si>
-  <si>
-    <t>LTR1601</t>
-  </si>
-  <si>
-    <t>LTR232_2015</t>
-  </si>
-  <si>
-    <t>LTR232</t>
-  </si>
-  <si>
-    <t>LTR232_2019</t>
-  </si>
-  <si>
-    <t>LTR232_2022</t>
-  </si>
-  <si>
-    <t>LTR308_2021</t>
-  </si>
-  <si>
-    <t>LTR351_2015</t>
-  </si>
-  <si>
-    <t>LTR351_2022</t>
-  </si>
-  <si>
-    <t>LTR411_2015</t>
-  </si>
-  <si>
-    <t>LTR411_2019</t>
-  </si>
-  <si>
-    <t>LTR625_2015</t>
-  </si>
-  <si>
-    <t>LTR625_2019</t>
-  </si>
-  <si>
-    <t>LTR627_2015</t>
-  </si>
-  <si>
-    <t>LTR627</t>
-  </si>
-  <si>
-    <t>LTR706_2018</t>
-  </si>
-  <si>
-    <t>LTR706_2021</t>
-  </si>
-  <si>
-    <t>LTR86_2017</t>
-  </si>
-  <si>
-    <t>LTR86_2020</t>
-  </si>
-  <si>
-    <t>metric</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>mean_residual</t>
-  </si>
-  <si>
-    <t>median_residual</t>
-  </si>
-  <si>
-    <t>mean_abs_res</t>
-  </si>
-  <si>
-    <t>pearson_r</t>
-  </si>
-  <si>
-    <t>pearson_p</t>
-  </si>
-  <si>
-    <t>pct_exact</t>
-  </si>
-  <si>
-    <t>DSFI</t>
-  </si>
-  <si>
-    <t>ASPT</t>
-  </si>
-  <si>
-    <t>#DEP</t>
-  </si>
-  <si>
-    <t>%EHP–%CrHi</t>
-  </si>
-  <si>
-    <t>EQR</t>
-  </si>
-  <si>
-    <t>median_diff</t>
-  </si>
-  <si>
-    <t>W_stat</t>
-  </si>
-  <si>
-    <t>W_p</t>
-  </si>
-  <si>
-    <t>LRMI</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Mean</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>LEPA</t>
-  </si>
-  <si>
-    <t>OTL</t>
-  </si>
-  <si>
-    <t>LEPA − LT-OTL (mean)</t>
-  </si>
-  <si>
-    <t>LEPA − LT-OTL (median)</t>
-  </si>
-  <si>
-    <t>Mean |residual|</t>
-  </si>
-  <si>
-    <t>Pearson r</t>
-  </si>
-  <si>
-    <t>% within ±0.005</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -589,25 +63,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -645,7 +111,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -679,7 +145,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -714,10 +179,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -890,81 +354,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>site_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>site_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_DSFI</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>our_DSFI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>res_DSFI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_ASPT</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>our_ASPT</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>res_ASPT</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_DEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>our_DEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>res_DEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_EHPCrHi</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>our_EHPCrHi</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>res_EHPCrHi</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_LRMI</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>our_LRMI</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>res_LRMI</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>lepa_class</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>our_class</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>class_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LTR1492_2022</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C2">
         <v>2022</v>
@@ -979,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.72222222222222221</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H2">
-        <v>0.72916666666666663</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="I2">
-        <v>-6.9444444444444198E-3</v>
+        <v>-0.00694444444444442</v>
       </c>
       <c r="J2">
         <v>0.1333333333333333</v>
@@ -997,13 +507,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M2">
-        <v>0.63401442307692302</v>
+        <v>0.634014423076923</v>
       </c>
       <c r="N2">
-        <v>0.21033653846153849</v>
+        <v>0.2103365384615385</v>
       </c>
       <c r="O2">
-        <v>0.42367788461538453</v>
+        <v>0.4236778846153845</v>
       </c>
       <c r="P2">
         <v>0.5</v>
@@ -1014,43 +524,51 @@
       <c r="R2">
         <v>0.11</v>
       </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>24</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LTR163_2019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C3">
         <v>2019</v>
       </c>
       <c r="D3">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E3">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H3">
-        <v>0.78205128205128227</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="I3">
-        <v>-4.2735042735044804E-3</v>
+        <v>-0.00427350427350448</v>
       </c>
       <c r="J3">
         <v>0.4</v>
@@ -1062,13 +580,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.69883966244725726</v>
+        <v>0.6988396624472573</v>
       </c>
       <c r="N3">
-        <v>0.38897679324894507</v>
+        <v>0.3889767932489451</v>
       </c>
       <c r="O3">
-        <v>0.30986286919831219</v>
+        <v>0.3098628691983122</v>
       </c>
       <c r="P3">
         <v>0.68</v>
@@ -1077,24 +595,32 @@
         <v>0.6</v>
       </c>
       <c r="R3">
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="S3" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" t="s">
-        <v>27</v>
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LTR386_2019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C4">
         <v>2019</v>
@@ -1109,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.74603174603174605</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="H4">
-        <v>0.74603174603174605</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1127,13 +653,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.77660891089108908</v>
+        <v>0.7766089108910891</v>
       </c>
       <c r="N4">
-        <v>0.51980198019801982</v>
+        <v>0.5198019801980198</v>
       </c>
       <c r="O4">
-        <v>0.25680693069306931</v>
+        <v>0.2568069306930693</v>
       </c>
       <c r="P4">
         <v>0.66</v>
@@ -1142,45 +668,53 @@
         <v>0.59</v>
       </c>
       <c r="R4">
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="S4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" t="s">
-        <v>23</v>
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LTR163_2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C5">
         <v>2022</v>
       </c>
       <c r="D5">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E5">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.75641025641025639</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="H5">
-        <v>0.76543209876543206</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="I5">
-        <v>-9.0218423551756688E-3</v>
+        <v>-0.009021842355175669</v>
       </c>
       <c r="J5">
         <v>0.8</v>
@@ -1192,13 +726,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.77420112781954886</v>
+        <v>0.7742011278195489</v>
       </c>
       <c r="N5">
-        <v>0.51061320754716977</v>
+        <v>0.5106132075471698</v>
       </c>
       <c r="O5">
-        <v>0.26358792027237909</v>
+        <v>0.2635879202723791</v>
       </c>
       <c r="P5">
         <v>0.79</v>
@@ -1207,63 +741,71 @@
         <v>0.73</v>
       </c>
       <c r="R5">
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="S5" t="s">
-        <v>27</v>
-      </c>
-      <c r="T5" t="s">
-        <v>27</v>
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LTR127_2015</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C6">
         <v>2015</v>
       </c>
       <c r="D6">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G6">
         <v>0.3888888888888889</v>
       </c>
       <c r="H6">
-        <v>0.45238095238095227</v>
+        <v>0.4523809523809523</v>
       </c>
       <c r="I6">
-        <v>-6.3492063492063378E-2</v>
+        <v>-0.06349206349206338</v>
       </c>
       <c r="J6">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K6">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.61981327800829877</v>
+        <v>0.6198132780082988</v>
       </c>
       <c r="N6">
-        <v>0.46809623430962338</v>
+        <v>0.4680962343096234</v>
       </c>
       <c r="O6">
-        <v>0.15171704369867539</v>
+        <v>0.1517170436986754</v>
       </c>
       <c r="P6">
         <v>0.31</v>
@@ -1274,22 +816,30 @@
       <c r="R6">
         <v>0.06</v>
       </c>
-      <c r="S6" t="s">
-        <v>24</v>
-      </c>
-      <c r="T6" t="s">
-        <v>33</v>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LTR127_2020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C7">
         <v>2020</v>
@@ -1304,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.57777777777777783</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="H7">
-        <v>0.60416666666666663</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="I7">
-        <v>-2.6388888888888799E-2</v>
+        <v>-0.0263888888888888</v>
       </c>
       <c r="J7">
         <v>0.2</v>
@@ -1322,13 +872,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.62902706185567003</v>
+        <v>0.62902706185567</v>
       </c>
       <c r="N7">
-        <v>0.39022229381443302</v>
+        <v>0.390222293814433</v>
       </c>
       <c r="O7">
-        <v>0.23880476804123699</v>
+        <v>0.238804768041237</v>
       </c>
       <c r="P7">
         <v>0.48</v>
@@ -1339,61 +889,69 @@
       <c r="R7">
         <v>0.06</v>
       </c>
-      <c r="S7" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" t="s">
-        <v>23</v>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LTR450_2015</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LTR450</t>
+        </is>
       </c>
       <c r="C8">
         <v>2015</v>
       </c>
       <c r="D8">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E8">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.52777777777777779</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="H8">
-        <v>0.52777777777777779</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K8">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.60287610619469023</v>
+        <v>0.6028761061946902</v>
       </c>
       <c r="N8">
-        <v>0.34292035398230092</v>
+        <v>0.3429203539823009</v>
       </c>
       <c r="O8">
-        <v>0.25995575221238931</v>
+        <v>0.2599557522123893</v>
       </c>
       <c r="P8">
         <v>0.38</v>
@@ -1404,61 +962,69 @@
       <c r="R8">
         <v>0.06</v>
       </c>
-      <c r="S8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T8" t="s">
-        <v>24</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LTR1466_2019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C9">
         <v>2019</v>
       </c>
       <c r="D9">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E9">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.72839506172839508</v>
+        <v>0.7283950617283951</v>
       </c>
       <c r="H9">
-        <v>0.72023809523809523</v>
+        <v>0.7202380952380952</v>
       </c>
       <c r="I9">
-        <v>8.156966490299844E-3</v>
+        <v>0.008156966490299844</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L9">
-        <v>6.6666666666666652E-2</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="M9">
-        <v>0.77762803234501354</v>
+        <v>0.7776280323450135</v>
       </c>
       <c r="N9">
-        <v>0.60242587601078168</v>
+        <v>0.6024258760107817</v>
       </c>
       <c r="O9">
-        <v>0.17520215633423189</v>
+        <v>0.1752021563342319</v>
       </c>
       <c r="P9">
         <v>0.83</v>
@@ -1467,45 +1033,53 @@
         <v>0.77</v>
       </c>
       <c r="R9">
-        <v>5.9999999999999942E-2</v>
-      </c>
-      <c r="S9" t="s">
-        <v>39</v>
-      </c>
-      <c r="T9" t="s">
-        <v>27</v>
+        <v>0.05999999999999994</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LTR127_2017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C10">
         <v>2017</v>
       </c>
       <c r="D10">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E10">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F10">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G10">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="H10">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="I10">
-        <v>5.5511151231257827E-17</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="J10">
         <v>0.2</v>
@@ -1520,10 +1094,10 @@
         <v>0.640194489465154</v>
       </c>
       <c r="N10">
-        <v>0.45583468395461912</v>
+        <v>0.4558346839546191</v>
       </c>
       <c r="O10">
-        <v>0.18435980551053491</v>
+        <v>0.1843598055105349</v>
       </c>
       <c r="P10">
         <v>0.36</v>
@@ -1532,33 +1106,41 @@
         <v>0.31</v>
       </c>
       <c r="R10">
-        <v>4.9999999999999989E-2</v>
-      </c>
-      <c r="S10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T10" t="s">
-        <v>24</v>
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LTR625_2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LTR625</t>
+        </is>
       </c>
       <c r="C11">
         <v>2022</v>
       </c>
       <c r="D11">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E11">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1567,25 +1149,25 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="H11">
-        <v>0.79999999999999993</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="I11">
-        <v>2.2222222222222369E-2</v>
+        <v>0.02222222222222237</v>
       </c>
       <c r="J11">
-        <v>1.0666666666666671</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="K11">
-        <v>1.0666666666666671</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="L11">
-        <v>-4.4408920985006262E-16</v>
+        <v>-4.440892098500626E-16</v>
       </c>
       <c r="M11">
-        <v>0.74626614639397193</v>
+        <v>0.7462661463939719</v>
       </c>
       <c r="N11">
-        <v>0.58447504069451983</v>
+        <v>0.5844750406945198</v>
       </c>
       <c r="O11">
         <v>0.1617911056994521</v>
@@ -1597,51 +1179,59 @@
         <v>0.78</v>
       </c>
       <c r="R11">
-        <v>4.9999999999999933E-2</v>
-      </c>
-      <c r="S11" t="s">
-        <v>39</v>
-      </c>
-      <c r="T11" t="s">
-        <v>27</v>
+        <v>0.04999999999999993</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LTR297_2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C12">
         <v>2021</v>
       </c>
       <c r="D12">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G12">
-        <v>0.70512820512820518</v>
+        <v>0.7051282051282052</v>
       </c>
       <c r="H12">
-        <v>0.70512820512820518</v>
+        <v>0.7051282051282052</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K12">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1662,63 +1252,71 @@
         <v>0.54</v>
       </c>
       <c r="R12">
-        <v>-4.0000000000000042E-2</v>
-      </c>
-      <c r="S12" t="s">
-        <v>23</v>
-      </c>
-      <c r="T12" t="s">
-        <v>23</v>
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LTR86_2015</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C13">
         <v>2015</v>
       </c>
       <c r="D13">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E13">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.63888888888888884</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="H13">
-        <v>0.63888888888888884</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K13">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L13">
-        <v>6.6666666666666596E-2</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="M13">
         <v>0.6891025641025641</v>
       </c>
       <c r="N13">
-        <v>0.59829059829059827</v>
+        <v>0.5982905982905983</v>
       </c>
       <c r="O13">
-        <v>9.0811965811965822E-2</v>
+        <v>0.09081196581196582</v>
       </c>
       <c r="P13">
         <v>0.5</v>
@@ -1727,89 +1325,105 @@
         <v>0.46</v>
       </c>
       <c r="R13">
-        <v>3.999999999999998E-2</v>
-      </c>
-      <c r="S13" t="s">
-        <v>23</v>
-      </c>
-      <c r="T13" t="s">
-        <v>23</v>
+        <v>0.03999999999999998</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LTR1447_2015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LTR1447</t>
+        </is>
       </c>
       <c r="C14">
         <v>2015</v>
       </c>
       <c r="D14">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E14">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F14">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G14">
-        <v>0.78205128205128205</v>
+        <v>0.782051282051282</v>
       </c>
       <c r="H14">
         <v>0.7901234567901233</v>
       </c>
       <c r="I14">
-        <v>-8.0721747388412535E-3</v>
+        <v>-0.008072174738841253</v>
       </c>
       <c r="J14">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K14">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.67680180180180183</v>
+        <v>0.6768018018018018</v>
       </c>
       <c r="N14">
-        <v>0.67680180180180183</v>
+        <v>0.6768018018018018</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q14">
         <v>0.65</v>
       </c>
       <c r="R14">
-        <v>3.9999999999999918E-2</v>
-      </c>
-      <c r="S14" t="s">
-        <v>27</v>
-      </c>
-      <c r="T14" t="s">
-        <v>27</v>
+        <v>0.03999999999999992</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LTR1466_2016</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C15">
         <v>2016</v>
@@ -1824,57 +1438,65 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.65333333333333332</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="H15">
-        <v>0.65333333333333332</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K15">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.69547134935304977</v>
+        <v>0.6954713493530498</v>
       </c>
       <c r="N15">
-        <v>0.56416984732824427</v>
+        <v>0.5641698473282443</v>
       </c>
       <c r="O15">
-        <v>0.13130150202480551</v>
+        <v>0.1313015020248055</v>
       </c>
       <c r="P15">
         <v>0.6</v>
       </c>
       <c r="Q15">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R15">
-        <v>3.9999999999999918E-2</v>
-      </c>
-      <c r="S15" t="s">
-        <v>27</v>
-      </c>
-      <c r="T15" t="s">
-        <v>23</v>
+        <v>0.03999999999999992</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s">
-        <v>51</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LTR1687_2016</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C16">
         <v>2016</v>
@@ -1889,28 +1511,28 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H16">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K16">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.74904580152671763</v>
+        <v>0.7490458015267176</v>
       </c>
       <c r="N16">
-        <v>0.57170542635658905</v>
+        <v>0.5717054263565891</v>
       </c>
       <c r="O16">
         <v>0.1773403751701286</v>
@@ -1919,36 +1541,44 @@
         <v>0.59</v>
       </c>
       <c r="Q16">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="R16">
-        <v>3.9999999999999918E-2</v>
-      </c>
-      <c r="S16" t="s">
-        <v>23</v>
-      </c>
-      <c r="T16" t="s">
-        <v>23</v>
+        <v>0.03999999999999992</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTR1687_2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C17">
         <v>2022</v>
       </c>
       <c r="D17">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1957,28 +1587,28 @@
         <v>1.074074074074074</v>
       </c>
       <c r="H17">
-        <v>0.96666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="I17">
-        <v>0.10740740740740751</v>
+        <v>0.1074074074074075</v>
       </c>
       <c r="J17">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K17">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L17">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M17">
-        <v>0.77702702702702697</v>
+        <v>0.777027027027027</v>
       </c>
       <c r="N17">
         <v>0.7432432432432432</v>
       </c>
       <c r="O17">
-        <v>3.3783783783783772E-2</v>
+        <v>0.03378378378378377</v>
       </c>
       <c r="P17">
         <v>0.7</v>
@@ -1987,42 +1617,50 @@
         <v>0.66</v>
       </c>
       <c r="R17">
-        <v>3.9999999999999918E-2</v>
-      </c>
-      <c r="S17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T17" t="s">
-        <v>27</v>
+        <v>0.03999999999999992</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" t="s">
-        <v>54</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LTR1461_2016</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C18">
         <v>2016</v>
       </c>
       <c r="D18">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E18">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F18">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G18">
-        <v>0.87037037037037035</v>
+        <v>0.8703703703703703</v>
       </c>
       <c r="H18">
-        <v>0.87037037037037035</v>
+        <v>0.8703703703703703</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2037,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0.82347972972972971</v>
+        <v>0.8234797297297297</v>
       </c>
       <c r="N18">
-        <v>0.79081632653061229</v>
+        <v>0.7908163265306123</v>
       </c>
       <c r="O18">
-        <v>3.2663403199117418E-2</v>
+        <v>0.03266340319911742</v>
       </c>
       <c r="P18">
         <v>0.64</v>
@@ -2052,24 +1690,32 @@
         <v>0.67</v>
       </c>
       <c r="R18">
-        <v>-3.000000000000003E-2</v>
-      </c>
-      <c r="S18" t="s">
-        <v>27</v>
-      </c>
-      <c r="T18" t="s">
-        <v>27</v>
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LTR1461_2019</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C19">
         <v>2019</v>
@@ -2084,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.74137931034482751</v>
+        <v>0.7413793103448275</v>
       </c>
       <c r="H19">
-        <v>0.75595238095238093</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="I19">
-        <v>-1.457307060755342E-2</v>
+        <v>-0.01457307060755342</v>
       </c>
       <c r="J19">
         <v>0.6</v>
@@ -2102,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.78899909828674475</v>
+        <v>0.7889990982867447</v>
       </c>
       <c r="N19">
-        <v>0.66708088567555357</v>
+        <v>0.6670808856755536</v>
       </c>
       <c r="O19">
-        <v>0.12191821261119121</v>
+        <v>0.1219182126111912</v>
       </c>
       <c r="P19">
         <v>0.66</v>
@@ -2117,24 +1763,32 @@
         <v>0.63</v>
       </c>
       <c r="R19">
-        <v>3.000000000000003E-2</v>
-      </c>
-      <c r="S19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T19" t="s">
-        <v>27</v>
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>54</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LTR1461_2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C20">
         <v>2022</v>
@@ -2149,31 +1803,31 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.62745098039215685</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="H20">
-        <v>0.62745098039215685</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K20">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L20">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M20">
-        <v>0.75688073394495414</v>
+        <v>0.7568807339449541</v>
       </c>
       <c r="N20">
-        <v>0.65940366972477071</v>
+        <v>0.6594036697247707</v>
       </c>
       <c r="O20">
-        <v>9.7477064220183429E-2</v>
+        <v>0.09747706422018343</v>
       </c>
       <c r="P20">
         <v>0.54</v>
@@ -2182,24 +1836,32 @@
         <v>0.51</v>
       </c>
       <c r="R20">
-        <v>3.000000000000003E-2</v>
-      </c>
-      <c r="S20" t="s">
-        <v>23</v>
-      </c>
-      <c r="T20" t="s">
-        <v>23</v>
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LTR1466_2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C21">
         <v>2022</v>
@@ -2214,28 +1876,28 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.56862745098039225</v>
+        <v>0.5686274509803922</v>
       </c>
       <c r="H21">
-        <v>0.56862745098039225</v>
+        <v>0.5686274509803922</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K21">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0.67123921085080152</v>
+        <v>0.6712392108508015</v>
       </c>
       <c r="N21">
-        <v>0.56304213135068149</v>
+        <v>0.5630421313506815</v>
       </c>
       <c r="O21">
         <v>0.10819707950012</v>
@@ -2247,24 +1909,32 @@
         <v>0.49</v>
       </c>
       <c r="R21">
-        <v>3.000000000000003E-2</v>
-      </c>
-      <c r="S21" t="s">
-        <v>23</v>
-      </c>
-      <c r="T21" t="s">
-        <v>23</v>
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LTR1488_2015</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C22">
         <v>2015</v>
@@ -2279,31 +1949,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.72222222222222221</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H22">
-        <v>0.71052631578947356</v>
+        <v>0.7105263157894736</v>
       </c>
       <c r="I22">
-        <v>1.169590643274865E-2</v>
+        <v>0.01169590643274865</v>
       </c>
       <c r="J22">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K22">
         <v>0.4</v>
       </c>
       <c r="L22">
-        <v>6.6666666666666652E-2</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="M22">
         <v>0.7799586776859504</v>
       </c>
       <c r="N22">
-        <v>0.75929752066115697</v>
+        <v>0.759297520661157</v>
       </c>
       <c r="O22">
-        <v>2.0661157024793431E-2</v>
+        <v>0.02066115702479343</v>
       </c>
       <c r="P22">
         <v>0.62</v>
@@ -2312,45 +1982,53 @@
         <v>0.59</v>
       </c>
       <c r="R22">
-        <v>3.000000000000003E-2</v>
-      </c>
-      <c r="S22" t="s">
-        <v>27</v>
-      </c>
-      <c r="T22" t="s">
-        <v>23</v>
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
-      <c r="A23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" t="s">
-        <v>29</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LTR386_2016</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C23">
         <v>2016</v>
       </c>
       <c r="D23">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E23">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F23">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G23">
-        <v>0.77999999999999992</v>
+        <v>0.7799999999999999</v>
       </c>
       <c r="H23">
-        <v>0.78205128205128227</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="I23">
-        <v>-2.0512820512823549E-3</v>
+        <v>-0.002051282051282355</v>
       </c>
       <c r="J23">
         <v>0.6</v>
@@ -2362,48 +2040,56 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.70482866043613701</v>
+        <v>0.704828660436137</v>
       </c>
       <c r="N23">
-        <v>0.67562305295950154</v>
+        <v>0.6756230529595015</v>
       </c>
       <c r="O23">
-        <v>2.9205607476635479E-2</v>
+        <v>0.02920560747663548</v>
       </c>
       <c r="P23">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q23">
         <v>0.72</v>
       </c>
       <c r="R23">
-        <v>-3.000000000000003E-2</v>
-      </c>
-      <c r="S23" t="s">
-        <v>27</v>
-      </c>
-      <c r="T23" t="s">
-        <v>27</v>
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LTR386_2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C24">
         <v>2022</v>
       </c>
       <c r="D24">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E24">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2412,10 +2098,10 @@
         <v>0.8222222222222223</v>
       </c>
       <c r="H24">
-        <v>0.81182795698924737</v>
+        <v>0.8118279569892474</v>
       </c>
       <c r="I24">
-        <v>1.0394265232974931E-2</v>
+        <v>0.01039426523297493</v>
       </c>
       <c r="J24">
         <v>0.6</v>
@@ -2427,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.72050290135396511</v>
+        <v>0.7205029013539651</v>
       </c>
       <c r="N24">
-        <v>0.57663690476190477</v>
+        <v>0.5766369047619048</v>
       </c>
       <c r="O24">
-        <v>0.14386599659206031</v>
+        <v>0.1438659965920603</v>
       </c>
       <c r="P24">
         <v>0.74</v>
@@ -2442,45 +2128,53 @@
         <v>0.71</v>
       </c>
       <c r="R24">
-        <v>3.000000000000003E-2</v>
-      </c>
-      <c r="S24" t="s">
-        <v>27</v>
-      </c>
-      <c r="T24" t="s">
-        <v>27</v>
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U24" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
-      <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>59</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LTR1488_2016</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C25">
         <v>2016</v>
       </c>
       <c r="D25">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E25">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.84920634920634919</v>
+        <v>0.8492063492063492</v>
       </c>
       <c r="H25">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I25">
-        <v>1.587301587301582E-2</v>
+        <v>0.01587301587301582</v>
       </c>
       <c r="J25">
         <v>0.4</v>
@@ -2492,13 +2186,13 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.80735660847880308</v>
+        <v>0.8073566084788031</v>
       </c>
       <c r="N25">
-        <v>0.75903990024937651</v>
+        <v>0.7590399002493765</v>
       </c>
       <c r="O25">
-        <v>4.8316708229426568E-2</v>
+        <v>0.04831670822942657</v>
       </c>
       <c r="P25">
         <v>0.68</v>
@@ -2507,24 +2201,32 @@
         <v>0.66</v>
       </c>
       <c r="R25">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S25" t="s">
-        <v>27</v>
-      </c>
-      <c r="T25" t="s">
-        <v>27</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LTR1492_2019</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C26">
         <v>2019</v>
@@ -2539,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.60784313725490202</v>
+        <v>0.607843137254902</v>
       </c>
       <c r="H26">
-        <v>0.60185185185185175</v>
+        <v>0.6018518518518517</v>
       </c>
       <c r="I26">
-        <v>5.9912854030502727E-3</v>
+        <v>0.005991285403050273</v>
       </c>
       <c r="J26">
         <v>0.2</v>
@@ -2557,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.66937869822485196</v>
+        <v>0.669378698224852</v>
       </c>
       <c r="N26">
         <v>0.5750739644970414</v>
       </c>
       <c r="O26">
-        <v>9.4304733727810564E-2</v>
+        <v>0.09430473372781056</v>
       </c>
       <c r="P26">
         <v>0.49</v>
@@ -2572,33 +2274,41 @@
         <v>0.47</v>
       </c>
       <c r="R26">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S26" t="s">
-        <v>23</v>
-      </c>
-      <c r="T26" t="s">
-        <v>23</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LTR1502_2015</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LTR1502</t>
+        </is>
       </c>
       <c r="C27">
         <v>2015</v>
       </c>
       <c r="D27">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E27">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2613,22 +2323,22 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K27">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.71747448979591844</v>
+        <v>0.7174744897959184</v>
       </c>
       <c r="N27">
-        <v>0.63456632653061229</v>
+        <v>0.6345663265306123</v>
       </c>
       <c r="O27">
-        <v>8.2908163265306145E-2</v>
+        <v>0.08290816326530615</v>
       </c>
       <c r="P27">
         <v>0.72</v>
@@ -2637,24 +2347,32 @@
         <v>0.7</v>
       </c>
       <c r="R27">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S27" t="s">
-        <v>27</v>
-      </c>
-      <c r="T27" t="s">
-        <v>27</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
-      <c r="A28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LTR163_2016</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C28">
         <v>2016</v>
@@ -2669,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.79761904761904756</v>
+        <v>0.7976190476190476</v>
       </c>
       <c r="H28">
-        <v>0.79885057471264365</v>
+        <v>0.7988505747126436</v>
       </c>
       <c r="I28">
-        <v>-1.2315270935960849E-3</v>
+        <v>-0.001231527093596085</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2687,13 +2405,13 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.72158626328699915</v>
+        <v>0.7215862632869992</v>
       </c>
       <c r="N28">
-        <v>0.65412919051512664</v>
+        <v>0.6541291905151266</v>
       </c>
       <c r="O28">
-        <v>6.7457072771872517E-2</v>
+        <v>0.06745707277187252</v>
       </c>
       <c r="P28">
         <v>0.88</v>
@@ -2702,45 +2420,53 @@
         <v>0.86</v>
       </c>
       <c r="R28">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S28" t="s">
-        <v>39</v>
-      </c>
-      <c r="T28" t="s">
-        <v>39</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" t="s">
-        <v>44</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LTR297_2018</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
       <c r="D29">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E29">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F29">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G29">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="H29">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="I29">
-        <v>5.5511151231257827E-17</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="J29">
         <v>0.2</v>
@@ -2752,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.76740506329113911</v>
+        <v>0.7674050632911391</v>
       </c>
       <c r="N29">
-        <v>0.66455696202531633</v>
+        <v>0.6645569620253163</v>
       </c>
       <c r="O29">
-        <v>0.10284810126582281</v>
+        <v>0.1028481012658228</v>
       </c>
       <c r="P29">
         <v>0.39</v>
@@ -2767,33 +2493,41 @@
         <v>0.37</v>
       </c>
       <c r="R29">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S29" t="s">
-        <v>24</v>
-      </c>
-      <c r="T29" t="s">
-        <v>24</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
-      <c r="A30" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LTR450_2020</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LTR450</t>
+        </is>
       </c>
       <c r="C30">
         <v>2020</v>
       </c>
       <c r="D30">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E30">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2817,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.61144578313253006</v>
+        <v>0.6114457831325301</v>
       </c>
       <c r="N30">
-        <v>0.54066265060240959</v>
+        <v>0.5406626506024096</v>
       </c>
       <c r="O30">
-        <v>7.0783132530120474E-2</v>
+        <v>0.07078313253012047</v>
       </c>
       <c r="P30">
         <v>0.38</v>
@@ -2832,45 +2566,53 @@
         <v>0.36</v>
       </c>
       <c r="R30">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S30" t="s">
-        <v>24</v>
-      </c>
-      <c r="T30" t="s">
-        <v>24</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LTR706_2015</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LTR706</t>
+        </is>
       </c>
       <c r="C31">
         <v>2015</v>
       </c>
       <c r="D31">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E31">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.42592592592592587</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="H31">
-        <v>0.42592592592592582</v>
+        <v>0.4259259259259258</v>
       </c>
       <c r="I31">
-        <v>5.5511151231257827E-17</v>
+        <v>5.551115123125783E-17</v>
       </c>
       <c r="J31">
         <v>0.1333333333333333</v>
@@ -2882,13 +2624,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M31">
-        <v>0.67164179104477606</v>
+        <v>0.6716417910447761</v>
       </c>
       <c r="N31">
-        <v>0.58768656716417911</v>
+        <v>0.5876865671641791</v>
       </c>
       <c r="O31">
-        <v>8.3955223880596952E-2</v>
+        <v>0.08395522388059695</v>
       </c>
       <c r="P31">
         <v>0.39</v>
@@ -2897,45 +2639,53 @@
         <v>0.37</v>
       </c>
       <c r="R31">
-        <v>2.0000000000000021E-2</v>
-      </c>
-      <c r="S31" t="s">
-        <v>24</v>
-      </c>
-      <c r="T31" t="s">
-        <v>24</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
-      <c r="A32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LTR86_2016</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C32">
         <v>2016</v>
       </c>
       <c r="D32">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G32">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H32">
-        <v>0.68939393939393945</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="I32">
-        <v>-2.2727272727272822E-2</v>
+        <v>-0.02272727272727282</v>
       </c>
       <c r="J32">
         <v>0.1333333333333333</v>
@@ -2947,10 +2697,10 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M32">
-        <v>0.77889447236180909</v>
+        <v>0.7788944723618091</v>
       </c>
       <c r="N32">
-        <v>0.67525125628140692</v>
+        <v>0.6752512562814069</v>
       </c>
       <c r="O32">
         <v>0.1036432160804022</v>
@@ -2962,42 +2712,50 @@
         <v>0.5</v>
       </c>
       <c r="R32">
-        <v>-2.0000000000000021E-2</v>
-      </c>
-      <c r="S32" t="s">
-        <v>23</v>
-      </c>
-      <c r="T32" t="s">
-        <v>23</v>
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
-      <c r="A33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LTR1063_2021</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LTR1063</t>
+        </is>
       </c>
       <c r="C33">
         <v>2021</v>
       </c>
       <c r="D33">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E33">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F33">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G33">
-        <v>0.39583333333333331</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H33">
-        <v>0.39583333333333331</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3012,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0.64056939501779353</v>
+        <v>0.6405693950177935</v>
       </c>
       <c r="N33">
-        <v>0.56717081850533801</v>
+        <v>0.567170818505338</v>
       </c>
       <c r="O33">
-        <v>7.3398576512455516E-2</v>
+        <v>0.07339857651245552</v>
       </c>
       <c r="P33">
         <v>0.35</v>
@@ -3027,42 +2785,50 @@
         <v>0.33</v>
       </c>
       <c r="R33">
-        <v>1.9999999999999959E-2</v>
-      </c>
-      <c r="S33" t="s">
-        <v>24</v>
-      </c>
-      <c r="T33" t="s">
-        <v>24</v>
+        <v>0.01999999999999996</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U33" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
-      <c r="A34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" t="s">
-        <v>75</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LTR308_2018</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LTR308</t>
+        </is>
       </c>
       <c r="C34">
         <v>2018</v>
       </c>
       <c r="D34">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E34">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.35416666666666669</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="H34">
-        <v>0.35416666666666669</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3077,13 +2843,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M34">
-        <v>0.61342592592592593</v>
+        <v>0.6134259259259259</v>
       </c>
       <c r="N34">
-        <v>0.53240740740740733</v>
+        <v>0.5324074074074073</v>
       </c>
       <c r="O34">
-        <v>8.1018518518518601E-2</v>
+        <v>0.0810185185185186</v>
       </c>
       <c r="P34">
         <v>0.36</v>
@@ -3092,45 +2858,53 @@
         <v>0.34</v>
       </c>
       <c r="R34">
-        <v>1.9999999999999959E-2</v>
-      </c>
-      <c r="S34" t="s">
-        <v>24</v>
-      </c>
-      <c r="T34" t="s">
-        <v>24</v>
+        <v>0.01999999999999996</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
-      <c r="A35" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LTR1447_2022</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LTR1447</t>
+        </is>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
       <c r="D35">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E35">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.78282828282828287</v>
+        <v>0.7828282828282829</v>
       </c>
       <c r="H35">
-        <v>0.78431372549019607</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="I35">
-        <v>-1.485442661913194E-3</v>
+        <v>-0.001485442661913194</v>
       </c>
       <c r="J35">
         <v>0.6</v>
@@ -3142,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1.0520134228187921</v>
+        <v>1.052013422818792</v>
       </c>
       <c r="N35">
-        <v>1.0425067204301079</v>
+        <v>1.042506720430108</v>
       </c>
       <c r="O35">
-        <v>9.5067023886838964E-3</v>
+        <v>0.009506702388683896</v>
       </c>
       <c r="P35">
         <v>0.78</v>
@@ -3157,89 +2931,105 @@
         <v>0.77</v>
       </c>
       <c r="R35">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S35" t="s">
-        <v>27</v>
-      </c>
-      <c r="T35" t="s">
-        <v>27</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
-      <c r="A36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" t="s">
-        <v>78</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LTR1449_2015</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LTR1449</t>
+        </is>
       </c>
       <c r="C36">
         <v>2015</v>
       </c>
       <c r="D36">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E36">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.76984126984126977</v>
+        <v>0.7698412698412698</v>
       </c>
       <c r="H36">
-        <v>0.79999999999999993</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="I36">
-        <v>-3.0158730158730159E-2</v>
+        <v>-0.03015873015873016</v>
       </c>
       <c r="J36">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K36">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0.69379194630872476</v>
+        <v>0.6937919463087248</v>
       </c>
       <c r="N36">
-        <v>0.69379194630872476</v>
+        <v>0.6937919463087248</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36">
         <v>0.7</v>
       </c>
       <c r="R36">
-        <v>-1.0000000000000011E-2</v>
-      </c>
-      <c r="S36" t="s">
-        <v>27</v>
-      </c>
-      <c r="T36" t="s">
-        <v>27</v>
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
-      <c r="A37" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LTR1488_2019</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C37">
         <v>2019</v>
@@ -3254,13 +3044,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H37">
-        <v>0.70370370370370372</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="I37">
-        <v>-3.703703703703709E-2</v>
+        <v>-0.03703703703703709</v>
       </c>
       <c r="J37">
         <v>0.2</v>
@@ -3272,13 +3062,13 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.68110972568578543</v>
+        <v>0.6811097256857854</v>
       </c>
       <c r="N37">
-        <v>0.67955112219451363</v>
+        <v>0.6795511221945136</v>
       </c>
       <c r="O37">
-        <v>1.558603491271793E-3</v>
+        <v>0.001558603491271793</v>
       </c>
       <c r="P37">
         <v>0.51</v>
@@ -3287,45 +3077,53 @@
         <v>0.52</v>
       </c>
       <c r="R37">
-        <v>-1.0000000000000011E-2</v>
-      </c>
-      <c r="S37" t="s">
-        <v>23</v>
-      </c>
-      <c r="T37" t="s">
-        <v>23</v>
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U37" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
-      <c r="A38" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LTR1488_2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C38">
         <v>2022</v>
       </c>
       <c r="D38">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E38">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.58000000000000007</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="H38">
-        <v>0.58641975308641969</v>
+        <v>0.5864197530864197</v>
       </c>
       <c r="I38">
-        <v>-6.4197530864196217E-3</v>
+        <v>-0.006419753086419622</v>
       </c>
       <c r="J38">
         <v>0.1333333333333333</v>
@@ -3340,10 +3138,10 @@
         <v>0.625</v>
       </c>
       <c r="N38">
-        <v>0.59096534653465338</v>
+        <v>0.5909653465346534</v>
       </c>
       <c r="O38">
-        <v>3.403465346534662E-2</v>
+        <v>0.03403465346534662</v>
       </c>
       <c r="P38">
         <v>0.42</v>
@@ -3352,33 +3150,41 @@
         <v>0.41</v>
       </c>
       <c r="R38">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S38" t="s">
-        <v>23</v>
-      </c>
-      <c r="T38" t="s">
-        <v>23</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
-      <c r="A39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LTR1492_2016</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C39">
         <v>2016</v>
       </c>
       <c r="D39">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E39">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3387,10 +3193,10 @@
         <v>0.6</v>
       </c>
       <c r="H39">
-        <v>0.61111111111111116</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="I39">
-        <v>-1.1111111111111179E-2</v>
+        <v>-0.01111111111111118</v>
       </c>
       <c r="J39">
         <v>0.2</v>
@@ -3405,10 +3211,10 @@
         <v>0.6772113022113021</v>
       </c>
       <c r="N39">
-        <v>0.63421375921375922</v>
+        <v>0.6342137592137592</v>
       </c>
       <c r="O39">
-        <v>4.2997542997542881E-2</v>
+        <v>0.04299754299754288</v>
       </c>
       <c r="P39">
         <v>0.45</v>
@@ -3417,42 +3223,50 @@
         <v>0.44</v>
       </c>
       <c r="R39">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S39" t="s">
-        <v>23</v>
-      </c>
-      <c r="T39" t="s">
-        <v>23</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
-      <c r="A40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LTR1501_2016</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LTR1501</t>
+        </is>
       </c>
       <c r="C40">
         <v>2016</v>
       </c>
       <c r="D40">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E40">
         <v>0.5</v>
       </c>
       <c r="F40">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G40">
-        <v>0.75396825396825395</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="H40">
-        <v>0.75396825396825395</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3467,13 +3281,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M40">
-        <v>0.62055687203791465</v>
+        <v>0.6205568720379147</v>
       </c>
       <c r="N40">
-        <v>0.41024881516587669</v>
+        <v>0.4102488151658767</v>
       </c>
       <c r="O40">
-        <v>0.21030805687203799</v>
+        <v>0.210308056872038</v>
       </c>
       <c r="P40">
         <v>0.46</v>
@@ -3482,24 +3296,32 @@
         <v>0.45</v>
       </c>
       <c r="R40">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S40" t="s">
-        <v>23</v>
-      </c>
-      <c r="T40" t="s">
-        <v>23</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U40" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
-      <c r="A41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" t="s">
-        <v>51</v>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LTR1687_2017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C41">
         <v>2017</v>
@@ -3514,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.57692307692307698</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="H41">
-        <v>0.57692307692307698</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3532,13 +3354,13 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0.66316793893129777</v>
+        <v>0.6631679389312978</v>
       </c>
       <c r="N41">
         <v>0.625</v>
       </c>
       <c r="O41">
-        <v>3.8167938931297767E-2</v>
+        <v>0.03816793893129777</v>
       </c>
       <c r="P41">
         <v>0.54</v>
@@ -3547,42 +3369,50 @@
         <v>0.53</v>
       </c>
       <c r="R41">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S41" t="s">
-        <v>23</v>
-      </c>
-      <c r="T41" t="s">
-        <v>23</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U41" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
-      <c r="A42" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" t="s">
-        <v>44</v>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LTR297_2015</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C42">
         <v>2015</v>
       </c>
       <c r="D42">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E42">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.41666666666666669</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H42">
-        <v>0.41666666666666669</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3597,13 +3427,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M42">
-        <v>0.56864754098360648</v>
+        <v>0.5686475409836065</v>
       </c>
       <c r="N42">
-        <v>0.51229508196721307</v>
+        <v>0.5122950819672131</v>
       </c>
       <c r="O42">
-        <v>5.6352459016393408E-2</v>
+        <v>0.05635245901639341</v>
       </c>
       <c r="P42">
         <v>0.36</v>
@@ -3612,42 +3442,50 @@
         <v>0.35</v>
       </c>
       <c r="R42">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S42" t="s">
-        <v>24</v>
-      </c>
-      <c r="T42" t="s">
-        <v>24</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U42" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
-      <c r="A43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" t="s">
-        <v>87</v>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LTR337_2016</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C43">
         <v>2016</v>
       </c>
       <c r="D43">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E43">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.73888888888888893</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="H43">
-        <v>0.73888888888888893</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3665,10 +3503,10 @@
         <v>0.7444707740916271</v>
       </c>
       <c r="N43">
-        <v>0.71929304897314372</v>
+        <v>0.7192930489731437</v>
       </c>
       <c r="O43">
-        <v>2.517772511848337E-2</v>
+        <v>0.02517772511848337</v>
       </c>
       <c r="P43">
         <v>0.78</v>
@@ -3677,45 +3515,53 @@
         <v>0.77</v>
       </c>
       <c r="R43">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S43" t="s">
-        <v>27</v>
-      </c>
-      <c r="T43" t="s">
-        <v>27</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U43" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
-      <c r="A44" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LTR337_2022</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C44">
         <v>2022</v>
       </c>
       <c r="D44">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E44">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F44">
-        <v>-0.16666666666666671</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="G44">
-        <v>0.72222222222222221</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H44">
-        <v>0.71568627450980393</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="I44">
-        <v>6.5359477124182774E-3</v>
+        <v>0.006535947712418277</v>
       </c>
       <c r="J44">
         <v>0.8</v>
@@ -3727,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0.75930851063829796</v>
+        <v>0.759308510638298</v>
       </c>
       <c r="N44">
-        <v>0.64903846153846156</v>
+        <v>0.6490384615384616</v>
       </c>
       <c r="O44">
         <v>0.1102700490998364</v>
@@ -3742,24 +3588,32 @@
         <v>0.75</v>
       </c>
       <c r="R44">
-        <v>-1.0000000000000011E-2</v>
-      </c>
-      <c r="S44" t="s">
-        <v>27</v>
-      </c>
-      <c r="T44" t="s">
-        <v>27</v>
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U44" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
-      <c r="A45" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LTR351_2019</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LTR351</t>
+        </is>
       </c>
       <c r="C45">
         <v>2019</v>
@@ -3774,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.70454545454545459</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="H45">
         <v>0.7045454545454547</v>
@@ -3783,22 +3637,22 @@
         <v>-1.110223024625157E-16</v>
       </c>
       <c r="J45">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K45">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L45">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M45">
-        <v>0.67630597014925364</v>
+        <v>0.6763059701492536</v>
       </c>
       <c r="N45">
-        <v>0.66697761194029848</v>
+        <v>0.6669776119402985</v>
       </c>
       <c r="O45">
-        <v>9.3283582089551675E-3</v>
+        <v>0.009328358208955168</v>
       </c>
       <c r="P45">
         <v>0.54</v>
@@ -3807,33 +3661,41 @@
         <v>0.53</v>
       </c>
       <c r="R45">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S45" t="s">
-        <v>23</v>
-      </c>
-      <c r="T45" t="s">
-        <v>23</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
-      <c r="A46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" t="s">
-        <v>92</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LTR411_2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LTR411</t>
+        </is>
       </c>
       <c r="C46">
         <v>2022</v>
       </c>
       <c r="D46">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E46">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3842,28 +3704,28 @@
         <v>0.8076923076923076</v>
       </c>
       <c r="H46">
-        <v>0.84615384615384615</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I46">
-        <v>-3.8461538461538547E-2</v>
+        <v>-0.03846153846153855</v>
       </c>
       <c r="J46">
-        <v>0.73333333333333328</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K46">
-        <v>0.73333333333333328</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>0.77741228070175428</v>
+        <v>0.7774122807017543</v>
       </c>
       <c r="N46">
-        <v>0.72149122807017541</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="O46">
-        <v>5.5921052631578871E-2</v>
+        <v>0.05592105263157887</v>
       </c>
       <c r="P46">
         <v>0.75</v>
@@ -3872,193 +3734,217 @@
         <v>0.74</v>
       </c>
       <c r="R46">
-        <v>1.0000000000000011E-2</v>
-      </c>
-      <c r="S46" t="s">
-        <v>27</v>
-      </c>
-      <c r="T46" t="s">
-        <v>27</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U46" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
-      <c r="A47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" t="s">
-        <v>65</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LTR1502_2019</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LTR1502</t>
+        </is>
       </c>
       <c r="C47">
         <v>2019</v>
       </c>
       <c r="D47">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E47">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H47">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K47">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L47">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M47">
-        <v>0.68672839506172834</v>
+        <v>0.6867283950617283</v>
       </c>
       <c r="N47">
-        <v>0.63271604938271608</v>
+        <v>0.6327160493827161</v>
       </c>
       <c r="O47">
-        <v>5.4012345679012252E-2</v>
+        <v>0.05401234567901225</v>
       </c>
       <c r="P47">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="Q47">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R47">
-        <v>9.9999999999998979E-3</v>
-      </c>
-      <c r="S47" t="s">
-        <v>23</v>
-      </c>
-      <c r="T47" t="s">
-        <v>23</v>
+        <v>0.009999999999999898</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U47" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
-      <c r="A48" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LTR337_2019</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C48">
         <v>2019</v>
       </c>
       <c r="D48">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E48">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.65909090909090906</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H48">
-        <v>0.65909090909090906</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K48">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L48">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M48">
         <v>0.6812339331619538</v>
       </c>
       <c r="N48">
-        <v>0.64110824742268036</v>
+        <v>0.6411082474226804</v>
       </c>
       <c r="O48">
-        <v>4.0125685739273442E-2</v>
+        <v>0.04012568573927344</v>
       </c>
       <c r="P48">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="Q48">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R48">
-        <v>9.9999999999998979E-3</v>
-      </c>
-      <c r="S48" t="s">
-        <v>23</v>
-      </c>
-      <c r="T48" t="s">
-        <v>23</v>
+        <v>0.009999999999999898</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U48" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:21">
-      <c r="A49" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" t="s">
-        <v>73</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LTR1063_2017</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LTR1063</t>
+        </is>
       </c>
       <c r="C49">
         <v>2017</v>
       </c>
       <c r="D49">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E49">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.41666666666666669</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H49">
-        <v>0.41666666666666669</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K49">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0.63056615776081426</v>
+        <v>0.6305661577608143</v>
       </c>
       <c r="N49">
-        <v>0.62420483460559795</v>
+        <v>0.6242048346055979</v>
       </c>
       <c r="O49">
-        <v>6.3613231552163141E-3</v>
+        <v>0.006361323155216314</v>
       </c>
       <c r="P49">
         <v>0.36</v>
@@ -4069,22 +3955,30 @@
       <c r="R49">
         <v>0</v>
       </c>
-      <c r="S49" t="s">
-        <v>24</v>
-      </c>
-      <c r="T49" t="s">
-        <v>24</v>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:21">
-      <c r="A50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" t="s">
-        <v>97</v>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LTR1299_2015</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LTR1299</t>
+        </is>
       </c>
       <c r="C50">
         <v>2015</v>
@@ -4099,28 +3993,28 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.97826086956521741</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H50">
         <v>1.007246376811594</v>
       </c>
       <c r="I50">
-        <v>-2.8985507246376611E-2</v>
+        <v>-0.02898550724637661</v>
       </c>
       <c r="J50">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K50">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>0.79053480475381999</v>
+        <v>0.79053480475382</v>
       </c>
       <c r="N50">
-        <v>0.79053480475381999</v>
+        <v>0.79053480475382</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -4134,43 +4028,51 @@
       <c r="R50">
         <v>0</v>
       </c>
-      <c r="S50" t="s">
-        <v>39</v>
-      </c>
-      <c r="T50" t="s">
-        <v>39</v>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U50" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21">
-      <c r="A51" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" t="s">
-        <v>97</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LTR1299_2019</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LTR1299</t>
+        </is>
       </c>
       <c r="C51">
         <v>2019</v>
       </c>
       <c r="D51">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E51">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.92424242424242431</v>
+        <v>0.9242424242424243</v>
       </c>
       <c r="H51">
-        <v>0.93181818181818177</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="I51">
-        <v>-7.575757575757458E-3</v>
+        <v>-0.007575757575757458</v>
       </c>
       <c r="J51">
         <v>0.8</v>
@@ -4182,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0.72261388286334061</v>
+        <v>0.7226138828633406</v>
       </c>
       <c r="N51">
         <v>0.7226138828633405</v>
@@ -4199,22 +4101,30 @@
       <c r="R51">
         <v>0</v>
       </c>
-      <c r="S51" t="s">
-        <v>39</v>
-      </c>
-      <c r="T51" t="s">
-        <v>39</v>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U51" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:21">
-      <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>97</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LTR1299_2022</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LTR1299</t>
+        </is>
       </c>
       <c r="C52">
         <v>2022</v>
@@ -4229,31 +4139,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0.90740740740740744</v>
+        <v>0.9074074074074074</v>
       </c>
       <c r="H52">
-        <v>0.92592592592592593</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="I52">
-        <v>-1.851851851851849E-2</v>
+        <v>-0.01851851851851849</v>
       </c>
       <c r="J52">
-        <v>1.2666666666666671</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="K52">
         <v>1.2</v>
       </c>
       <c r="L52">
-        <v>6.6666666666666652E-2</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="M52">
-        <v>0.95772879464285721</v>
+        <v>0.9577287946428572</v>
       </c>
       <c r="N52">
         <v>0.9556361607142857</v>
       </c>
       <c r="O52">
-        <v>2.0926339285715079E-3</v>
+        <v>0.002092633928571508</v>
       </c>
       <c r="P52">
         <v>1</v>
@@ -4264,22 +4174,30 @@
       <c r="R52">
         <v>0</v>
       </c>
-      <c r="S52" t="s">
-        <v>39</v>
-      </c>
-      <c r="T52" t="s">
-        <v>39</v>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U52" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
-      <c r="A53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" t="s">
-        <v>101</v>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LTR1320_2016</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LTR1320</t>
+        </is>
       </c>
       <c r="C53">
         <v>2016</v>
@@ -4294,13 +4212,13 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0.94642857142857151</v>
+        <v>0.9464285714285715</v>
       </c>
       <c r="H53">
         <v>0.9642857142857143</v>
       </c>
       <c r="I53">
-        <v>-1.785714285714279E-2</v>
+        <v>-0.01785714285714279</v>
       </c>
       <c r="J53">
         <v>1.533333333333333</v>
@@ -4312,10 +4230,10 @@
         <v>0.1333333333333335</v>
       </c>
       <c r="M53">
-        <v>0.86574952561669827</v>
+        <v>0.8657495256166983</v>
       </c>
       <c r="N53">
-        <v>0.86574952561669827</v>
+        <v>0.8657495256166983</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -4329,58 +4247,66 @@
       <c r="R53">
         <v>0</v>
       </c>
-      <c r="S53" t="s">
-        <v>39</v>
-      </c>
-      <c r="T53" t="s">
-        <v>39</v>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:21">
-      <c r="A54" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" t="s">
-        <v>101</v>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LTR1320_2019</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LTR1320</t>
+        </is>
       </c>
       <c r="C54">
         <v>2019</v>
       </c>
       <c r="D54">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E54">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0.85714285714285721</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="H54">
-        <v>0.85606060606060608</v>
+        <v>0.8560606060606061</v>
       </c>
       <c r="I54">
-        <v>1.0822510822511291E-3</v>
+        <v>0.001082251082251129</v>
       </c>
       <c r="J54">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K54">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <v>0.69161991584852722</v>
+        <v>0.6916199158485272</v>
       </c>
       <c r="N54">
-        <v>0.69161991584852733</v>
+        <v>0.6916199158485273</v>
       </c>
       <c r="O54">
         <v>-1.110223024625157E-16</v>
@@ -4394,22 +4320,30 @@
       <c r="R54">
         <v>0</v>
       </c>
-      <c r="S54" t="s">
-        <v>27</v>
-      </c>
-      <c r="T54" t="s">
-        <v>27</v>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:21">
-      <c r="A55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B55" t="s">
-        <v>101</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LTR1320_2022</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LTR1320</t>
+        </is>
       </c>
       <c r="C55">
         <v>2022</v>
@@ -4424,31 +4358,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.94827586206896541</v>
+        <v>0.9482758620689654</v>
       </c>
       <c r="H55">
-        <v>0.96551724137931039</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="I55">
-        <v>-1.724137931034497E-2</v>
+        <v>-0.01724137931034497</v>
       </c>
       <c r="J55">
-        <v>1.0666666666666671</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="K55">
-        <v>1.0666666666666671</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="L55">
-        <v>-4.4408920985006262E-16</v>
+        <v>-4.440892098500626E-16</v>
       </c>
       <c r="M55">
         <v>0.9419642857142857</v>
       </c>
       <c r="N55">
-        <v>0.94332855093256807</v>
+        <v>0.9433285509325681</v>
       </c>
       <c r="O55">
-        <v>-1.364265218282368E-3</v>
+        <v>-0.001364265218282368</v>
       </c>
       <c r="P55">
         <v>0.99</v>
@@ -4459,22 +4393,30 @@
       <c r="R55">
         <v>0</v>
       </c>
-      <c r="S55" t="s">
-        <v>39</v>
-      </c>
-      <c r="T55" t="s">
-        <v>39</v>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U55" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:21">
-      <c r="A56" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56" t="s">
-        <v>105</v>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LTR1379_2015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LTR1379</t>
+        </is>
       </c>
       <c r="C56">
         <v>2015</v>
@@ -4489,31 +4431,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.95454545454545459</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="H56">
-        <v>0.96969696969696972</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="I56">
-        <v>-1.515151515151514E-2</v>
+        <v>-0.01515151515151514</v>
       </c>
       <c r="J56">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K56">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0.78232388316151202</v>
+        <v>0.782323883161512</v>
       </c>
       <c r="N56">
-        <v>0.78178694158075601</v>
+        <v>0.781786941580756</v>
       </c>
       <c r="O56">
-        <v>5.3694158075601184E-4</v>
+        <v>0.0005369415807560118</v>
       </c>
       <c r="P56">
         <v>0.92</v>
@@ -4524,40 +4466,48 @@
       <c r="R56">
         <v>0</v>
       </c>
-      <c r="S56" t="s">
-        <v>39</v>
-      </c>
-      <c r="T56" t="s">
-        <v>39</v>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U56" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
-      <c r="A57" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" t="s">
-        <v>105</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LTR1379_2019</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LTR1379</t>
+        </is>
       </c>
       <c r="C57">
         <v>2019</v>
       </c>
       <c r="D57">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E57">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0.86231884057971009</v>
+        <v>0.8623188405797101</v>
       </c>
       <c r="H57">
-        <v>0.86231884057971009</v>
+        <v>0.8623188405797101</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -4572,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>0.75490552325581395</v>
+        <v>0.7549055232558139</v>
       </c>
       <c r="N57">
-        <v>0.75490552325581395</v>
+        <v>0.7549055232558139</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -4589,40 +4539,48 @@
       <c r="R57">
         <v>0</v>
       </c>
-      <c r="S57" t="s">
-        <v>27</v>
-      </c>
-      <c r="T57" t="s">
-        <v>27</v>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U57" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:21">
-      <c r="A58" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58" t="s">
-        <v>105</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LTR1379_2022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LTR1379</t>
+        </is>
       </c>
       <c r="C58">
         <v>2022</v>
       </c>
       <c r="D58">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E58">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0.80645161290322587</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="H58">
-        <v>0.80645161290322587</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4637,13 +4595,13 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>0.65586756993006989</v>
+        <v>0.6558675699300699</v>
       </c>
       <c r="N58">
-        <v>0.64560439560439564</v>
+        <v>0.6456043956043956</v>
       </c>
       <c r="O58">
-        <v>1.026317432567425E-2</v>
+        <v>0.01026317432567425</v>
       </c>
       <c r="P58">
         <v>0.79</v>
@@ -4654,40 +4612,48 @@
       <c r="R58">
         <v>0</v>
       </c>
-      <c r="S58" t="s">
-        <v>27</v>
-      </c>
-      <c r="T58" t="s">
-        <v>27</v>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U58" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
-      <c r="A59" t="s">
-        <v>108</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LTR1385_2016</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LTR1385</t>
+        </is>
       </c>
       <c r="C59">
         <v>2016</v>
       </c>
       <c r="D59">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E59">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0.97222222222222221</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="H59">
-        <v>0.97222222222222221</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4702,57 +4668,65 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>0.84218146718146714</v>
+        <v>0.8421814671814671</v>
       </c>
       <c r="N59">
-        <v>0.84218146718146714</v>
+        <v>0.8421814671814671</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q59">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R59">
         <v>0</v>
       </c>
-      <c r="S59" t="s">
-        <v>39</v>
-      </c>
-      <c r="T59" t="s">
-        <v>39</v>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U59" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:21">
-      <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60" t="s">
-        <v>109</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LTR1385_2019</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LTR1385</t>
+        </is>
       </c>
       <c r="C60">
         <v>2019</v>
       </c>
       <c r="D60">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E60">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.68333333333333324</v>
+        <v>0.6833333333333332</v>
       </c>
       <c r="H60">
-        <v>0.68333333333333324</v>
+        <v>0.6833333333333332</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4767,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0.75842126623376616</v>
+        <v>0.7584212662337662</v>
       </c>
       <c r="N60">
-        <v>0.75842126623376616</v>
+        <v>0.7584212662337662</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -4784,40 +4758,48 @@
       <c r="R60">
         <v>0</v>
       </c>
-      <c r="S60" t="s">
-        <v>27</v>
-      </c>
-      <c r="T60" t="s">
-        <v>27</v>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:21">
-      <c r="A61" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" t="s">
-        <v>109</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LTR1385_2022</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LTR1385</t>
+        </is>
       </c>
       <c r="C61">
         <v>2022</v>
       </c>
       <c r="D61">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E61">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.81746031746031755</v>
+        <v>0.8174603174603176</v>
       </c>
       <c r="H61">
-        <v>0.81746031746031755</v>
+        <v>0.8174603174603176</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4832,13 +4814,13 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>0.91226708074534157</v>
+        <v>0.9122670807453416</v>
       </c>
       <c r="N61">
-        <v>0.91300940438871458</v>
+        <v>0.9130094043887146</v>
       </c>
       <c r="O61">
-        <v>-7.4232364337301071E-4</v>
+        <v>-0.0007423236433730107</v>
       </c>
       <c r="P61">
         <v>0.75</v>
@@ -4849,22 +4831,30 @@
       <c r="R61">
         <v>0</v>
       </c>
-      <c r="S61" t="s">
-        <v>27</v>
-      </c>
-      <c r="T61" t="s">
-        <v>27</v>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
-      <c r="A62" t="s">
-        <v>112</v>
-      </c>
-      <c r="B62" t="s">
-        <v>48</v>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LTR1447_2019</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LTR1447</t>
+        </is>
       </c>
       <c r="C62">
         <v>2019</v>
@@ -4879,122 +4869,138 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>0.73611111111111116</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="H62">
-        <v>0.73611111111111116</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K62">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L62">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M62">
-        <v>0.70195195195195192</v>
+        <v>0.7019519519519519</v>
       </c>
       <c r="N62">
-        <v>0.70195195195195192</v>
+        <v>0.7019519519519519</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="Q62">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="R62">
         <v>0</v>
       </c>
-      <c r="S62" t="s">
-        <v>23</v>
-      </c>
-      <c r="T62" t="s">
-        <v>23</v>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U62" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:21">
-      <c r="A63" t="s">
-        <v>113</v>
-      </c>
-      <c r="B63" t="s">
-        <v>78</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LTR1449_2019</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LTR1449</t>
+        </is>
       </c>
       <c r="C63">
         <v>2019</v>
       </c>
       <c r="D63">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E63">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>0.84090909090909094</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="H63">
-        <v>0.84782608695652184</v>
+        <v>0.8478260869565218</v>
       </c>
       <c r="I63">
-        <v>-6.9169960474309011E-3</v>
+        <v>-0.006916996047430901</v>
       </c>
       <c r="J63">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K63">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <v>0.75375536480686689</v>
+        <v>0.7537553648068669</v>
       </c>
       <c r="N63">
-        <v>0.75393982808022919</v>
+        <v>0.7539398280802292</v>
       </c>
       <c r="O63">
-        <v>-1.8446327336230081E-4</v>
+        <v>-0.0001844632733623008</v>
       </c>
       <c r="P63">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q63">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R63">
         <v>0</v>
       </c>
-      <c r="S63" t="s">
-        <v>27</v>
-      </c>
-      <c r="T63" t="s">
-        <v>27</v>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U63" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
-      <c r="A64" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" t="s">
-        <v>78</v>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LTR1449_2022</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LTR1449</t>
+        </is>
       </c>
       <c r="C64">
         <v>2022</v>
@@ -5009,28 +5015,28 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.90804597701149425</v>
+        <v>0.9080459770114943</v>
       </c>
       <c r="H64">
         <v>0.9137931034482758</v>
       </c>
       <c r="I64">
-        <v>-5.7471264367815467E-3</v>
+        <v>-0.005747126436781547</v>
       </c>
       <c r="J64">
-        <v>0.73333333333333328</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K64">
-        <v>0.73333333333333328</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
-        <v>0.80741995073891626</v>
+        <v>0.8074199507389163</v>
       </c>
       <c r="N64">
-        <v>0.80741995073891626</v>
+        <v>0.8074199507389163</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -5044,22 +5050,30 @@
       <c r="R64">
         <v>0</v>
       </c>
-      <c r="S64" t="s">
-        <v>39</v>
-      </c>
-      <c r="T64" t="s">
-        <v>39</v>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U64" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
-      <c r="A65" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LTR1501_2019</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LTR1501</t>
+        </is>
       </c>
       <c r="C65">
         <v>2019</v>
@@ -5074,31 +5088,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>0.71153846153846156</v>
+        <v>0.7115384615384616</v>
       </c>
       <c r="H65">
-        <v>0.70370370370370372</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="I65">
-        <v>7.8347578347578439E-3</v>
+        <v>0.007834757834757844</v>
       </c>
       <c r="J65">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="K65">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L65">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="M65">
-        <v>0.64578384798099753</v>
+        <v>0.6457838479809975</v>
       </c>
       <c r="N65">
-        <v>0.63687648456057011</v>
+        <v>0.6368764845605701</v>
       </c>
       <c r="O65">
-        <v>8.9073634204274166E-3</v>
+        <v>0.008907363420427417</v>
       </c>
       <c r="P65">
         <v>0.53</v>
@@ -5109,22 +5123,30 @@
       <c r="R65">
         <v>0</v>
       </c>
-      <c r="S65" t="s">
-        <v>23</v>
-      </c>
-      <c r="T65" t="s">
-        <v>23</v>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U65" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
-      <c r="A66" t="s">
-        <v>116</v>
-      </c>
-      <c r="B66" t="s">
-        <v>83</v>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LTR1501_2022</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LTR1501</t>
+        </is>
       </c>
       <c r="C66">
         <v>2022</v>
@@ -5139,10 +5161,10 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>0.70370370370370372</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="H66">
-        <v>0.70370370370370372</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5160,10 +5182,10 @@
         <v>0.7540137614678899</v>
       </c>
       <c r="N66">
-        <v>0.73967889908256879</v>
+        <v>0.7396788990825688</v>
       </c>
       <c r="O66">
-        <v>1.433486238532111E-2</v>
+        <v>0.01433486238532111</v>
       </c>
       <c r="P66">
         <v>0.52</v>
@@ -5174,61 +5196,69 @@
       <c r="R66">
         <v>0</v>
       </c>
-      <c r="S66" t="s">
-        <v>23</v>
-      </c>
-      <c r="T66" t="s">
-        <v>23</v>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U66" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
-      <c r="A67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" t="s">
-        <v>65</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LTR1502_2022</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LTR1502</t>
+        </is>
       </c>
       <c r="C67">
         <v>2022</v>
       </c>
       <c r="D67">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E67">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0.79012345679012341</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="H67">
-        <v>0.80864197530864201</v>
+        <v>0.808641975308642</v>
       </c>
       <c r="I67">
-        <v>-1.8518518518518601E-2</v>
+        <v>-0.0185185185185186</v>
       </c>
       <c r="J67">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K67">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <v>0.76472809667673725</v>
+        <v>0.7647280966767372</v>
       </c>
       <c r="N67">
-        <v>0.74053030303030298</v>
+        <v>0.740530303030303</v>
       </c>
       <c r="O67">
-        <v>2.4197793646434259E-2</v>
+        <v>0.02419779364643426</v>
       </c>
       <c r="P67">
         <v>0.67</v>
@@ -5239,22 +5269,30 @@
       <c r="R67">
         <v>0</v>
       </c>
-      <c r="S67" t="s">
-        <v>27</v>
-      </c>
-      <c r="T67" t="s">
-        <v>27</v>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U67" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:21">
-      <c r="A68" t="s">
-        <v>118</v>
-      </c>
-      <c r="B68" t="s">
-        <v>119</v>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LTR1601_2021</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LTR1601</t>
+        </is>
       </c>
       <c r="C68">
         <v>2021</v>
@@ -5269,19 +5307,19 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H68">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K68">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -5290,7 +5328,7 @@
         <v>0.5316091954022989</v>
       </c>
       <c r="N68">
-        <v>0.53160919540229878</v>
+        <v>0.5316091954022988</v>
       </c>
       <c r="O68">
         <v>1.110223024625157E-16</v>
@@ -5304,22 +5342,30 @@
       <c r="R68">
         <v>0</v>
       </c>
-      <c r="S68" t="s">
-        <v>33</v>
-      </c>
-      <c r="T68" t="s">
-        <v>33</v>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
       </c>
       <c r="U68" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:21">
-      <c r="A69" t="s">
-        <v>120</v>
-      </c>
-      <c r="B69" t="s">
-        <v>121</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LTR232_2015</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LTR232</t>
+        </is>
       </c>
       <c r="C69">
         <v>2015</v>
@@ -5334,28 +5380,28 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>0.90196078431372551</v>
+        <v>0.9019607843137255</v>
       </c>
       <c r="H69">
-        <v>0.91666666666666663</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I69">
-        <v>-1.4705882352941121E-2</v>
+        <v>-0.01470588235294112</v>
       </c>
       <c r="J69">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K69">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0.69444444444444442</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="N69">
-        <v>0.69444444444444442</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -5369,58 +5415,66 @@
       <c r="R69">
         <v>0</v>
       </c>
-      <c r="S69" t="s">
-        <v>39</v>
-      </c>
-      <c r="T69" t="s">
-        <v>39</v>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="U69" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:21">
-      <c r="A70" t="s">
-        <v>122</v>
-      </c>
-      <c r="B70" t="s">
-        <v>121</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LTR232_2019</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LTR232</t>
+        </is>
       </c>
       <c r="C70">
         <v>2019</v>
       </c>
       <c r="D70">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E70">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>0.77160493827160492</v>
+        <v>0.7716049382716049</v>
       </c>
       <c r="H70">
-        <v>0.77160493827160492</v>
+        <v>0.7716049382716049</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K70">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0.61628919860627174</v>
+        <v>0.6162891986062717</v>
       </c>
       <c r="N70">
-        <v>0.61628919860627174</v>
+        <v>0.6162891986062717</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -5434,22 +5488,30 @@
       <c r="R70">
         <v>0</v>
       </c>
-      <c r="S70" t="s">
-        <v>27</v>
-      </c>
-      <c r="T70" t="s">
-        <v>27</v>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U70" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
-      <c r="A71" t="s">
-        <v>123</v>
-      </c>
-      <c r="B71" t="s">
-        <v>121</v>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LTR232_2022</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LTR232</t>
+        </is>
       </c>
       <c r="C71">
         <v>2022</v>
@@ -5464,19 +5526,19 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>0.71568627450980393</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="H71">
-        <v>0.71568627450980393</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
       <c r="J71">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K71">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -5485,10 +5547,10 @@
         <v>0.6875</v>
       </c>
       <c r="N71">
-        <v>0.66369047619047616</v>
+        <v>0.6636904761904762</v>
       </c>
       <c r="O71">
-        <v>2.3809523809523839E-2</v>
+        <v>0.02380952380952384</v>
       </c>
       <c r="P71">
         <v>0.59</v>
@@ -5499,34 +5561,42 @@
       <c r="R71">
         <v>0</v>
       </c>
-      <c r="S71" t="s">
-        <v>23</v>
-      </c>
-      <c r="T71" t="s">
-        <v>23</v>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U71" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
-      <c r="A72" t="s">
-        <v>124</v>
-      </c>
-      <c r="B72" t="s">
-        <v>75</v>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LTR308_2021</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LTR308</t>
+        </is>
       </c>
       <c r="C72">
         <v>2021</v>
       </c>
       <c r="D72">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E72">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F72">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G72">
         <v>0.25</v>
@@ -5547,10 +5617,10 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>0.63153310104529603</v>
+        <v>0.631533101045296</v>
       </c>
       <c r="N72">
-        <v>0.63153310104529603</v>
+        <v>0.631533101045296</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5564,22 +5634,30 @@
       <c r="R72">
         <v>0</v>
       </c>
-      <c r="S72" t="s">
-        <v>24</v>
-      </c>
-      <c r="T72" t="s">
-        <v>24</v>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U72" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
-      <c r="A73" t="s">
-        <v>125</v>
-      </c>
-      <c r="B73" t="s">
-        <v>90</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LTR351_2015</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LTR351</t>
+        </is>
       </c>
       <c r="C73">
         <v>2015</v>
@@ -5594,13 +5672,13 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>0.70114942528735635</v>
+        <v>0.7011494252873564</v>
       </c>
       <c r="H73">
         <v>0.7055555555555556</v>
       </c>
       <c r="I73">
-        <v>-4.4061302681992487E-3</v>
+        <v>-0.004406130268199249</v>
       </c>
       <c r="J73">
         <v>0.4</v>
@@ -5612,13 +5690,13 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0.74750237868696467</v>
+        <v>0.7475023786869647</v>
       </c>
       <c r="N73">
-        <v>0.74571836346336817</v>
+        <v>0.7457183634633682</v>
       </c>
       <c r="O73">
-        <v>1.7840152235965019E-3</v>
+        <v>0.001784015223596502</v>
       </c>
       <c r="P73">
         <v>0.59</v>
@@ -5629,40 +5707,48 @@
       <c r="R73">
         <v>0</v>
       </c>
-      <c r="S73" t="s">
-        <v>23</v>
-      </c>
-      <c r="T73" t="s">
-        <v>23</v>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U73" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
-      <c r="A74" t="s">
-        <v>126</v>
-      </c>
-      <c r="B74" t="s">
-        <v>90</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LTR351_2022</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LTR351</t>
+        </is>
       </c>
       <c r="C74">
         <v>2022</v>
       </c>
       <c r="D74">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E74">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>0.81547619047619058</v>
+        <v>0.8154761904761906</v>
       </c>
       <c r="H74">
-        <v>0.81547619047619058</v>
+        <v>0.8154761904761906</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5677,13 +5763,13 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0.77499999999999991</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="N74">
-        <v>0.74196927374301669</v>
+        <v>0.7419692737430167</v>
       </c>
       <c r="O74">
-        <v>3.3030726256983223E-2</v>
+        <v>0.03303072625698322</v>
       </c>
       <c r="P74">
         <v>0.71</v>
@@ -5694,43 +5780,51 @@
       <c r="R74">
         <v>0</v>
       </c>
-      <c r="S74" t="s">
-        <v>27</v>
-      </c>
-      <c r="T74" t="s">
-        <v>27</v>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U74" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
-      <c r="A75" t="s">
-        <v>127</v>
-      </c>
-      <c r="B75" t="s">
-        <v>92</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LTR411_2015</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LTR411</t>
+        </is>
       </c>
       <c r="C75">
         <v>2015</v>
       </c>
       <c r="D75">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E75">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0.77011494252873558</v>
+        <v>0.7701149425287356</v>
       </c>
       <c r="H75">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I75">
-        <v>-7.6628352490422103E-3</v>
+        <v>-0.00766283524904221</v>
       </c>
       <c r="J75">
         <v>0.2</v>
@@ -5742,75 +5836,83 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0.65762362637362637</v>
+        <v>0.6576236263736264</v>
       </c>
       <c r="N75">
-        <v>0.62328296703296704</v>
+        <v>0.623282967032967</v>
       </c>
       <c r="O75">
-        <v>3.434065934065933E-2</v>
+        <v>0.03434065934065933</v>
       </c>
       <c r="P75">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="Q75">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="R75">
         <v>0</v>
       </c>
-      <c r="S75" t="s">
-        <v>23</v>
-      </c>
-      <c r="T75" t="s">
-        <v>23</v>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U75" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:21">
-      <c r="A76" t="s">
-        <v>128</v>
-      </c>
-      <c r="B76" t="s">
-        <v>92</v>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LTR411_2019</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LTR411</t>
+        </is>
       </c>
       <c r="C76">
         <v>2019</v>
       </c>
       <c r="D76">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E76">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0.82539682539682546</v>
+        <v>0.8253968253968255</v>
       </c>
       <c r="H76">
-        <v>0.82575757575757569</v>
+        <v>0.8257575757575757</v>
       </c>
       <c r="I76">
-        <v>-3.6075036075022831E-4</v>
+        <v>-0.0003607503607502283</v>
       </c>
       <c r="J76">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K76">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76">
-        <v>0.73792016806722682</v>
+        <v>0.7379201680672268</v>
       </c>
       <c r="N76">
-        <v>0.73792016806722682</v>
+        <v>0.7379201680672268</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -5824,61 +5926,69 @@
       <c r="R76">
         <v>0</v>
       </c>
-      <c r="S76" t="s">
-        <v>27</v>
-      </c>
-      <c r="T76" t="s">
-        <v>27</v>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
-      <c r="A77" t="s">
-        <v>129</v>
-      </c>
-      <c r="B77" t="s">
-        <v>42</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LTR625_2015</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LTR625</t>
+        </is>
       </c>
       <c r="C77">
         <v>2015</v>
       </c>
       <c r="D77">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E77">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0.58333333333333337</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H77">
-        <v>0.57692307692307698</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="I77">
-        <v>6.4102564102563866E-3</v>
+        <v>0.006410256410256387</v>
       </c>
       <c r="J77">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K77">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77">
-        <v>0.63616071428571419</v>
+        <v>0.6361607142857142</v>
       </c>
       <c r="N77">
-        <v>0.63106796116504849</v>
+        <v>0.6310679611650485</v>
       </c>
       <c r="O77">
-        <v>5.0927531206657051E-3</v>
+        <v>0.005092753120665705</v>
       </c>
       <c r="P77">
         <v>0.4</v>
@@ -5889,43 +5999,51 @@
       <c r="R77">
         <v>0</v>
       </c>
-      <c r="S77" t="s">
-        <v>23</v>
-      </c>
-      <c r="T77" t="s">
-        <v>23</v>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U77" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:21">
-      <c r="A78" t="s">
-        <v>130</v>
-      </c>
-      <c r="B78" t="s">
-        <v>42</v>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LTR625_2019</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LTR625</t>
+        </is>
       </c>
       <c r="C78">
         <v>2019</v>
       </c>
       <c r="D78">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E78">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H78">
-        <v>0.83870967741935487</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="I78">
-        <v>-5.3763440860215006E-3</v>
+        <v>-0.005376344086021501</v>
       </c>
       <c r="J78">
         <v>0.4</v>
@@ -5937,39 +6055,47 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>0.71261682242990643</v>
+        <v>0.7126168224299064</v>
       </c>
       <c r="N78">
-        <v>0.70059625212947185</v>
+        <v>0.7005962521294719</v>
       </c>
       <c r="O78">
-        <v>1.2020570300434571E-2</v>
+        <v>0.01202057030043457</v>
       </c>
       <c r="P78">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q78">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R78">
         <v>0</v>
       </c>
-      <c r="S78" t="s">
-        <v>27</v>
-      </c>
-      <c r="T78" t="s">
-        <v>27</v>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="U78" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
-      <c r="A79" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" t="s">
-        <v>132</v>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LTR627_2015</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LTR627</t>
+        </is>
       </c>
       <c r="C79">
         <v>2015</v>
@@ -5984,10 +6110,10 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0.55555555555555547</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="H79">
-        <v>0.55555555555555547</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -6002,48 +6128,56 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>0.59175531914893609</v>
+        <v>0.5917553191489361</v>
       </c>
       <c r="N79">
-        <v>0.59139784946236562</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="O79">
-        <v>3.5746968657046629E-4</v>
+        <v>0.0003574696865704663</v>
       </c>
       <c r="P79">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="Q79">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="R79">
         <v>0</v>
       </c>
-      <c r="S79" t="s">
-        <v>33</v>
-      </c>
-      <c r="T79" t="s">
-        <v>33</v>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
       </c>
       <c r="U79" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:21">
-      <c r="A80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B80" t="s">
-        <v>70</v>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LTR706_2018</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LTR706</t>
+        </is>
       </c>
       <c r="C80">
         <v>2018</v>
       </c>
       <c r="D80">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E80">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -6067,10 +6201,10 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M80">
-        <v>0.74374999999999991</v>
+        <v>0.7437499999999999</v>
       </c>
       <c r="N80">
-        <v>0.74374999999999991</v>
+        <v>0.7437499999999999</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -6084,34 +6218,42 @@
       <c r="R80">
         <v>0</v>
       </c>
-      <c r="S80" t="s">
-        <v>23</v>
-      </c>
-      <c r="T80" t="s">
-        <v>23</v>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="U80" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
-      <c r="A81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B81" t="s">
-        <v>70</v>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LTR706_2021</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LTR706</t>
+        </is>
       </c>
       <c r="C81">
         <v>2021</v>
       </c>
       <c r="D81">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E81">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F81">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G81">
         <v>0.5</v>
@@ -6132,13 +6274,13 @@
         <v>0</v>
       </c>
       <c r="M81">
-        <v>0.66249999999999998</v>
+        <v>0.6625</v>
       </c>
       <c r="N81">
-        <v>0.66326530612244894</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="O81">
-        <v>-7.6530612244896101E-4</v>
+        <v>-0.000765306122448961</v>
       </c>
       <c r="P81">
         <v>0.38</v>
@@ -6149,34 +6291,42 @@
       <c r="R81">
         <v>0</v>
       </c>
-      <c r="S81" t="s">
-        <v>24</v>
-      </c>
-      <c r="T81" t="s">
-        <v>24</v>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U81" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
-      <c r="A82" t="s">
-        <v>135</v>
-      </c>
-      <c r="B82" t="s">
-        <v>46</v>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LTR86_2017</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C82">
         <v>2017</v>
       </c>
       <c r="D82">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E82">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F82">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G82">
         <v>0.5</v>
@@ -6188,19 +6338,19 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="K82">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82">
-        <v>0.79799107142857151</v>
+        <v>0.7979910714285715</v>
       </c>
       <c r="N82">
-        <v>0.79799107142857151</v>
+        <v>0.7979910714285715</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -6214,40 +6364,48 @@
       <c r="R82">
         <v>0</v>
       </c>
-      <c r="S82" t="s">
-        <v>24</v>
-      </c>
-      <c r="T82" t="s">
-        <v>24</v>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U82" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
-      <c r="A83" t="s">
-        <v>136</v>
-      </c>
-      <c r="B83" t="s">
-        <v>46</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LTR86_2020</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C83">
         <v>2020</v>
       </c>
       <c r="D83">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E83">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F83">
-        <v>-5.5511151231257827E-17</v>
+        <v>-5.551115123125783E-17</v>
       </c>
       <c r="G83">
         <v>0.4861111111111111</v>
       </c>
       <c r="H83">
-        <v>0.48611111111111122</v>
+        <v>0.4861111111111112</v>
       </c>
       <c r="I83">
         <v>-1.110223024625157E-16</v>
@@ -6262,13 +6420,13 @@
         <v>2.775557561562891E-17</v>
       </c>
       <c r="M83">
-        <v>0.64524291497975705</v>
+        <v>0.6452429149797571</v>
       </c>
       <c r="N83">
-        <v>0.64536659877800406</v>
+        <v>0.6453665987780041</v>
       </c>
       <c r="O83">
-        <v>-1.2368379824700959E-4</v>
+        <v>-0.0001236837982470096</v>
       </c>
       <c r="P83">
         <v>0.36</v>
@@ -6279,11 +6437,15 @@
       <c r="R83">
         <v>0</v>
       </c>
-      <c r="S83" t="s">
-        <v>24</v>
-      </c>
-      <c r="T83" t="s">
-        <v>24</v>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="U83" t="b">
         <v>1</v>
@@ -6295,161 +6457,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>145</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_residual</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>median_residual</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_abs_res</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pearson_r</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pearson_p</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>pct_exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="B2">
         <v>82</v>
       </c>
       <c r="C2">
-        <v>-8.1300813008130159E-3</v>
+        <v>-0.008130081300813016</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1.6260162601626021E-2</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="F2">
-        <v>0.98057167065517914</v>
+        <v>0.9805716706551791</v>
       </c>
       <c r="G2">
-        <v>2.3248111383687509E-58</v>
+        <v>2.324811138368751E-58</v>
       </c>
       <c r="H2">
-        <v>90.243902439024396</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>146</v>
+        <v>90.2439024390244</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="B3">
         <v>82</v>
       </c>
       <c r="C3">
-        <v>-3.0349976227720772E-3</v>
+        <v>-0.003034997622772077</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8.0009557228063015E-3</v>
+        <v>0.008000955722806301</v>
       </c>
       <c r="F3">
-        <v>0.99489549770906449</v>
+        <v>0.9948954977090645</v>
       </c>
       <c r="G3">
-        <v>1.8456448153608171E-81</v>
+        <v>1.845644815360817E-81</v>
       </c>
       <c r="H3">
-        <v>58.536585365853647</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>147</v>
+        <v>58.53658536585365</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#DEP</t>
+        </is>
       </c>
       <c r="B4">
         <v>82</v>
       </c>
       <c r="C4">
-        <v>4.8780487804877936E-3</v>
+        <v>0.004878048780487794</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4.8780487804878248E-3</v>
+        <v>0.004878048780487825</v>
       </c>
       <c r="F4">
-        <v>0.99827453135450184</v>
+        <v>0.9982745313545018</v>
       </c>
       <c r="G4">
-        <v>2.8330785893447558E-100</v>
+        <v>2.833078589344756E-100</v>
       </c>
       <c r="H4">
-        <v>93.902439024390233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>148</v>
+        <v>93.90243902439023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>%EHP–%CrHi</t>
+        </is>
       </c>
       <c r="B5">
         <v>82</v>
       </c>
       <c r="C5">
-        <v>6.1991911856556323E-2</v>
+        <v>0.06199191185655632</v>
       </c>
       <c r="D5">
-        <v>2.7191666297559421E-2</v>
+        <v>0.02719166629755942</v>
       </c>
       <c r="E5">
-        <v>6.2069473857915183E-2</v>
+        <v>0.06206947385791518</v>
       </c>
       <c r="F5">
-        <v>0.77439977280480576</v>
+        <v>0.7743997728048058</v>
       </c>
       <c r="G5">
-        <v>1.4198582086442121E-17</v>
+        <v>1.419858208644212E-17</v>
       </c>
       <c r="H5">
-        <v>35.365853658536587</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>149</v>
+        <v>35.36585365853659</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
       </c>
       <c r="B6">
         <v>82</v>
       </c>
       <c r="C6">
-        <v>1.4024390243902431E-2</v>
+        <v>0.01402439024390243</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1.7682926829268291E-2</v>
+        <v>0.01768292682926829</v>
       </c>
       <c r="F6">
-        <v>0.99113150060212873</v>
+        <v>0.9911315006021287</v>
       </c>
       <c r="G6">
-        <v>6.7735269143270236E-72</v>
+        <v>6.773526914327024E-72</v>
       </c>
       <c r="H6">
         <v>42.68292682926829</v>
@@ -6461,30 +6649,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>145</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>median_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>W_stat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>W_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="B2">
         <v>82</v>
@@ -6496,12 +6696,14 @@
         <v>21.5</v>
       </c>
       <c r="E2">
-        <v>2.856962661506433E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>146</v>
+        <v>0.02856962661506433</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="B3">
         <v>82</v>
@@ -6513,12 +6715,14 @@
         <v>283</v>
       </c>
       <c r="E3">
-        <v>4.986171585865202E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>147</v>
+        <v>0.004986171585865202</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#DEP</t>
+        </is>
       </c>
       <c r="B4">
         <v>82</v>
@@ -6530,18 +6734,20 @@
         <v>165</v>
       </c>
       <c r="E4">
-        <v>0.67510875834133199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>148</v>
+        <v>0.675108758341332</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>%EHP–%CrHi</t>
+        </is>
       </c>
       <c r="B5">
         <v>82</v>
       </c>
       <c r="C5">
-        <v>2.7191666297559421E-2</v>
+        <v>0.02719166629755942</v>
       </c>
       <c r="D5">
         <v>2173</v>
@@ -6550,9 +6756,11 @@
         <v>9.351120724331913E-12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>153</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LRMI</t>
+        </is>
       </c>
       <c r="B6">
         <v>82</v>
@@ -6564,7 +6772,7 @@
         <v>989</v>
       </c>
       <c r="E6">
-        <v>6.6033834348955154E-6</v>
+        <v>6.603383434895515E-06</v>
       </c>
     </row>
   </sheetData>
@@ -6573,51 +6781,71 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" t="s">
-        <v>161</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LEPA</t>
+        </is>
       </c>
       <c r="C2">
         <v>82</v>
       </c>
       <c r="D2">
-        <v>0.57099999999999995</v>
+        <v>0.571</v>
       </c>
       <c r="E2">
-        <v>0.26100000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="F2">
         <v>0.5</v>
@@ -6629,21 +6857,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" t="s">
-        <v>162</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
       </c>
       <c r="C3">
         <v>82</v>
       </c>
       <c r="D3">
-        <v>0.57899999999999996</v>
+        <v>0.579</v>
       </c>
       <c r="E3">
-        <v>0.26300000000000001</v>
+        <v>0.263</v>
       </c>
       <c r="F3">
         <v>0.5</v>
@@ -6655,12 +6887,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" t="s">
-        <v>161</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LEPA</t>
+        </is>
       </c>
       <c r="C4">
         <v>82</v>
@@ -6669,50 +6905,58 @@
         <v>0.7</v>
       </c>
       <c r="E4">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="F4">
-        <v>0.72499999999999998</v>
+        <v>0.725</v>
       </c>
       <c r="G4">
         <v>0.25</v>
       </c>
       <c r="H4">
-        <v>1.0740000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" t="s">
-        <v>162</v>
+        <v>1.074</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
       </c>
       <c r="C5">
         <v>82</v>
       </c>
       <c r="D5">
-        <v>0.70299999999999996</v>
+        <v>0.703</v>
       </c>
       <c r="E5">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="F5">
-        <v>0.72499999999999998</v>
+        <v>0.725</v>
       </c>
       <c r="G5">
         <v>0.25</v>
       </c>
       <c r="H5">
-        <v>1.0069999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>161</v>
+        <v>1.007</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#DEP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LEPA</t>
+        </is>
       </c>
       <c r="C6">
         <v>82</v>
@@ -6721,24 +6965,28 @@
         <v>0.437</v>
       </c>
       <c r="E6">
-        <v>0.31900000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="F6">
-        <v>0.36699999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>1.5329999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" t="s">
-        <v>162</v>
+        <v>1.533</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#DEP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
       </c>
       <c r="C7">
         <v>82</v>
@@ -6750,7 +6998,7 @@
         <v>0.311</v>
       </c>
       <c r="F7">
-        <v>0.36699999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -6759,76 +7007,88 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>161</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>%EHP–%CrHi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LEPA</t>
+        </is>
       </c>
       <c r="C8">
         <v>82</v>
       </c>
       <c r="D8">
-        <v>0.71799999999999997</v>
+        <v>0.718</v>
       </c>
       <c r="E8">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="F8">
-        <v>0.70299999999999996</v>
+        <v>0.703</v>
       </c>
       <c r="G8">
-        <v>0.53200000000000003</v>
+        <v>0.532</v>
       </c>
       <c r="H8">
         <v>1.052</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B9" t="s">
-        <v>162</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>%EHP–%CrHi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
       </c>
       <c r="C9">
         <v>82</v>
       </c>
       <c r="D9">
-        <v>0.65600000000000003</v>
+        <v>0.656</v>
       </c>
       <c r="E9">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="F9">
-        <v>0.65700000000000003</v>
+        <v>0.657</v>
       </c>
       <c r="G9">
         <v>0.21</v>
       </c>
       <c r="H9">
-        <v>1.0429999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" t="s">
-        <v>161</v>
+        <v>1.043</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LEPA</t>
+        </is>
       </c>
       <c r="C10">
         <v>82</v>
       </c>
       <c r="D10">
-        <v>0.60499999999999998</v>
+        <v>0.605</v>
       </c>
       <c r="E10">
         <v>0.185</v>
       </c>
       <c r="F10">
-        <v>0.59499999999999997</v>
+        <v>0.595</v>
       </c>
       <c r="G10">
         <v>0.23</v>
@@ -6837,18 +7097,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" t="s">
-        <v>162</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
       </c>
       <c r="C11">
         <v>82</v>
       </c>
       <c r="D11">
-        <v>0.59099999999999997</v>
+        <v>0.591</v>
       </c>
       <c r="E11">
         <v>0.189</v>
@@ -6869,71 +7133,89 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>145</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LEPA − LT-OTL (mean)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LEPA − LT-OTL (median)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |residual|</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson r</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>% within ±0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="B2">
         <v>82</v>
       </c>
       <c r="C2">
-        <v>-8.0999999999999996E-3</v>
+        <v>-0.0081</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1.6299999999999999E-2</v>
+        <v>0.0163</v>
       </c>
       <c r="F2">
-        <v>0.98099999999999998</v>
+        <v>0.981</v>
       </c>
       <c r="G2">
         <v>90.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>146</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="B3">
         <v>82</v>
       </c>
       <c r="C3">
-        <v>-3.0000000000000001E-3</v>
+        <v>-0.003</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="F3">
         <v>0.995</v>
@@ -6942,70 +7224,76 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>147</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#DEP</t>
+        </is>
       </c>
       <c r="B4">
         <v>82</v>
       </c>
       <c r="C4">
-        <v>4.8999999999999998E-3</v>
+        <v>0.0049</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4.8999999999999998E-3</v>
+        <v>0.0049</v>
       </c>
       <c r="F4">
         <v>0.998</v>
       </c>
       <c r="G4">
-        <v>93.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>148</v>
+        <v>93.90000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>%EHP–%CrHi</t>
+        </is>
       </c>
       <c r="B5">
         <v>82</v>
       </c>
       <c r="C5">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="D5">
-        <v>2.7199999999999998E-2</v>
+        <v>0.0272</v>
       </c>
       <c r="E5">
-        <v>6.2100000000000002E-2</v>
+        <v>0.0621</v>
       </c>
       <c r="F5">
-        <v>0.77400000000000002</v>
+        <v>0.774</v>
       </c>
       <c r="G5">
         <v>35.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>149</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
       </c>
       <c r="B6">
         <v>82</v>
       </c>
       <c r="C6">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1.77E-2</v>
+        <v>0.0177</v>
       </c>
       <c r="F6">
-        <v>0.99099999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="G6">
         <v>42.7</v>
